--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -10197,7 +10197,7 @@
         <v/>
       </c>
       <c r="J196" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="K196" t="str">
         <v>Manual</v>
@@ -13458,7 +13458,7 @@
         <v>UK work days (max 30)</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -13474,7 +13474,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -10176,7 +10176,7 @@
         <v>Monday</v>
       </c>
       <c r="C196" t="str">
-        <v>417 Meadow Lane</v>
+        <v>Oxford</v>
       </c>
       <c r="D196" t="str">
         <v>Oxford</v>
@@ -13474,7 +13474,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z257"/>
+  <dimension ref="A1:AA257"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -410,22 +410,23 @@
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
     <col min="10" max="10" width="24.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" customWidth="1"/>
-    <col min="15" max="15" width="24.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
     <col min="16" max="16" width="24.83203125" customWidth="1"/>
-    <col min="17" max="17" width="18.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="24.83203125" customWidth="1"/>
+    <col min="17" max="17" width="24.83203125" customWidth="1"/>
+    <col min="18" max="18" width="18.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
     <col min="20" max="20" width="24.83203125" customWidth="1"/>
-    <col min="21" max="21" width="14.83203125" customWidth="1"/>
-    <col min="22" max="22" width="30.83203125" customWidth="1"/>
-    <col min="23" max="23" width="50.83203125" customWidth="1"/>
-    <col min="24" max="24" width="8.83203125" customWidth="1"/>
-    <col min="25" max="25" width="10.83203125" customWidth="1"/>
-    <col min="26" max="26" width="12.83203125" customWidth="1"/>
+    <col min="21" max="21" width="24.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="23" max="23" width="30.83203125" customWidth="1"/>
+    <col min="24" max="24" width="50.83203125" customWidth="1"/>
+    <col min="25" max="25" width="8.83203125" customWidth="1"/>
+    <col min="26" max="26" width="10.83203125" customWidth="1"/>
+    <col min="27" max="27" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,51 +461,54 @@
         <v>GPS captured at</v>
       </c>
       <c r="K1" t="str">
+        <v>GPS trigger</v>
+      </c>
+      <c r="L1" t="str">
         <v>Working</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Source</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Evening city</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Evening country</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Evening GPS</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Evening captured at</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Morning city</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Morning country</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>Morning GPS</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>Morning captured at</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>Bracket inferred</v>
       </c>
-      <c r="V1" t="str">
+      <c r="W1" t="str">
         <v>Country conflict</v>
       </c>
-      <c r="W1" t="str">
+      <c r="X1" t="str">
         <v>Booking source</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Y1" t="str">
         <v>Auto GPS</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="Z1" t="str">
         <v>Auto booking</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AA1" t="str">
         <v>GPS confirmed</v>
       </c>
     </row>
@@ -543,11 +547,11 @@
         <v/>
       </c>
       <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>Booking</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
       <c r="N2" t="str">
         <v/>
       </c>
@@ -576,15 +580,18 @@
         <v/>
       </c>
       <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
         <v>calendar: Flight TG623: Osaka - BKK, departs 11:45am</v>
       </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
       <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="AA2" t="str">
         <v/>
       </c>
     </row>
@@ -623,11 +630,11 @@
         <v/>
       </c>
       <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>Booking</v>
       </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
       <c r="N3" t="str">
         <v/>
       </c>
@@ -656,15 +663,18 @@
         <v/>
       </c>
       <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
         <v>calendar: Flight TG916: BKK - LHR, departs 12:50</v>
       </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
       <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z3" t="str">
+      <c r="AA3" t="str">
         <v/>
       </c>
     </row>
@@ -703,11 +713,11 @@
         <v/>
       </c>
       <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>Booking</v>
       </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
       <c r="N4" t="str">
         <v/>
       </c>
@@ -736,15 +746,18 @@
         <v/>
       </c>
       <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
         <v>calendar: flights to ski</v>
       </c>
-      <c r="X4" t="str">
-        <v/>
-      </c>
       <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z4" t="str">
+      <c r="AA4" t="str">
         <v/>
       </c>
     </row>
@@ -783,11 +796,11 @@
         <v/>
       </c>
       <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>Booking</v>
       </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
       <c r="N5" t="str">
         <v/>
       </c>
@@ -816,15 +829,18 @@
         <v/>
       </c>
       <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
         <v>calendar: Sheraton Milan Malpensa Airport Hotel &amp; Conference Centre check in</v>
       </c>
-      <c r="X5" t="str">
-        <v/>
-      </c>
       <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z5" t="str">
+      <c r="AA5" t="str">
         <v/>
       </c>
     </row>
@@ -863,11 +879,11 @@
         <v/>
       </c>
       <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>Booking</v>
       </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
       <c r="N6" t="str">
         <v/>
       </c>
@@ -896,15 +912,18 @@
         <v/>
       </c>
       <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
         <v>calendar: Sheraton Milan Malpensa Airport Hotel &amp; Conference Centre check out</v>
       </c>
-      <c r="X6" t="str">
-        <v/>
-      </c>
       <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z6" t="str">
+      <c r="AA6" t="str">
         <v/>
       </c>
     </row>
@@ -943,11 +962,11 @@
         <v/>
       </c>
       <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>Booking</v>
       </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
       <c r="N7" t="str">
         <v/>
       </c>
@@ -976,15 +995,18 @@
         <v/>
       </c>
       <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
         <v>email: Fw: Your e-ticket receipt Z4CHJV: 22 May 2025 07:40</v>
       </c>
-      <c r="X7" t="str">
-        <v/>
-      </c>
       <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z7" t="str">
+      <c r="AA7" t="str">
         <v/>
       </c>
     </row>
@@ -1023,11 +1045,11 @@
         <v/>
       </c>
       <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>Booking</v>
       </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
       <c r="N8" t="str">
         <v/>
       </c>
@@ -1056,15 +1078,18 @@
         <v/>
       </c>
       <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
         <v>email: Fw: Your booking confirmation ZTYPRP</v>
       </c>
-      <c r="X8" t="str">
-        <v/>
-      </c>
       <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z8" t="str">
+      <c r="AA8" t="str">
         <v/>
       </c>
     </row>
@@ -1103,11 +1128,11 @@
         <v/>
       </c>
       <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>Booking</v>
       </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
       <c r="N9" t="str">
         <v/>
       </c>
@@ -1136,15 +1161,18 @@
         <v/>
       </c>
       <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
         <v xml:space="preserve">calendar: VC Teams re Cernobbio </v>
       </c>
-      <c r="X9" t="str">
-        <v/>
-      </c>
       <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z9" t="str">
+      <c r="AA9" t="str">
         <v/>
       </c>
     </row>
@@ -1183,11 +1211,11 @@
         <v/>
       </c>
       <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>Booking</v>
       </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
       <c r="N10" t="str">
         <v/>
       </c>
@@ -1216,15 +1244,18 @@
         <v/>
       </c>
       <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
         <v>calendar: Flight BA2588: Gatwick - Verona, departs 07:40am</v>
       </c>
-      <c r="X10" t="str">
-        <v/>
-      </c>
       <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z10" t="str">
+      <c r="AA10" t="str">
         <v/>
       </c>
     </row>
@@ -1263,11 +1294,11 @@
         <v/>
       </c>
       <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>Booking</v>
       </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
       <c r="N11" t="str">
         <v/>
       </c>
@@ -1296,15 +1327,18 @@
         <v/>
       </c>
       <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
         <v>calendar: Flight BA0585: Malpensa - LHR, departs 08:10am</v>
       </c>
-      <c r="X11" t="str">
-        <v/>
-      </c>
       <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z11" t="str">
+      <c r="AA11" t="str">
         <v/>
       </c>
     </row>
@@ -1343,11 +1377,11 @@
         <v/>
       </c>
       <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>Booking</v>
       </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
       <c r="N12" t="str">
         <v/>
       </c>
@@ -1376,15 +1410,18 @@
         <v/>
       </c>
       <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
         <v>email: Fw: Confirmation of your booking</v>
       </c>
-      <c r="X12" t="str">
-        <v/>
-      </c>
       <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z12" t="str">
+      <c r="AA12" t="str">
         <v/>
       </c>
     </row>
@@ -1423,11 +1460,11 @@
         <v/>
       </c>
       <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>Booking</v>
       </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
       <c r="N13" t="str">
         <v/>
       </c>
@@ -1456,15 +1493,18 @@
         <v/>
       </c>
       <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
         <v>calendar: Flight BA570: LHR-LIN, departs 18:45</v>
       </c>
-      <c r="X13" t="str">
-        <v/>
-      </c>
       <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z13" t="str">
+      <c r="AA13" t="str">
         <v/>
       </c>
     </row>
@@ -1503,11 +1543,11 @@
         <v/>
       </c>
       <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>Booking</v>
       </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
       <c r="N14" t="str">
         <v/>
       </c>
@@ -1536,15 +1576,18 @@
         <v/>
       </c>
       <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
         <v>calendar: The Westin Palace, Milan check in</v>
       </c>
-      <c r="X14" t="str">
-        <v/>
-      </c>
       <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z14" t="str">
+      <c r="AA14" t="str">
         <v/>
       </c>
     </row>
@@ -1583,11 +1626,11 @@
         <v/>
       </c>
       <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>Booking</v>
       </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
       <c r="N15" t="str">
         <v/>
       </c>
@@ -1616,15 +1659,18 @@
         <v/>
       </c>
       <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
         <v>calendar: The Westin Palace, Milan check out</v>
       </c>
-      <c r="X15" t="str">
-        <v/>
-      </c>
       <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z15" t="str">
+      <c r="AA15" t="str">
         <v/>
       </c>
     </row>
@@ -1663,11 +1709,11 @@
         <v/>
       </c>
       <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>Booking</v>
       </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
       <c r="N16" t="str">
         <v/>
       </c>
@@ -1696,15 +1742,18 @@
         <v/>
       </c>
       <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X16" t="str">
-        <v/>
-      </c>
       <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z16" t="str">
+      <c r="AA16" t="str">
         <v/>
       </c>
     </row>
@@ -1743,11 +1792,11 @@
         <v/>
       </c>
       <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>Booking</v>
       </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
       <c r="N17" t="str">
         <v/>
       </c>
@@ -1776,15 +1825,18 @@
         <v/>
       </c>
       <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X17" t="str">
-        <v/>
-      </c>
       <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z17" t="str">
+      <c r="AA17" t="str">
         <v/>
       </c>
     </row>
@@ -1823,11 +1875,11 @@
         <v/>
       </c>
       <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v>Booking</v>
       </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
       <c r="N18" t="str">
         <v/>
       </c>
@@ -1856,15 +1908,18 @@
         <v/>
       </c>
       <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X18" t="str">
-        <v/>
-      </c>
       <c r="Y18" t="str">
+        <v/>
+      </c>
+      <c r="Z18" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z18" t="str">
+      <c r="AA18" t="str">
         <v/>
       </c>
     </row>
@@ -1903,11 +1958,11 @@
         <v/>
       </c>
       <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
         <v>Booking</v>
       </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
       <c r="N19" t="str">
         <v/>
       </c>
@@ -1936,15 +1991,18 @@
         <v/>
       </c>
       <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X19" t="str">
-        <v/>
-      </c>
       <c r="Y19" t="str">
+        <v/>
+      </c>
+      <c r="Z19" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z19" t="str">
+      <c r="AA19" t="str">
         <v/>
       </c>
     </row>
@@ -1983,11 +2041,11 @@
         <v/>
       </c>
       <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <v>Booking</v>
       </c>
-      <c r="M20" t="str">
-        <v/>
-      </c>
       <c r="N20" t="str">
         <v/>
       </c>
@@ -2016,15 +2074,18 @@
         <v/>
       </c>
       <c r="W20" t="str">
+        <v/>
+      </c>
+      <c r="X20" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X20" t="str">
-        <v/>
-      </c>
       <c r="Y20" t="str">
+        <v/>
+      </c>
+      <c r="Z20" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z20" t="str">
+      <c r="AA20" t="str">
         <v/>
       </c>
     </row>
@@ -2063,11 +2124,11 @@
         <v/>
       </c>
       <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <v>Booking</v>
       </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
       <c r="N21" t="str">
         <v/>
       </c>
@@ -2096,15 +2157,18 @@
         <v/>
       </c>
       <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X21" t="str">
-        <v/>
-      </c>
       <c r="Y21" t="str">
+        <v/>
+      </c>
+      <c r="Z21" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z21" t="str">
+      <c r="AA21" t="str">
         <v/>
       </c>
     </row>
@@ -2143,11 +2207,11 @@
         <v/>
       </c>
       <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
         <v>Booking</v>
       </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
       <c r="N22" t="str">
         <v/>
       </c>
@@ -2176,15 +2240,18 @@
         <v/>
       </c>
       <c r="W22" t="str">
+        <v/>
+      </c>
+      <c r="X22" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X22" t="str">
-        <v/>
-      </c>
       <c r="Y22" t="str">
+        <v/>
+      </c>
+      <c r="Z22" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z22" t="str">
+      <c r="AA22" t="str">
         <v/>
       </c>
     </row>
@@ -2223,11 +2290,11 @@
         <v/>
       </c>
       <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
         <v>Booking</v>
       </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
       <c r="N23" t="str">
         <v/>
       </c>
@@ -2256,15 +2323,18 @@
         <v/>
       </c>
       <c r="W23" t="str">
+        <v/>
+      </c>
+      <c r="X23" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X23" t="str">
-        <v/>
-      </c>
       <c r="Y23" t="str">
+        <v/>
+      </c>
+      <c r="Z23" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z23" t="str">
+      <c r="AA23" t="str">
         <v/>
       </c>
     </row>
@@ -2303,11 +2373,11 @@
         <v/>
       </c>
       <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
         <v>Booking</v>
       </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
       <c r="N24" t="str">
         <v/>
       </c>
@@ -2336,15 +2406,18 @@
         <v/>
       </c>
       <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X24" t="str">
-        <v/>
-      </c>
       <c r="Y24" t="str">
+        <v/>
+      </c>
+      <c r="Z24" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z24" t="str">
+      <c r="AA24" t="str">
         <v/>
       </c>
     </row>
@@ -2383,11 +2456,11 @@
         <v/>
       </c>
       <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
         <v>Booking</v>
       </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
       <c r="N25" t="str">
         <v/>
       </c>
@@ -2416,15 +2489,18 @@
         <v/>
       </c>
       <c r="W25" t="str">
+        <v/>
+      </c>
+      <c r="X25" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X25" t="str">
-        <v/>
-      </c>
       <c r="Y25" t="str">
+        <v/>
+      </c>
+      <c r="Z25" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z25" t="str">
+      <c r="AA25" t="str">
         <v/>
       </c>
     </row>
@@ -2463,11 +2539,11 @@
         <v/>
       </c>
       <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
         <v>Booking</v>
       </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
       <c r="N26" t="str">
         <v/>
       </c>
@@ -2496,15 +2572,18 @@
         <v/>
       </c>
       <c r="W26" t="str">
+        <v/>
+      </c>
+      <c r="X26" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X26" t="str">
-        <v/>
-      </c>
       <c r="Y26" t="str">
+        <v/>
+      </c>
+      <c r="Z26" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z26" t="str">
+      <c r="AA26" t="str">
         <v/>
       </c>
     </row>
@@ -2543,11 +2622,11 @@
         <v/>
       </c>
       <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
         <v>Booking</v>
       </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
       <c r="N27" t="str">
         <v/>
       </c>
@@ -2576,15 +2655,18 @@
         <v/>
       </c>
       <c r="W27" t="str">
+        <v/>
+      </c>
+      <c r="X27" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X27" t="str">
-        <v/>
-      </c>
       <c r="Y27" t="str">
+        <v/>
+      </c>
+      <c r="Z27" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z27" t="str">
+      <c r="AA27" t="str">
         <v/>
       </c>
     </row>
@@ -2623,11 +2705,11 @@
         <v/>
       </c>
       <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
         <v>Booking</v>
       </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
       <c r="N28" t="str">
         <v/>
       </c>
@@ -2656,15 +2738,18 @@
         <v/>
       </c>
       <c r="W28" t="str">
+        <v/>
+      </c>
+      <c r="X28" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X28" t="str">
-        <v/>
-      </c>
       <c r="Y28" t="str">
+        <v/>
+      </c>
+      <c r="Z28" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z28" t="str">
+      <c r="AA28" t="str">
         <v/>
       </c>
     </row>
@@ -2703,11 +2788,11 @@
         <v/>
       </c>
       <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
         <v>Booking</v>
       </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
       <c r="N29" t="str">
         <v/>
       </c>
@@ -2736,15 +2821,18 @@
         <v/>
       </c>
       <c r="W29" t="str">
+        <v/>
+      </c>
+      <c r="X29" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X29" t="str">
-        <v/>
-      </c>
       <c r="Y29" t="str">
+        <v/>
+      </c>
+      <c r="Z29" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z29" t="str">
+      <c r="AA29" t="str">
         <v/>
       </c>
     </row>
@@ -2783,11 +2871,11 @@
         <v/>
       </c>
       <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
         <v>Booking</v>
       </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
       <c r="N30" t="str">
         <v/>
       </c>
@@ -2816,15 +2904,18 @@
         <v/>
       </c>
       <c r="W30" t="str">
+        <v/>
+      </c>
+      <c r="X30" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X30" t="str">
-        <v/>
-      </c>
       <c r="Y30" t="str">
+        <v/>
+      </c>
+      <c r="Z30" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z30" t="str">
+      <c r="AA30" t="str">
         <v/>
       </c>
     </row>
@@ -2863,11 +2954,11 @@
         <v/>
       </c>
       <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
         <v>Booking</v>
       </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
       <c r="N31" t="str">
         <v/>
       </c>
@@ -2896,15 +2987,18 @@
         <v/>
       </c>
       <c r="W31" t="str">
+        <v/>
+      </c>
+      <c r="X31" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X31" t="str">
-        <v/>
-      </c>
       <c r="Y31" t="str">
+        <v/>
+      </c>
+      <c r="Z31" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z31" t="str">
+      <c r="AA31" t="str">
         <v/>
       </c>
     </row>
@@ -2943,11 +3037,11 @@
         <v/>
       </c>
       <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
         <v>Booking</v>
       </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
       <c r="N32" t="str">
         <v/>
       </c>
@@ -2976,15 +3070,18 @@
         <v/>
       </c>
       <c r="W32" t="str">
+        <v/>
+      </c>
+      <c r="X32" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X32" t="str">
-        <v/>
-      </c>
       <c r="Y32" t="str">
+        <v/>
+      </c>
+      <c r="Z32" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z32" t="str">
+      <c r="AA32" t="str">
         <v/>
       </c>
     </row>
@@ -3023,11 +3120,11 @@
         <v/>
       </c>
       <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
         <v>Booking</v>
       </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
       <c r="N33" t="str">
         <v/>
       </c>
@@ -3056,15 +3153,18 @@
         <v/>
       </c>
       <c r="W33" t="str">
+        <v/>
+      </c>
+      <c r="X33" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X33" t="str">
-        <v/>
-      </c>
       <c r="Y33" t="str">
+        <v/>
+      </c>
+      <c r="Z33" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z33" t="str">
+      <c r="AA33" t="str">
         <v/>
       </c>
     </row>
@@ -3103,11 +3203,11 @@
         <v/>
       </c>
       <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
         <v>Booking</v>
       </c>
-      <c r="M34" t="str">
-        <v/>
-      </c>
       <c r="N34" t="str">
         <v/>
       </c>
@@ -3136,15 +3236,18 @@
         <v/>
       </c>
       <c r="W34" t="str">
+        <v/>
+      </c>
+      <c r="X34" t="str">
         <v>email: Fw: Thank you for booking with us | From London to Bangkok on 21 June 2025</v>
       </c>
-      <c r="X34" t="str">
-        <v/>
-      </c>
       <c r="Y34" t="str">
+        <v/>
+      </c>
+      <c r="Z34" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z34" t="str">
+      <c r="AA34" t="str">
         <v/>
       </c>
     </row>
@@ -3183,11 +3286,11 @@
         <v/>
       </c>
       <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
         <v>Booking</v>
       </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
       <c r="N35" t="str">
         <v/>
       </c>
@@ -3216,15 +3319,18 @@
         <v/>
       </c>
       <c r="W35" t="str">
+        <v/>
+      </c>
+      <c r="X35" t="str">
         <v>calendar: Flight LX333: LHR - ZUR, departs 13:45</v>
       </c>
-      <c r="X35" t="str">
-        <v/>
-      </c>
       <c r="Y35" t="str">
+        <v/>
+      </c>
+      <c r="Z35" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z35" t="str">
+      <c r="AA35" t="str">
         <v/>
       </c>
     </row>
@@ -3263,11 +3369,11 @@
         <v/>
       </c>
       <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
         <v>Booking</v>
       </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
       <c r="N36" t="str">
         <v/>
       </c>
@@ -3296,15 +3402,18 @@
         <v/>
       </c>
       <c r="W36" t="str">
+        <v/>
+      </c>
+      <c r="X36" t="str">
         <v>calendar: The Westin Singapore check in</v>
       </c>
-      <c r="X36" t="str">
-        <v/>
-      </c>
       <c r="Y36" t="str">
+        <v/>
+      </c>
+      <c r="Z36" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z36" t="str">
+      <c r="AA36" t="str">
         <v/>
       </c>
     </row>
@@ -3343,11 +3452,11 @@
         <v/>
       </c>
       <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
         <v>Booking</v>
       </c>
-      <c r="M37" t="str">
-        <v/>
-      </c>
       <c r="N37" t="str">
         <v/>
       </c>
@@ -3376,15 +3485,18 @@
         <v/>
       </c>
       <c r="W37" t="str">
+        <v/>
+      </c>
+      <c r="X37" t="str">
         <v>calendar: Flight LH769: SIN - MUC, departs 23:25</v>
       </c>
-      <c r="X37" t="str">
-        <v/>
-      </c>
       <c r="Y37" t="str">
+        <v/>
+      </c>
+      <c r="Z37" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z37" t="str">
+      <c r="AA37" t="str">
         <v/>
       </c>
     </row>
@@ -3423,11 +3535,11 @@
         <v/>
       </c>
       <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
         <v>Booking</v>
       </c>
-      <c r="M38" t="str">
-        <v/>
-      </c>
       <c r="N38" t="str">
         <v/>
       </c>
@@ -3456,15 +3568,18 @@
         <v/>
       </c>
       <c r="W38" t="str">
+        <v/>
+      </c>
+      <c r="X38" t="str">
         <v>calendar: Flight LH2470: MUC - LHR, departs 07:10am</v>
       </c>
-      <c r="X38" t="str">
-        <v/>
-      </c>
       <c r="Y38" t="str">
+        <v/>
+      </c>
+      <c r="Z38" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z38" t="str">
+      <c r="AA38" t="str">
         <v/>
       </c>
     </row>
@@ -3503,11 +3618,11 @@
         <v/>
       </c>
       <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
         <v>Booking</v>
       </c>
-      <c r="M39" t="str">
-        <v/>
-      </c>
       <c r="N39" t="str">
         <v/>
       </c>
@@ -3536,15 +3651,18 @@
         <v/>
       </c>
       <c r="W39" t="str">
+        <v/>
+      </c>
+      <c r="X39" t="str">
         <v>calendar: Sonder Atelier Apartments Porta Romana check in</v>
       </c>
-      <c r="X39" t="str">
-        <v/>
-      </c>
       <c r="Y39" t="str">
+        <v/>
+      </c>
+      <c r="Z39" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z39" t="str">
+      <c r="AA39" t="str">
         <v/>
       </c>
     </row>
@@ -3583,11 +3701,11 @@
         <v/>
       </c>
       <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
         <v>Booking</v>
       </c>
-      <c r="M40" t="str">
-        <v/>
-      </c>
       <c r="N40" t="str">
         <v/>
       </c>
@@ -3616,15 +3734,18 @@
         <v/>
       </c>
       <c r="W40" t="str">
+        <v/>
+      </c>
+      <c r="X40" t="str">
         <v>calendar: Finance department review</v>
       </c>
-      <c r="X40" t="str">
-        <v/>
-      </c>
       <c r="Y40" t="str">
+        <v/>
+      </c>
+      <c r="Z40" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z40" t="str">
+      <c r="AA40" t="str">
         <v/>
       </c>
     </row>
@@ -3663,11 +3784,11 @@
         <v/>
       </c>
       <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
         <v>Booking</v>
       </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
       <c r="N41" t="str">
         <v/>
       </c>
@@ -3696,15 +3817,18 @@
         <v/>
       </c>
       <c r="W41" t="str">
+        <v/>
+      </c>
+      <c r="X41" t="str">
         <v>calendar: Sonder Atelier Apartments Porta Romana check out</v>
       </c>
-      <c r="X41" t="str">
-        <v/>
-      </c>
       <c r="Y41" t="str">
+        <v/>
+      </c>
+      <c r="Z41" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z41" t="str">
+      <c r="AA41" t="str">
         <v/>
       </c>
     </row>
@@ -3743,11 +3867,11 @@
         <v/>
       </c>
       <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
         <v>Booking</v>
       </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
       <c r="N42" t="str">
         <v/>
       </c>
@@ -3776,15 +3900,18 @@
         <v/>
       </c>
       <c r="W42" t="str">
+        <v/>
+      </c>
+      <c r="X42" t="str">
         <v>email: Fw: Booking: 13 August</v>
       </c>
-      <c r="X42" t="str">
-        <v/>
-      </c>
       <c r="Y42" t="str">
+        <v/>
+      </c>
+      <c r="Z42" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z42" t="str">
+      <c r="AA42" t="str">
         <v/>
       </c>
     </row>
@@ -3823,11 +3950,11 @@
         <v/>
       </c>
       <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
         <v>Booking</v>
       </c>
-      <c r="M43" t="str">
-        <v/>
-      </c>
       <c r="N43" t="str">
         <v/>
       </c>
@@ -3856,15 +3983,18 @@
         <v/>
       </c>
       <c r="W43" t="str">
+        <v/>
+      </c>
+      <c r="X43" t="str">
         <v>calendar: Casa Brera, a Luxury Collection Hotel, Milan check out</v>
       </c>
-      <c r="X43" t="str">
-        <v/>
-      </c>
       <c r="Y43" t="str">
+        <v/>
+      </c>
+      <c r="Z43" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z43" t="str">
+      <c r="AA43" t="str">
         <v/>
       </c>
     </row>
@@ -3903,11 +4033,11 @@
         <v/>
       </c>
       <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
         <v>Booking</v>
       </c>
-      <c r="M44" t="str">
-        <v/>
-      </c>
       <c r="N44" t="str">
         <v/>
       </c>
@@ -3936,15 +4066,18 @@
         <v/>
       </c>
       <c r="W44" t="str">
+        <v/>
+      </c>
+      <c r="X44" t="str">
         <v>calendar: The Westin Palace, Milan check in</v>
       </c>
-      <c r="X44" t="str">
-        <v/>
-      </c>
       <c r="Y44" t="str">
+        <v/>
+      </c>
+      <c r="Z44" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z44" t="str">
+      <c r="AA44" t="str">
         <v/>
       </c>
     </row>
@@ -3983,11 +4116,11 @@
         <v/>
       </c>
       <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
         <v>Booking</v>
       </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
       <c r="N45" t="str">
         <v/>
       </c>
@@ -4016,15 +4149,18 @@
         <v/>
       </c>
       <c r="W45" t="str">
+        <v/>
+      </c>
+      <c r="X45" t="str">
         <v>calendar: The Westin Palace, Milan check out</v>
       </c>
-      <c r="X45" t="str">
-        <v/>
-      </c>
       <c r="Y45" t="str">
+        <v/>
+      </c>
+      <c r="Z45" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z45" t="str">
+      <c r="AA45" t="str">
         <v/>
       </c>
     </row>
@@ -4063,11 +4199,11 @@
         <v/>
       </c>
       <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
         <v>Booking</v>
       </c>
-      <c r="M46" t="str">
-        <v/>
-      </c>
       <c r="N46" t="str">
         <v/>
       </c>
@@ -4096,15 +4232,18 @@
         <v/>
       </c>
       <c r="W46" t="str">
+        <v/>
+      </c>
+      <c r="X46" t="str">
         <v>calendar: The Westin Palace, Milan check out</v>
       </c>
-      <c r="X46" t="str">
-        <v/>
-      </c>
       <c r="Y46" t="str">
+        <v/>
+      </c>
+      <c r="Z46" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z46" t="str">
+      <c r="AA46" t="str">
         <v/>
       </c>
     </row>
@@ -4143,11 +4282,11 @@
         <v/>
       </c>
       <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
         <v>Booking</v>
       </c>
-      <c r="M47" t="str">
-        <v/>
-      </c>
       <c r="N47" t="str">
         <v/>
       </c>
@@ -4176,15 +4315,18 @@
         <v/>
       </c>
       <c r="W47" t="str">
+        <v/>
+      </c>
+      <c r="X47" t="str">
         <v>calendar: British Airways flight 584 to Milan (Y6AZA3)</v>
       </c>
-      <c r="X47" t="str">
-        <v/>
-      </c>
       <c r="Y47" t="str">
+        <v/>
+      </c>
+      <c r="Z47" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z47" t="str">
+      <c r="AA47" t="str">
         <v/>
       </c>
     </row>
@@ -4223,11 +4365,11 @@
         <v/>
       </c>
       <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
         <v>Booking</v>
       </c>
-      <c r="M48" t="str">
-        <v/>
-      </c>
       <c r="N48" t="str">
         <v/>
       </c>
@@ -4256,15 +4398,18 @@
         <v/>
       </c>
       <c r="W48" t="str">
+        <v/>
+      </c>
+      <c r="X48" t="str">
         <v>calendar: British Airways flight 573 to London (Y6AZA3)</v>
       </c>
-      <c r="X48" t="str">
-        <v/>
-      </c>
       <c r="Y48" t="str">
+        <v/>
+      </c>
+      <c r="Z48" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z48" t="str">
+      <c r="AA48" t="str">
         <v/>
       </c>
     </row>
@@ -4303,11 +4448,11 @@
         <v/>
       </c>
       <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
         <v>Booking</v>
       </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
       <c r="N49" t="str">
         <v/>
       </c>
@@ -4336,15 +4481,18 @@
         <v/>
       </c>
       <c r="W49" t="str">
+        <v/>
+      </c>
+      <c r="X49" t="str">
         <v>calendar: Instyle: Home - Gatwick</v>
       </c>
-      <c r="X49" t="str">
-        <v/>
-      </c>
       <c r="Y49" t="str">
+        <v/>
+      </c>
+      <c r="Z49" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z49" t="str">
+      <c r="AA49" t="str">
         <v/>
       </c>
     </row>
@@ -4383,11 +4531,11 @@
         <v/>
       </c>
       <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
         <v>Booking</v>
       </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
       <c r="N50" t="str">
         <v/>
       </c>
@@ -4416,15 +4564,18 @@
         <v/>
       </c>
       <c r="W50" t="str">
+        <v/>
+      </c>
+      <c r="X50" t="str">
         <v>email: Fw: Booking confirmation | Wednesday, 15 October 2025 - Reference: PGGTXF</v>
       </c>
-      <c r="X50" t="str">
-        <v/>
-      </c>
       <c r="Y50" t="str">
+        <v/>
+      </c>
+      <c r="Z50" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z50" t="str">
+      <c r="AA50" t="str">
         <v/>
       </c>
     </row>
@@ -4463,11 +4614,11 @@
         <v/>
       </c>
       <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
         <v>Booking</v>
       </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
       <c r="N51" t="str">
         <v/>
       </c>
@@ -4496,15 +4647,18 @@
         <v/>
       </c>
       <c r="W51" t="str">
+        <v/>
+      </c>
+      <c r="X51" t="str">
         <v>calendar: The St. Regis Rome check in</v>
       </c>
-      <c r="X51" t="str">
-        <v/>
-      </c>
       <c r="Y51" t="str">
+        <v/>
+      </c>
+      <c r="Z51" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z51" t="str">
+      <c r="AA51" t="str">
         <v/>
       </c>
     </row>
@@ -4543,11 +4697,11 @@
         <v/>
       </c>
       <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
         <v>Booking</v>
       </c>
-      <c r="M52" t="str">
-        <v/>
-      </c>
       <c r="N52" t="str">
         <v/>
       </c>
@@ -4576,15 +4730,18 @@
         <v/>
       </c>
       <c r="W52" t="str">
+        <v/>
+      </c>
+      <c r="X52" t="str">
         <v>calendar: The St. Regis Rome check out</v>
       </c>
-      <c r="X52" t="str">
-        <v/>
-      </c>
       <c r="Y52" t="str">
+        <v/>
+      </c>
+      <c r="Z52" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z52" t="str">
+      <c r="AA52" t="str">
         <v/>
       </c>
     </row>
@@ -4623,11 +4780,11 @@
         <v/>
       </c>
       <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
         <v>Booking</v>
       </c>
-      <c r="M53" t="str">
-        <v/>
-      </c>
       <c r="N53" t="str">
         <v/>
       </c>
@@ -4656,15 +4813,18 @@
         <v/>
       </c>
       <c r="W53" t="str">
+        <v/>
+      </c>
+      <c r="X53" t="str">
         <v>calendar: Hotel Grande Bretagne, a Luxury Collection Hotel, Athens check in</v>
       </c>
-      <c r="X53" t="str">
-        <v/>
-      </c>
       <c r="Y53" t="str">
+        <v/>
+      </c>
+      <c r="Z53" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z53" t="str">
+      <c r="AA53" t="str">
         <v/>
       </c>
     </row>
@@ -4703,11 +4863,11 @@
         <v/>
       </c>
       <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
         <v>Booking</v>
       </c>
-      <c r="M54" t="str">
-        <v/>
-      </c>
       <c r="N54" t="str">
         <v/>
       </c>
@@ -4736,15 +4896,18 @@
         <v/>
       </c>
       <c r="W54" t="str">
+        <v/>
+      </c>
+      <c r="X54" t="str">
         <v>calendar: Hotel Grande Bretagne, a Luxury Collection Hotel, Athens check out</v>
       </c>
-      <c r="X54" t="str">
-        <v/>
-      </c>
       <c r="Y54" t="str">
+        <v/>
+      </c>
+      <c r="Z54" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z54" t="str">
+      <c r="AA54" t="str">
         <v/>
       </c>
     </row>
@@ -4783,11 +4946,11 @@
         <v/>
       </c>
       <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
         <v>Booking</v>
       </c>
-      <c r="M55" t="str">
-        <v/>
-      </c>
       <c r="N55" t="str">
         <v/>
       </c>
@@ -4816,15 +4979,18 @@
         <v/>
       </c>
       <c r="W55" t="str">
+        <v/>
+      </c>
+      <c r="X55" t="str">
         <v>email: Fw: Your booking confirmation ZQ7388</v>
       </c>
-      <c r="X55" t="str">
-        <v/>
-      </c>
       <c r="Y55" t="str">
+        <v/>
+      </c>
+      <c r="Z55" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z55" t="str">
+      <c r="AA55" t="str">
         <v/>
       </c>
     </row>
@@ -4863,11 +5029,11 @@
         <v/>
       </c>
       <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
         <v>Booking</v>
       </c>
-      <c r="M56" t="str">
-        <v/>
-      </c>
       <c r="N56" t="str">
         <v/>
       </c>
@@ -4896,15 +5062,18 @@
         <v/>
       </c>
       <c r="W56" t="str">
+        <v/>
+      </c>
+      <c r="X56" t="str">
         <v>calendar: Flight AF7551: LHR - Nice, departs 08:55am</v>
       </c>
-      <c r="X56" t="str">
-        <v/>
-      </c>
       <c r="Y56" t="str">
+        <v/>
+      </c>
+      <c r="Z56" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z56" t="str">
+      <c r="AA56" t="str">
         <v/>
       </c>
     </row>
@@ -4943,11 +5112,11 @@
         <v/>
       </c>
       <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
         <v>Booking</v>
       </c>
-      <c r="M57" t="str">
-        <v/>
-      </c>
       <c r="N57" t="str">
         <v/>
       </c>
@@ -4976,15 +5145,18 @@
         <v/>
       </c>
       <c r="W57" t="str">
+        <v/>
+      </c>
+      <c r="X57" t="str">
         <v>calendar: Flight BA343: Nice - London, departs 11:25am</v>
       </c>
-      <c r="X57" t="str">
-        <v/>
-      </c>
       <c r="Y57" t="str">
+        <v/>
+      </c>
+      <c r="Z57" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z57" t="str">
+      <c r="AA57" t="str">
         <v/>
       </c>
     </row>
@@ -5023,11 +5195,11 @@
         <v/>
       </c>
       <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
         <v>Booking</v>
       </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
       <c r="N58" t="str">
         <v/>
       </c>
@@ -5056,15 +5228,18 @@
         <v/>
       </c>
       <c r="W58" t="str">
+        <v/>
+      </c>
+      <c r="X58" t="str">
         <v>calendar: Preparation call: Mainstage - Lenovo 360 Accelerate EMEA 2025</v>
       </c>
-      <c r="X58" t="str">
-        <v/>
-      </c>
       <c r="Y58" t="str">
+        <v/>
+      </c>
+      <c r="Z58" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z58" t="str">
+      <c r="AA58" t="str">
         <v/>
       </c>
     </row>
@@ -5103,11 +5278,11 @@
         <v/>
       </c>
       <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
         <v>Booking</v>
       </c>
-      <c r="M59" t="str">
-        <v/>
-      </c>
       <c r="N59" t="str">
         <v/>
       </c>
@@ -5136,15 +5311,18 @@
         <v/>
       </c>
       <c r="W59" t="str">
+        <v/>
+      </c>
+      <c r="X59" t="str">
         <v>calendar: Flight BA354: LHR - NCE, departs 15:35</v>
       </c>
-      <c r="X59" t="str">
-        <v/>
-      </c>
       <c r="Y59" t="str">
+        <v/>
+      </c>
+      <c r="Z59" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z59" t="str">
+      <c r="AA59" t="str">
         <v/>
       </c>
     </row>
@@ -5183,11 +5361,11 @@
         <v/>
       </c>
       <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
         <v>Booking</v>
       </c>
-      <c r="M60" t="str">
-        <v/>
-      </c>
       <c r="N60" t="str">
         <v/>
       </c>
@@ -5216,15 +5394,18 @@
         <v/>
       </c>
       <c r="W60" t="str">
+        <v/>
+      </c>
+      <c r="X60" t="str">
         <v>calendar: La Bastide de Mougins, a Tribute Portfolio Hotel check in</v>
       </c>
-      <c r="X60" t="str">
-        <v/>
-      </c>
       <c r="Y60" t="str">
+        <v/>
+      </c>
+      <c r="Z60" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z60" t="str">
+      <c r="AA60" t="str">
         <v/>
       </c>
     </row>
@@ -5263,11 +5444,11 @@
         <v/>
       </c>
       <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
         <v>Booking</v>
       </c>
-      <c r="M61" t="str">
-        <v/>
-      </c>
       <c r="N61" t="str">
         <v/>
       </c>
@@ -5296,15 +5477,18 @@
         <v/>
       </c>
       <c r="W61" t="str">
+        <v/>
+      </c>
+      <c r="X61" t="str">
         <v>calendar: La Bastide de Mougins, a Tribute Portfolio Hotel check out</v>
       </c>
-      <c r="X61" t="str">
-        <v/>
-      </c>
       <c r="Y61" t="str">
+        <v/>
+      </c>
+      <c r="Z61" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z61" t="str">
+      <c r="AA61" t="str">
         <v/>
       </c>
     </row>
@@ -5343,11 +5527,11 @@
         <v/>
       </c>
       <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
         <v>Booking</v>
       </c>
-      <c r="M62" t="str">
-        <v/>
-      </c>
       <c r="N62" t="str">
         <v/>
       </c>
@@ -5376,15 +5560,18 @@
         <v/>
       </c>
       <c r="W62" t="str">
+        <v/>
+      </c>
+      <c r="X62" t="str">
         <v>calendar: Flight BA357: NCE - LHR, departs 21:40</v>
       </c>
-      <c r="X62" t="str">
-        <v/>
-      </c>
       <c r="Y62" t="str">
+        <v/>
+      </c>
+      <c r="Z62" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z62" t="str">
+      <c r="AA62" t="str">
         <v/>
       </c>
     </row>
@@ -5423,11 +5610,11 @@
         <v/>
       </c>
       <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
         <v>Booking</v>
       </c>
-      <c r="M63" t="str">
-        <v/>
-      </c>
       <c r="N63" t="str">
         <v/>
       </c>
@@ -5456,15 +5643,18 @@
         <v/>
       </c>
       <c r="W63" t="str">
+        <v/>
+      </c>
+      <c r="X63" t="str">
         <v>email: Fw: Confirmation of your booking</v>
       </c>
-      <c r="X63" t="str">
-        <v/>
-      </c>
       <c r="Y63" t="str">
+        <v/>
+      </c>
+      <c r="Z63" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z63" t="str">
+      <c r="AA63" t="str">
         <v/>
       </c>
     </row>
@@ -5503,11 +5693,11 @@
         <v/>
       </c>
       <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
         <v>Booking</v>
       </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
       <c r="N64" t="str">
         <v/>
       </c>
@@ -5536,15 +5726,18 @@
         <v/>
       </c>
       <c r="W64" t="str">
+        <v/>
+      </c>
+      <c r="X64" t="str">
         <v>calendar: Flight BA564: LHR - LIN, departs 07:10am</v>
       </c>
-      <c r="X64" t="str">
-        <v/>
-      </c>
       <c r="Y64" t="str">
+        <v/>
+      </c>
+      <c r="Z64" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z64" t="str">
+      <c r="AA64" t="str">
         <v/>
       </c>
     </row>
@@ -5583,11 +5776,11 @@
         <v/>
       </c>
       <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
         <v>Booking</v>
       </c>
-      <c r="M65" t="str">
-        <v/>
-      </c>
       <c r="N65" t="str">
         <v/>
       </c>
@@ -5616,15 +5809,18 @@
         <v/>
       </c>
       <c r="W65" t="str">
+        <v/>
+      </c>
+      <c r="X65" t="str">
         <v>calendar: Hotel Phoenix</v>
       </c>
-      <c r="X65" t="str">
-        <v/>
-      </c>
       <c r="Y65" t="str">
+        <v/>
+      </c>
+      <c r="Z65" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z65" t="str">
+      <c r="AA65" t="str">
         <v/>
       </c>
     </row>
@@ -5663,11 +5859,11 @@
         <v/>
       </c>
       <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
         <v>Booking</v>
       </c>
-      <c r="M66" t="str">
-        <v/>
-      </c>
       <c r="N66" t="str">
         <v/>
       </c>
@@ -5696,15 +5892,18 @@
         <v/>
       </c>
       <c r="W66" t="str">
+        <v/>
+      </c>
+      <c r="X66" t="str">
         <v>calendar: Flight BA0813: Copenhagen - LHR, departs 10:50</v>
       </c>
-      <c r="X66" t="str">
-        <v/>
-      </c>
       <c r="Y66" t="str">
+        <v/>
+      </c>
+      <c r="Z66" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z66" t="str">
+      <c r="AA66" t="str">
         <v/>
       </c>
     </row>
@@ -5743,11 +5942,11 @@
         <v/>
       </c>
       <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
         <v>Booking</v>
       </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
       <c r="N67" t="str">
         <v/>
       </c>
@@ -5776,15 +5975,18 @@
         <v/>
       </c>
       <c r="W67" t="str">
+        <v/>
+      </c>
+      <c r="X67" t="str">
         <v>email: Fw: Your booking confirmation CM93FN -  MXP-BCN 06 October</v>
       </c>
-      <c r="X67" t="str">
-        <v/>
-      </c>
       <c r="Y67" t="str">
+        <v/>
+      </c>
+      <c r="Z67" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z67" t="str">
+      <c r="AA67" t="str">
         <v/>
       </c>
     </row>
@@ -5823,11 +6025,11 @@
         <v/>
       </c>
       <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
         <v>Booking</v>
       </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
       <c r="N68" t="str">
         <v/>
       </c>
@@ -5856,15 +6058,18 @@
         <v/>
       </c>
       <c r="W68" t="str">
+        <v/>
+      </c>
+      <c r="X68" t="str">
         <v>calendar: Flight BA564: LHR - LIN, departs 07:10am</v>
       </c>
-      <c r="X68" t="str">
-        <v/>
-      </c>
       <c r="Y68" t="str">
+        <v/>
+      </c>
+      <c r="Z68" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z68" t="str">
+      <c r="AA68" t="str">
         <v/>
       </c>
     </row>
@@ -5903,11 +6108,11 @@
         <v/>
       </c>
       <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
         <v>Booking</v>
       </c>
-      <c r="M69" t="str">
-        <v/>
-      </c>
       <c r="N69" t="str">
         <v/>
       </c>
@@ -5936,15 +6141,18 @@
         <v/>
       </c>
       <c r="W69" t="str">
+        <v/>
+      </c>
+      <c r="X69" t="str">
         <v>calendar: Flight BA565: LIN - LHR, departs 11:10am</v>
       </c>
-      <c r="X69" t="str">
-        <v/>
-      </c>
       <c r="Y69" t="str">
+        <v/>
+      </c>
+      <c r="Z69" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z69" t="str">
+      <c r="AA69" t="str">
         <v/>
       </c>
     </row>
@@ -5983,11 +6191,11 @@
         <v/>
       </c>
       <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
         <v>Booking</v>
       </c>
-      <c r="M70" t="str">
-        <v/>
-      </c>
       <c r="N70" t="str">
         <v/>
       </c>
@@ -6016,15 +6224,18 @@
         <v/>
       </c>
       <c r="W70" t="str">
+        <v/>
+      </c>
+      <c r="X70" t="str">
         <v>calendar: Flight BA580: LHR - MXP, departs 15:20</v>
       </c>
-      <c r="X70" t="str">
-        <v/>
-      </c>
       <c r="Y70" t="str">
+        <v/>
+      </c>
+      <c r="Z70" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z70" t="str">
+      <c r="AA70" t="str">
         <v/>
       </c>
     </row>
@@ -6063,11 +6274,11 @@
         <v/>
       </c>
       <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
         <v>Booking</v>
       </c>
-      <c r="M71" t="str">
-        <v/>
-      </c>
       <c r="N71" t="str">
         <v/>
       </c>
@@ -6096,15 +6307,18 @@
         <v/>
       </c>
       <c r="W71" t="str">
+        <v/>
+      </c>
+      <c r="X71" t="str">
         <v>calendar: Hotel: W Hotel</v>
       </c>
-      <c r="X71" t="str">
-        <v/>
-      </c>
       <c r="Y71" t="str">
+        <v/>
+      </c>
+      <c r="Z71" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z71" t="str">
+      <c r="AA71" t="str">
         <v/>
       </c>
     </row>
@@ -6143,11 +6357,11 @@
         <v/>
       </c>
       <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
         <v>Booking</v>
       </c>
-      <c r="M72" t="str">
-        <v/>
-      </c>
       <c r="N72" t="str">
         <v/>
       </c>
@@ -6176,15 +6390,18 @@
         <v/>
       </c>
       <c r="W72" t="str">
+        <v/>
+      </c>
+      <c r="X72" t="str">
         <v>calendar: Flight BA483: BCN-LHR, departs 14:00</v>
       </c>
-      <c r="X72" t="str">
-        <v/>
-      </c>
       <c r="Y72" t="str">
+        <v/>
+      </c>
+      <c r="Z72" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z72" t="str">
+      <c r="AA72" t="str">
         <v/>
       </c>
     </row>
@@ -6223,11 +6440,11 @@
         <v/>
       </c>
       <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
         <v>Booking</v>
       </c>
-      <c r="M73" t="str">
-        <v/>
-      </c>
       <c r="N73" t="str">
         <v/>
       </c>
@@ -6256,15 +6473,18 @@
         <v/>
       </c>
       <c r="W73" t="str">
+        <v/>
+      </c>
+      <c r="X73" t="str">
         <v>email: Fw: Your booking confirmation YRRK9O</v>
       </c>
-      <c r="X73" t="str">
-        <v/>
-      </c>
       <c r="Y73" t="str">
+        <v/>
+      </c>
+      <c r="Z73" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z73" t="str">
+      <c r="AA73" t="str">
         <v/>
       </c>
     </row>
@@ -6303,11 +6523,11 @@
         <v/>
       </c>
       <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
         <v>Booking</v>
       </c>
-      <c r="M74" t="str">
-        <v/>
-      </c>
       <c r="N74" t="str">
         <v/>
       </c>
@@ -6336,15 +6556,18 @@
         <v/>
       </c>
       <c r="W74" t="str">
+        <v/>
+      </c>
+      <c r="X74" t="str">
         <v>calendar: Finance department review</v>
       </c>
-      <c r="X74" t="str">
-        <v/>
-      </c>
       <c r="Y74" t="str">
+        <v/>
+      </c>
+      <c r="Z74" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z74" t="str">
+      <c r="AA74" t="str">
         <v/>
       </c>
     </row>
@@ -6383,11 +6606,11 @@
         <v/>
       </c>
       <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
         <v>Booking</v>
       </c>
-      <c r="M75" t="str">
-        <v/>
-      </c>
       <c r="N75" t="str">
         <v/>
       </c>
@@ -6416,15 +6639,18 @@
         <v/>
       </c>
       <c r="W75" t="str">
+        <v/>
+      </c>
+      <c r="X75" t="str">
         <v>calendar: Eurostar: Brussels - London, departs 15:51</v>
       </c>
-      <c r="X75" t="str">
-        <v/>
-      </c>
       <c r="Y75" t="str">
+        <v/>
+      </c>
+      <c r="Z75" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z75" t="str">
+      <c r="AA75" t="str">
         <v/>
       </c>
     </row>
@@ -6463,11 +6689,11 @@
         <v/>
       </c>
       <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
         <v>Booking</v>
       </c>
-      <c r="M76" t="str">
-        <v/>
-      </c>
       <c r="N76" t="str">
         <v/>
       </c>
@@ -6496,15 +6722,18 @@
         <v/>
       </c>
       <c r="W76" t="str">
+        <v/>
+      </c>
+      <c r="X76" t="str">
         <v>calendar: Flight BA584: LHR - MXP, departs 20:00</v>
       </c>
-      <c r="X76" t="str">
-        <v/>
-      </c>
       <c r="Y76" t="str">
+        <v/>
+      </c>
+      <c r="Z76" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z76" t="str">
+      <c r="AA76" t="str">
         <v/>
       </c>
     </row>
@@ -6543,11 +6772,11 @@
         <v/>
       </c>
       <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
         <v>Booking</v>
       </c>
-      <c r="M77" t="str">
-        <v/>
-      </c>
       <c r="N77" t="str">
         <v/>
       </c>
@@ -6576,15 +6805,18 @@
         <v/>
       </c>
       <c r="W77" t="str">
+        <v/>
+      </c>
+      <c r="X77" t="str">
         <v>calendar: Flight BA583: MXP - LHR, departs 20:25</v>
       </c>
-      <c r="X77" t="str">
-        <v/>
-      </c>
       <c r="Y77" t="str">
+        <v/>
+      </c>
+      <c r="Z77" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z77" t="str">
+      <c r="AA77" t="str">
         <v/>
       </c>
     </row>
@@ -6623,11 +6855,11 @@
         <v/>
       </c>
       <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
         <v>Booking</v>
       </c>
-      <c r="M78" t="str">
-        <v/>
-      </c>
       <c r="N78" t="str">
         <v/>
       </c>
@@ -6656,15 +6888,18 @@
         <v/>
       </c>
       <c r="W78" t="str">
+        <v/>
+      </c>
+      <c r="X78" t="str">
         <v>calendar: Flight BA1542: LHR - MXP</v>
       </c>
-      <c r="X78" t="str">
-        <v/>
-      </c>
       <c r="Y78" t="str">
+        <v/>
+      </c>
+      <c r="Z78" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z78" t="str">
+      <c r="AA78" t="str">
         <v/>
       </c>
     </row>
@@ -6703,11 +6938,11 @@
         <v/>
       </c>
       <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
         <v>Booking</v>
       </c>
-      <c r="M79" t="str">
-        <v/>
-      </c>
       <c r="N79" t="str">
         <v/>
       </c>
@@ -6736,15 +6971,18 @@
         <v/>
       </c>
       <c r="W79" t="str">
+        <v/>
+      </c>
+      <c r="X79" t="str">
         <v>calendar: Flight BA294: Chicago - LHR, departs 16:55</v>
       </c>
-      <c r="X79" t="str">
-        <v/>
-      </c>
       <c r="Y79" t="str">
+        <v/>
+      </c>
+      <c r="Z79" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z79" t="str">
+      <c r="AA79" t="str">
         <v/>
       </c>
     </row>
@@ -6783,11 +7021,11 @@
         <v/>
       </c>
       <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
         <v>Booking</v>
       </c>
-      <c r="M80" t="str">
-        <v/>
-      </c>
       <c r="N80" t="str">
         <v/>
       </c>
@@ -6816,15 +7054,18 @@
         <v/>
       </c>
       <c r="W80" t="str">
+        <v/>
+      </c>
+      <c r="X80" t="str">
         <v>calendar: Catalyst Europe 25</v>
       </c>
-      <c r="X80" t="str">
-        <v/>
-      </c>
       <c r="Y80" t="str">
+        <v/>
+      </c>
+      <c r="Z80" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z80" t="str">
+      <c r="AA80" t="str">
         <v/>
       </c>
     </row>
@@ -6863,11 +7104,11 @@
         <v/>
       </c>
       <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
         <v>Manual</v>
       </c>
-      <c r="M81" t="str">
-        <v/>
-      </c>
       <c r="N81" t="str">
         <v/>
       </c>
@@ -6905,6 +7146,9 @@
         <v/>
       </c>
       <c r="Z81" t="str">
+        <v/>
+      </c>
+      <c r="AA81" t="str">
         <v/>
       </c>
     </row>
@@ -6943,11 +7187,11 @@
         <v/>
       </c>
       <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
         <v>Manual</v>
       </c>
-      <c r="M82" t="str">
-        <v/>
-      </c>
       <c r="N82" t="str">
         <v/>
       </c>
@@ -6985,6 +7229,9 @@
         <v/>
       </c>
       <c r="Z82" t="str">
+        <v/>
+      </c>
+      <c r="AA82" t="str">
         <v/>
       </c>
     </row>
@@ -7023,11 +7270,11 @@
         <v/>
       </c>
       <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
         <v>Manual</v>
       </c>
-      <c r="M83" t="str">
-        <v/>
-      </c>
       <c r="N83" t="str">
         <v/>
       </c>
@@ -7065,6 +7312,9 @@
         <v/>
       </c>
       <c r="Z83" t="str">
+        <v/>
+      </c>
+      <c r="AA83" t="str">
         <v/>
       </c>
     </row>
@@ -7103,11 +7353,11 @@
         <v/>
       </c>
       <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
         <v>Manual</v>
       </c>
-      <c r="M84" t="str">
-        <v/>
-      </c>
       <c r="N84" t="str">
         <v/>
       </c>
@@ -7145,6 +7395,9 @@
         <v/>
       </c>
       <c r="Z84" t="str">
+        <v/>
+      </c>
+      <c r="AA84" t="str">
         <v/>
       </c>
     </row>
@@ -7183,11 +7436,11 @@
         <v/>
       </c>
       <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
         <v>Manual</v>
       </c>
-      <c r="M85" t="str">
-        <v/>
-      </c>
       <c r="N85" t="str">
         <v/>
       </c>
@@ -7225,6 +7478,9 @@
         <v/>
       </c>
       <c r="Z85" t="str">
+        <v/>
+      </c>
+      <c r="AA85" t="str">
         <v/>
       </c>
     </row>
@@ -7263,11 +7519,11 @@
         <v/>
       </c>
       <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
         <v>Manual</v>
       </c>
-      <c r="M86" t="str">
-        <v/>
-      </c>
       <c r="N86" t="str">
         <v/>
       </c>
@@ -7305,6 +7561,9 @@
         <v/>
       </c>
       <c r="Z86" t="str">
+        <v/>
+      </c>
+      <c r="AA86" t="str">
         <v/>
       </c>
     </row>
@@ -7343,11 +7602,11 @@
         <v/>
       </c>
       <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
         <v>Manual</v>
       </c>
-      <c r="M87" t="str">
-        <v/>
-      </c>
       <c r="N87" t="str">
         <v/>
       </c>
@@ -7385,6 +7644,9 @@
         <v/>
       </c>
       <c r="Z87" t="str">
+        <v/>
+      </c>
+      <c r="AA87" t="str">
         <v/>
       </c>
     </row>
@@ -7423,11 +7685,11 @@
         <v/>
       </c>
       <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
         <v>Manual</v>
       </c>
-      <c r="M88" t="str">
-        <v/>
-      </c>
       <c r="N88" t="str">
         <v/>
       </c>
@@ -7465,6 +7727,9 @@
         <v/>
       </c>
       <c r="Z88" t="str">
+        <v/>
+      </c>
+      <c r="AA88" t="str">
         <v/>
       </c>
     </row>
@@ -7503,11 +7768,11 @@
         <v/>
       </c>
       <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
         <v>Manual</v>
       </c>
-      <c r="M89" t="str">
-        <v/>
-      </c>
       <c r="N89" t="str">
         <v/>
       </c>
@@ -7545,6 +7810,9 @@
         <v/>
       </c>
       <c r="Z89" t="str">
+        <v/>
+      </c>
+      <c r="AA89" t="str">
         <v/>
       </c>
     </row>
@@ -7583,11 +7851,11 @@
         <v/>
       </c>
       <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
         <v>Manual</v>
       </c>
-      <c r="M90" t="str">
-        <v/>
-      </c>
       <c r="N90" t="str">
         <v/>
       </c>
@@ -7625,6 +7893,9 @@
         <v/>
       </c>
       <c r="Z90" t="str">
+        <v/>
+      </c>
+      <c r="AA90" t="str">
         <v/>
       </c>
     </row>
@@ -7663,11 +7934,11 @@
         <v/>
       </c>
       <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
         <v>Manual</v>
       </c>
-      <c r="M91" t="str">
-        <v/>
-      </c>
       <c r="N91" t="str">
         <v/>
       </c>
@@ -7705,6 +7976,9 @@
         <v/>
       </c>
       <c r="Z91" t="str">
+        <v/>
+      </c>
+      <c r="AA91" t="str">
         <v/>
       </c>
     </row>
@@ -7743,11 +8017,11 @@
         <v/>
       </c>
       <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
         <v>Manual</v>
       </c>
-      <c r="M92" t="str">
-        <v/>
-      </c>
       <c r="N92" t="str">
         <v/>
       </c>
@@ -7785,6 +8059,9 @@
         <v/>
       </c>
       <c r="Z92" t="str">
+        <v/>
+      </c>
+      <c r="AA92" t="str">
         <v/>
       </c>
     </row>
@@ -7823,11 +8100,11 @@
         <v/>
       </c>
       <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
         <v>Manual</v>
       </c>
-      <c r="M93" t="str">
-        <v/>
-      </c>
       <c r="N93" t="str">
         <v/>
       </c>
@@ -7865,6 +8142,9 @@
         <v/>
       </c>
       <c r="Z93" t="str">
+        <v/>
+      </c>
+      <c r="AA93" t="str">
         <v/>
       </c>
     </row>
@@ -7903,11 +8183,11 @@
         <v/>
       </c>
       <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
         <v>Manual</v>
       </c>
-      <c r="M94" t="str">
-        <v/>
-      </c>
       <c r="N94" t="str">
         <v/>
       </c>
@@ -7945,6 +8225,9 @@
         <v/>
       </c>
       <c r="Z94" t="str">
+        <v/>
+      </c>
+      <c r="AA94" t="str">
         <v/>
       </c>
     </row>
@@ -7983,11 +8266,11 @@
         <v/>
       </c>
       <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
         <v>Manual</v>
       </c>
-      <c r="M95" t="str">
-        <v/>
-      </c>
       <c r="N95" t="str">
         <v/>
       </c>
@@ -8025,6 +8308,9 @@
         <v/>
       </c>
       <c r="Z95" t="str">
+        <v/>
+      </c>
+      <c r="AA95" t="str">
         <v/>
       </c>
     </row>
@@ -8063,11 +8349,11 @@
         <v/>
       </c>
       <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
         <v>Manual</v>
       </c>
-      <c r="M96" t="str">
-        <v/>
-      </c>
       <c r="N96" t="str">
         <v/>
       </c>
@@ -8105,6 +8391,9 @@
         <v/>
       </c>
       <c r="Z96" t="str">
+        <v/>
+      </c>
+      <c r="AA96" t="str">
         <v/>
       </c>
     </row>
@@ -8143,11 +8432,11 @@
         <v/>
       </c>
       <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
         <v>Manual</v>
       </c>
-      <c r="M97" t="str">
-        <v/>
-      </c>
       <c r="N97" t="str">
         <v/>
       </c>
@@ -8185,6 +8474,9 @@
         <v/>
       </c>
       <c r="Z97" t="str">
+        <v/>
+      </c>
+      <c r="AA97" t="str">
         <v/>
       </c>
     </row>
@@ -8223,11 +8515,11 @@
         <v/>
       </c>
       <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
         <v>Manual</v>
       </c>
-      <c r="M98" t="str">
-        <v/>
-      </c>
       <c r="N98" t="str">
         <v/>
       </c>
@@ -8265,6 +8557,9 @@
         <v/>
       </c>
       <c r="Z98" t="str">
+        <v/>
+      </c>
+      <c r="AA98" t="str">
         <v/>
       </c>
     </row>
@@ -8303,11 +8598,11 @@
         <v/>
       </c>
       <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
         <v>Manual</v>
       </c>
-      <c r="M99" t="str">
-        <v/>
-      </c>
       <c r="N99" t="str">
         <v/>
       </c>
@@ -8345,6 +8640,9 @@
         <v/>
       </c>
       <c r="Z99" t="str">
+        <v/>
+      </c>
+      <c r="AA99" t="str">
         <v/>
       </c>
     </row>
@@ -8383,11 +8681,11 @@
         <v/>
       </c>
       <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
         <v>Manual</v>
       </c>
-      <c r="M100" t="str">
-        <v/>
-      </c>
       <c r="N100" t="str">
         <v/>
       </c>
@@ -8425,6 +8723,9 @@
         <v/>
       </c>
       <c r="Z100" t="str">
+        <v/>
+      </c>
+      <c r="AA100" t="str">
         <v/>
       </c>
     </row>
@@ -8463,11 +8764,11 @@
         <v/>
       </c>
       <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
         <v>Manual</v>
       </c>
-      <c r="M101" t="str">
-        <v/>
-      </c>
       <c r="N101" t="str">
         <v/>
       </c>
@@ -8505,6 +8806,9 @@
         <v/>
       </c>
       <c r="Z101" t="str">
+        <v/>
+      </c>
+      <c r="AA101" t="str">
         <v/>
       </c>
     </row>
@@ -8543,11 +8847,11 @@
         <v/>
       </c>
       <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
         <v>Manual</v>
       </c>
-      <c r="M102" t="str">
-        <v/>
-      </c>
       <c r="N102" t="str">
         <v/>
       </c>
@@ -8585,6 +8889,9 @@
         <v/>
       </c>
       <c r="Z102" t="str">
+        <v/>
+      </c>
+      <c r="AA102" t="str">
         <v/>
       </c>
     </row>
@@ -8623,11 +8930,11 @@
         <v/>
       </c>
       <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
         <v>Manual</v>
       </c>
-      <c r="M103" t="str">
-        <v/>
-      </c>
       <c r="N103" t="str">
         <v/>
       </c>
@@ -8665,6 +8972,9 @@
         <v/>
       </c>
       <c r="Z103" t="str">
+        <v/>
+      </c>
+      <c r="AA103" t="str">
         <v/>
       </c>
     </row>
@@ -8703,11 +9013,11 @@
         <v/>
       </c>
       <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
         <v>Manual</v>
       </c>
-      <c r="M104" t="str">
-        <v/>
-      </c>
       <c r="N104" t="str">
         <v/>
       </c>
@@ -8745,6 +9055,9 @@
         <v/>
       </c>
       <c r="Z104" t="str">
+        <v/>
+      </c>
+      <c r="AA104" t="str">
         <v/>
       </c>
     </row>
@@ -8783,11 +9096,11 @@
         <v/>
       </c>
       <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
         <v>Manual</v>
       </c>
-      <c r="M105" t="str">
-        <v/>
-      </c>
       <c r="N105" t="str">
         <v/>
       </c>
@@ -8825,6 +9138,9 @@
         <v/>
       </c>
       <c r="Z105" t="str">
+        <v/>
+      </c>
+      <c r="AA105" t="str">
         <v/>
       </c>
     </row>
@@ -8863,11 +9179,11 @@
         <v/>
       </c>
       <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
         <v>Manual</v>
       </c>
-      <c r="M106" t="str">
-        <v/>
-      </c>
       <c r="N106" t="str">
         <v/>
       </c>
@@ -8905,6 +9221,9 @@
         <v/>
       </c>
       <c r="Z106" t="str">
+        <v/>
+      </c>
+      <c r="AA106" t="str">
         <v/>
       </c>
     </row>
@@ -8943,11 +9262,11 @@
         <v/>
       </c>
       <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
         <v>Manual</v>
       </c>
-      <c r="M107" t="str">
-        <v/>
-      </c>
       <c r="N107" t="str">
         <v/>
       </c>
@@ -8985,6 +9304,9 @@
         <v/>
       </c>
       <c r="Z107" t="str">
+        <v/>
+      </c>
+      <c r="AA107" t="str">
         <v/>
       </c>
     </row>
@@ -9023,11 +9345,11 @@
         <v/>
       </c>
       <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
         <v>Manual</v>
       </c>
-      <c r="M108" t="str">
-        <v/>
-      </c>
       <c r="N108" t="str">
         <v/>
       </c>
@@ -9065,6 +9387,9 @@
         <v/>
       </c>
       <c r="Z108" t="str">
+        <v/>
+      </c>
+      <c r="AA108" t="str">
         <v/>
       </c>
     </row>
@@ -9103,11 +9428,11 @@
         <v/>
       </c>
       <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
         <v>Manual</v>
       </c>
-      <c r="M109" t="str">
-        <v/>
-      </c>
       <c r="N109" t="str">
         <v/>
       </c>
@@ -9145,6 +9470,9 @@
         <v/>
       </c>
       <c r="Z109" t="str">
+        <v/>
+      </c>
+      <c r="AA109" t="str">
         <v/>
       </c>
     </row>
@@ -9183,11 +9511,11 @@
         <v/>
       </c>
       <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
         <v>Manual</v>
       </c>
-      <c r="M110" t="str">
-        <v/>
-      </c>
       <c r="N110" t="str">
         <v/>
       </c>
@@ -9225,6 +9553,9 @@
         <v/>
       </c>
       <c r="Z110" t="str">
+        <v/>
+      </c>
+      <c r="AA110" t="str">
         <v/>
       </c>
     </row>
@@ -9263,11 +9594,11 @@
         <v/>
       </c>
       <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
         <v>Manual</v>
       </c>
-      <c r="M111" t="str">
-        <v/>
-      </c>
       <c r="N111" t="str">
         <v/>
       </c>
@@ -9305,6 +9636,9 @@
         <v/>
       </c>
       <c r="Z111" t="str">
+        <v/>
+      </c>
+      <c r="AA111" t="str">
         <v/>
       </c>
     </row>
@@ -9343,11 +9677,11 @@
         <v/>
       </c>
       <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
         <v>Manual</v>
       </c>
-      <c r="M112" t="str">
-        <v/>
-      </c>
       <c r="N112" t="str">
         <v/>
       </c>
@@ -9385,6 +9719,9 @@
         <v/>
       </c>
       <c r="Z112" t="str">
+        <v/>
+      </c>
+      <c r="AA112" t="str">
         <v/>
       </c>
     </row>
@@ -9423,11 +9760,11 @@
         <v/>
       </c>
       <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
         <v>Manual</v>
       </c>
-      <c r="M113" t="str">
-        <v/>
-      </c>
       <c r="N113" t="str">
         <v/>
       </c>
@@ -9465,6 +9802,9 @@
         <v/>
       </c>
       <c r="Z113" t="str">
+        <v/>
+      </c>
+      <c r="AA113" t="str">
         <v/>
       </c>
     </row>
@@ -9503,11 +9843,11 @@
         <v/>
       </c>
       <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
         <v>Manual</v>
       </c>
-      <c r="M114" t="str">
-        <v/>
-      </c>
       <c r="N114" t="str">
         <v/>
       </c>
@@ -9545,6 +9885,9 @@
         <v/>
       </c>
       <c r="Z114" t="str">
+        <v/>
+      </c>
+      <c r="AA114" t="str">
         <v/>
       </c>
     </row>
@@ -9583,11 +9926,11 @@
         <v/>
       </c>
       <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
         <v>Manual</v>
       </c>
-      <c r="M115" t="str">
-        <v/>
-      </c>
       <c r="N115" t="str">
         <v/>
       </c>
@@ -9625,6 +9968,9 @@
         <v/>
       </c>
       <c r="Z115" t="str">
+        <v/>
+      </c>
+      <c r="AA115" t="str">
         <v/>
       </c>
     </row>
@@ -9663,11 +10009,11 @@
         <v/>
       </c>
       <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
         <v>Manual</v>
       </c>
-      <c r="M116" t="str">
-        <v/>
-      </c>
       <c r="N116" t="str">
         <v/>
       </c>
@@ -9705,6 +10051,9 @@
         <v/>
       </c>
       <c r="Z116" t="str">
+        <v/>
+      </c>
+      <c r="AA116" t="str">
         <v/>
       </c>
     </row>
@@ -9743,11 +10092,11 @@
         <v/>
       </c>
       <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
         <v>Manual</v>
       </c>
-      <c r="M117" t="str">
-        <v/>
-      </c>
       <c r="N117" t="str">
         <v/>
       </c>
@@ -9785,6 +10134,9 @@
         <v/>
       </c>
       <c r="Z117" t="str">
+        <v/>
+      </c>
+      <c r="AA117" t="str">
         <v/>
       </c>
     </row>
@@ -9823,11 +10175,11 @@
         <v/>
       </c>
       <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
         <v>Manual</v>
       </c>
-      <c r="M118" t="str">
-        <v/>
-      </c>
       <c r="N118" t="str">
         <v/>
       </c>
@@ -9865,6 +10217,9 @@
         <v/>
       </c>
       <c r="Z118" t="str">
+        <v/>
+      </c>
+      <c r="AA118" t="str">
         <v/>
       </c>
     </row>
@@ -9903,11 +10258,11 @@
         <v/>
       </c>
       <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
         <v>Manual</v>
       </c>
-      <c r="M119" t="str">
-        <v/>
-      </c>
       <c r="N119" t="str">
         <v/>
       </c>
@@ -9945,6 +10300,9 @@
         <v/>
       </c>
       <c r="Z119" t="str">
+        <v/>
+      </c>
+      <c r="AA119" t="str">
         <v/>
       </c>
     </row>
@@ -9983,11 +10341,11 @@
         <v/>
       </c>
       <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
         <v>Manual</v>
       </c>
-      <c r="M120" t="str">
-        <v/>
-      </c>
       <c r="N120" t="str">
         <v/>
       </c>
@@ -10025,6 +10383,9 @@
         <v/>
       </c>
       <c r="Z120" t="str">
+        <v/>
+      </c>
+      <c r="AA120" t="str">
         <v/>
       </c>
     </row>
@@ -10063,11 +10424,11 @@
         <v/>
       </c>
       <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
         <v>Manual</v>
       </c>
-      <c r="M121" t="str">
-        <v/>
-      </c>
       <c r="N121" t="str">
         <v/>
       </c>
@@ -10105,6 +10466,9 @@
         <v/>
       </c>
       <c r="Z121" t="str">
+        <v/>
+      </c>
+      <c r="AA121" t="str">
         <v/>
       </c>
     </row>
@@ -10143,11 +10507,11 @@
         <v/>
       </c>
       <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
         <v>Manual</v>
       </c>
-      <c r="M122" t="str">
-        <v/>
-      </c>
       <c r="N122" t="str">
         <v/>
       </c>
@@ -10185,6 +10549,9 @@
         <v/>
       </c>
       <c r="Z122" t="str">
+        <v/>
+      </c>
+      <c r="AA122" t="str">
         <v/>
       </c>
     </row>
@@ -10223,11 +10590,11 @@
         <v/>
       </c>
       <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
         <v>Manual</v>
       </c>
-      <c r="M123" t="str">
-        <v/>
-      </c>
       <c r="N123" t="str">
         <v/>
       </c>
@@ -10265,6 +10632,9 @@
         <v/>
       </c>
       <c r="Z123" t="str">
+        <v/>
+      </c>
+      <c r="AA123" t="str">
         <v/>
       </c>
     </row>
@@ -10303,11 +10673,11 @@
         <v/>
       </c>
       <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
         <v>Manual</v>
       </c>
-      <c r="M124" t="str">
-        <v/>
-      </c>
       <c r="N124" t="str">
         <v/>
       </c>
@@ -10345,6 +10715,9 @@
         <v/>
       </c>
       <c r="Z124" t="str">
+        <v/>
+      </c>
+      <c r="AA124" t="str">
         <v/>
       </c>
     </row>
@@ -10383,11 +10756,11 @@
         <v/>
       </c>
       <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
         <v>Manual</v>
       </c>
-      <c r="M125" t="str">
-        <v/>
-      </c>
       <c r="N125" t="str">
         <v/>
       </c>
@@ -10425,6 +10798,9 @@
         <v/>
       </c>
       <c r="Z125" t="str">
+        <v/>
+      </c>
+      <c r="AA125" t="str">
         <v/>
       </c>
     </row>
@@ -10463,11 +10839,11 @@
         <v/>
       </c>
       <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
         <v>Manual</v>
       </c>
-      <c r="M126" t="str">
-        <v/>
-      </c>
       <c r="N126" t="str">
         <v/>
       </c>
@@ -10505,6 +10881,9 @@
         <v/>
       </c>
       <c r="Z126" t="str">
+        <v/>
+      </c>
+      <c r="AA126" t="str">
         <v/>
       </c>
     </row>
@@ -10543,11 +10922,11 @@
         <v/>
       </c>
       <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
         <v>Manual</v>
       </c>
-      <c r="M127" t="str">
-        <v/>
-      </c>
       <c r="N127" t="str">
         <v/>
       </c>
@@ -10585,6 +10964,9 @@
         <v/>
       </c>
       <c r="Z127" t="str">
+        <v/>
+      </c>
+      <c r="AA127" t="str">
         <v/>
       </c>
     </row>
@@ -10623,11 +11005,11 @@
         <v/>
       </c>
       <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
         <v>Manual</v>
       </c>
-      <c r="M128" t="str">
-        <v/>
-      </c>
       <c r="N128" t="str">
         <v/>
       </c>
@@ -10665,6 +11047,9 @@
         <v/>
       </c>
       <c r="Z128" t="str">
+        <v/>
+      </c>
+      <c r="AA128" t="str">
         <v/>
       </c>
     </row>
@@ -10703,11 +11088,11 @@
         <v/>
       </c>
       <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
         <v>Manual</v>
       </c>
-      <c r="M129" t="str">
-        <v/>
-      </c>
       <c r="N129" t="str">
         <v/>
       </c>
@@ -10745,6 +11130,9 @@
         <v/>
       </c>
       <c r="Z129" t="str">
+        <v/>
+      </c>
+      <c r="AA129" t="str">
         <v/>
       </c>
     </row>
@@ -10783,11 +11171,11 @@
         <v/>
       </c>
       <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
         <v>Manual</v>
       </c>
-      <c r="M130" t="str">
-        <v/>
-      </c>
       <c r="N130" t="str">
         <v/>
       </c>
@@ -10825,6 +11213,9 @@
         <v/>
       </c>
       <c r="Z130" t="str">
+        <v/>
+      </c>
+      <c r="AA130" t="str">
         <v/>
       </c>
     </row>
@@ -10863,11 +11254,11 @@
         <v/>
       </c>
       <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
         <v>Manual</v>
       </c>
-      <c r="M131" t="str">
-        <v/>
-      </c>
       <c r="N131" t="str">
         <v/>
       </c>
@@ -10905,6 +11296,9 @@
         <v/>
       </c>
       <c r="Z131" t="str">
+        <v/>
+      </c>
+      <c r="AA131" t="str">
         <v/>
       </c>
     </row>
@@ -10943,11 +11337,11 @@
         <v/>
       </c>
       <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
         <v>Manual</v>
       </c>
-      <c r="M132" t="str">
-        <v/>
-      </c>
       <c r="N132" t="str">
         <v/>
       </c>
@@ -10985,6 +11379,9 @@
         <v/>
       </c>
       <c r="Z132" t="str">
+        <v/>
+      </c>
+      <c r="AA132" t="str">
         <v/>
       </c>
     </row>
@@ -11023,11 +11420,11 @@
         <v/>
       </c>
       <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
         <v>Manual</v>
       </c>
-      <c r="M133" t="str">
-        <v/>
-      </c>
       <c r="N133" t="str">
         <v/>
       </c>
@@ -11065,6 +11462,9 @@
         <v/>
       </c>
       <c r="Z133" t="str">
+        <v/>
+      </c>
+      <c r="AA133" t="str">
         <v/>
       </c>
     </row>
@@ -11103,11 +11503,11 @@
         <v/>
       </c>
       <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
         <v>Manual</v>
       </c>
-      <c r="M134" t="str">
-        <v/>
-      </c>
       <c r="N134" t="str">
         <v/>
       </c>
@@ -11145,6 +11545,9 @@
         <v/>
       </c>
       <c r="Z134" t="str">
+        <v/>
+      </c>
+      <c r="AA134" t="str">
         <v/>
       </c>
     </row>
@@ -11183,11 +11586,11 @@
         <v/>
       </c>
       <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
         <v>Manual</v>
       </c>
-      <c r="M135" t="str">
-        <v/>
-      </c>
       <c r="N135" t="str">
         <v/>
       </c>
@@ -11225,6 +11628,9 @@
         <v/>
       </c>
       <c r="Z135" t="str">
+        <v/>
+      </c>
+      <c r="AA135" t="str">
         <v/>
       </c>
     </row>
@@ -11263,11 +11669,11 @@
         <v/>
       </c>
       <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
         <v>Manual</v>
       </c>
-      <c r="M136" t="str">
-        <v/>
-      </c>
       <c r="N136" t="str">
         <v/>
       </c>
@@ -11305,6 +11711,9 @@
         <v/>
       </c>
       <c r="Z136" t="str">
+        <v/>
+      </c>
+      <c r="AA136" t="str">
         <v/>
       </c>
     </row>
@@ -11343,11 +11752,11 @@
         <v/>
       </c>
       <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
         <v>Manual</v>
       </c>
-      <c r="M137" t="str">
-        <v/>
-      </c>
       <c r="N137" t="str">
         <v/>
       </c>
@@ -11385,6 +11794,9 @@
         <v/>
       </c>
       <c r="Z137" t="str">
+        <v/>
+      </c>
+      <c r="AA137" t="str">
         <v/>
       </c>
     </row>
@@ -11423,11 +11835,11 @@
         <v/>
       </c>
       <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
         <v>Manual</v>
       </c>
-      <c r="M138" t="str">
-        <v/>
-      </c>
       <c r="N138" t="str">
         <v/>
       </c>
@@ -11465,6 +11877,9 @@
         <v/>
       </c>
       <c r="Z138" t="str">
+        <v/>
+      </c>
+      <c r="AA138" t="str">
         <v/>
       </c>
     </row>
@@ -11503,11 +11918,11 @@
         <v/>
       </c>
       <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
         <v>Manual</v>
       </c>
-      <c r="M139" t="str">
-        <v/>
-      </c>
       <c r="N139" t="str">
         <v/>
       </c>
@@ -11545,6 +11960,9 @@
         <v/>
       </c>
       <c r="Z139" t="str">
+        <v/>
+      </c>
+      <c r="AA139" t="str">
         <v/>
       </c>
     </row>
@@ -11583,11 +12001,11 @@
         <v/>
       </c>
       <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
         <v>Manual</v>
       </c>
-      <c r="M140" t="str">
-        <v/>
-      </c>
       <c r="N140" t="str">
         <v/>
       </c>
@@ -11625,6 +12043,9 @@
         <v/>
       </c>
       <c r="Z140" t="str">
+        <v/>
+      </c>
+      <c r="AA140" t="str">
         <v/>
       </c>
     </row>
@@ -11663,11 +12084,11 @@
         <v/>
       </c>
       <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
         <v>Manual</v>
       </c>
-      <c r="M141" t="str">
-        <v/>
-      </c>
       <c r="N141" t="str">
         <v/>
       </c>
@@ -11705,6 +12126,9 @@
         <v/>
       </c>
       <c r="Z141" t="str">
+        <v/>
+      </c>
+      <c r="AA141" t="str">
         <v/>
       </c>
     </row>
@@ -11743,11 +12167,11 @@
         <v/>
       </c>
       <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
         <v>Manual</v>
       </c>
-      <c r="M142" t="str">
-        <v/>
-      </c>
       <c r="N142" t="str">
         <v/>
       </c>
@@ -11785,6 +12209,9 @@
         <v/>
       </c>
       <c r="Z142" t="str">
+        <v/>
+      </c>
+      <c r="AA142" t="str">
         <v/>
       </c>
     </row>
@@ -11823,11 +12250,11 @@
         <v/>
       </c>
       <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
         <v>Manual</v>
       </c>
-      <c r="M143" t="str">
-        <v/>
-      </c>
       <c r="N143" t="str">
         <v/>
       </c>
@@ -11865,6 +12292,9 @@
         <v/>
       </c>
       <c r="Z143" t="str">
+        <v/>
+      </c>
+      <c r="AA143" t="str">
         <v/>
       </c>
     </row>
@@ -11903,11 +12333,11 @@
         <v/>
       </c>
       <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
         <v>Manual</v>
       </c>
-      <c r="M144" t="str">
-        <v/>
-      </c>
       <c r="N144" t="str">
         <v/>
       </c>
@@ -11945,6 +12375,9 @@
         <v/>
       </c>
       <c r="Z144" t="str">
+        <v/>
+      </c>
+      <c r="AA144" t="str">
         <v/>
       </c>
     </row>
@@ -11983,11 +12416,11 @@
         <v/>
       </c>
       <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
         <v>Manual</v>
       </c>
-      <c r="M145" t="str">
-        <v/>
-      </c>
       <c r="N145" t="str">
         <v/>
       </c>
@@ -12025,6 +12458,9 @@
         <v/>
       </c>
       <c r="Z145" t="str">
+        <v/>
+      </c>
+      <c r="AA145" t="str">
         <v/>
       </c>
     </row>
@@ -12063,11 +12499,11 @@
         <v/>
       </c>
       <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
         <v>Manual</v>
       </c>
-      <c r="M146" t="str">
-        <v/>
-      </c>
       <c r="N146" t="str">
         <v/>
       </c>
@@ -12105,6 +12541,9 @@
         <v/>
       </c>
       <c r="Z146" t="str">
+        <v/>
+      </c>
+      <c r="AA146" t="str">
         <v/>
       </c>
     </row>
@@ -12143,11 +12582,11 @@
         <v/>
       </c>
       <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
         <v>Manual</v>
       </c>
-      <c r="M147" t="str">
-        <v/>
-      </c>
       <c r="N147" t="str">
         <v/>
       </c>
@@ -12185,6 +12624,9 @@
         <v/>
       </c>
       <c r="Z147" t="str">
+        <v/>
+      </c>
+      <c r="AA147" t="str">
         <v/>
       </c>
     </row>
@@ -12223,11 +12665,11 @@
         <v/>
       </c>
       <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
         <v>Manual</v>
       </c>
-      <c r="M148" t="str">
-        <v/>
-      </c>
       <c r="N148" t="str">
         <v/>
       </c>
@@ -12265,6 +12707,9 @@
         <v/>
       </c>
       <c r="Z148" t="str">
+        <v/>
+      </c>
+      <c r="AA148" t="str">
         <v/>
       </c>
     </row>
@@ -12303,11 +12748,11 @@
         <v/>
       </c>
       <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str">
         <v>Manual</v>
       </c>
-      <c r="M149" t="str">
-        <v/>
-      </c>
       <c r="N149" t="str">
         <v/>
       </c>
@@ -12345,6 +12790,9 @@
         <v/>
       </c>
       <c r="Z149" t="str">
+        <v/>
+      </c>
+      <c r="AA149" t="str">
         <v/>
       </c>
     </row>
@@ -12383,11 +12831,11 @@
         <v/>
       </c>
       <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
         <v>Manual</v>
       </c>
-      <c r="M150" t="str">
-        <v/>
-      </c>
       <c r="N150" t="str">
         <v/>
       </c>
@@ -12425,6 +12873,9 @@
         <v/>
       </c>
       <c r="Z150" t="str">
+        <v/>
+      </c>
+      <c r="AA150" t="str">
         <v/>
       </c>
     </row>
@@ -12463,11 +12914,11 @@
         <v/>
       </c>
       <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
         <v>Manual</v>
       </c>
-      <c r="M151" t="str">
-        <v/>
-      </c>
       <c r="N151" t="str">
         <v/>
       </c>
@@ -12505,6 +12956,9 @@
         <v/>
       </c>
       <c r="Z151" t="str">
+        <v/>
+      </c>
+      <c r="AA151" t="str">
         <v/>
       </c>
     </row>
@@ -12543,11 +12997,11 @@
         <v/>
       </c>
       <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
         <v>Manual</v>
       </c>
-      <c r="M152" t="str">
-        <v/>
-      </c>
       <c r="N152" t="str">
         <v/>
       </c>
@@ -12585,6 +13039,9 @@
         <v/>
       </c>
       <c r="Z152" t="str">
+        <v/>
+      </c>
+      <c r="AA152" t="str">
         <v/>
       </c>
     </row>
@@ -12623,11 +13080,11 @@
         <v/>
       </c>
       <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
         <v>Manual</v>
       </c>
-      <c r="M153" t="str">
-        <v/>
-      </c>
       <c r="N153" t="str">
         <v/>
       </c>
@@ -12665,6 +13122,9 @@
         <v/>
       </c>
       <c r="Z153" t="str">
+        <v/>
+      </c>
+      <c r="AA153" t="str">
         <v/>
       </c>
     </row>
@@ -12703,11 +13163,11 @@
         <v/>
       </c>
       <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
         <v>Manual</v>
       </c>
-      <c r="M154" t="str">
-        <v/>
-      </c>
       <c r="N154" t="str">
         <v/>
       </c>
@@ -12745,6 +13205,9 @@
         <v/>
       </c>
       <c r="Z154" t="str">
+        <v/>
+      </c>
+      <c r="AA154" t="str">
         <v/>
       </c>
     </row>
@@ -12783,11 +13246,11 @@
         <v/>
       </c>
       <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
         <v>Manual</v>
       </c>
-      <c r="M155" t="str">
-        <v/>
-      </c>
       <c r="N155" t="str">
         <v/>
       </c>
@@ -12825,6 +13288,9 @@
         <v/>
       </c>
       <c r="Z155" t="str">
+        <v/>
+      </c>
+      <c r="AA155" t="str">
         <v/>
       </c>
     </row>
@@ -12863,11 +13329,11 @@
         <v/>
       </c>
       <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str">
         <v>Manual</v>
       </c>
-      <c r="M156" t="str">
-        <v/>
-      </c>
       <c r="N156" t="str">
         <v/>
       </c>
@@ -12905,6 +13371,9 @@
         <v/>
       </c>
       <c r="Z156" t="str">
+        <v/>
+      </c>
+      <c r="AA156" t="str">
         <v/>
       </c>
     </row>
@@ -12943,11 +13412,11 @@
         <v/>
       </c>
       <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
         <v>Manual</v>
       </c>
-      <c r="M157" t="str">
-        <v/>
-      </c>
       <c r="N157" t="str">
         <v/>
       </c>
@@ -12985,6 +13454,9 @@
         <v/>
       </c>
       <c r="Z157" t="str">
+        <v/>
+      </c>
+      <c r="AA157" t="str">
         <v/>
       </c>
     </row>
@@ -13023,11 +13495,11 @@
         <v/>
       </c>
       <c r="L158" t="str">
+        <v/>
+      </c>
+      <c r="M158" t="str">
         <v>Manual</v>
       </c>
-      <c r="M158" t="str">
-        <v/>
-      </c>
       <c r="N158" t="str">
         <v/>
       </c>
@@ -13065,6 +13537,9 @@
         <v/>
       </c>
       <c r="Z158" t="str">
+        <v/>
+      </c>
+      <c r="AA158" t="str">
         <v/>
       </c>
     </row>
@@ -13103,11 +13578,11 @@
         <v/>
       </c>
       <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str">
         <v>Manual</v>
       </c>
-      <c r="M159" t="str">
-        <v/>
-      </c>
       <c r="N159" t="str">
         <v/>
       </c>
@@ -13145,6 +13620,9 @@
         <v/>
       </c>
       <c r="Z159" t="str">
+        <v/>
+      </c>
+      <c r="AA159" t="str">
         <v/>
       </c>
     </row>
@@ -13183,11 +13661,11 @@
         <v/>
       </c>
       <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str">
         <v>Manual</v>
       </c>
-      <c r="M160" t="str">
-        <v/>
-      </c>
       <c r="N160" t="str">
         <v/>
       </c>
@@ -13225,6 +13703,9 @@
         <v/>
       </c>
       <c r="Z160" t="str">
+        <v/>
+      </c>
+      <c r="AA160" t="str">
         <v/>
       </c>
     </row>
@@ -13263,11 +13744,11 @@
         <v/>
       </c>
       <c r="L161" t="str">
+        <v/>
+      </c>
+      <c r="M161" t="str">
         <v>Manual</v>
       </c>
-      <c r="M161" t="str">
-        <v/>
-      </c>
       <c r="N161" t="str">
         <v/>
       </c>
@@ -13305,6 +13786,9 @@
         <v/>
       </c>
       <c r="Z161" t="str">
+        <v/>
+      </c>
+      <c r="AA161" t="str">
         <v/>
       </c>
     </row>
@@ -13343,11 +13827,11 @@
         <v/>
       </c>
       <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str">
         <v>Manual</v>
       </c>
-      <c r="M162" t="str">
-        <v/>
-      </c>
       <c r="N162" t="str">
         <v/>
       </c>
@@ -13385,6 +13869,9 @@
         <v/>
       </c>
       <c r="Z162" t="str">
+        <v/>
+      </c>
+      <c r="AA162" t="str">
         <v/>
       </c>
     </row>
@@ -13423,11 +13910,11 @@
         <v/>
       </c>
       <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
         <v>Manual</v>
       </c>
-      <c r="M163" t="str">
-        <v/>
-      </c>
       <c r="N163" t="str">
         <v/>
       </c>
@@ -13465,6 +13952,9 @@
         <v/>
       </c>
       <c r="Z163" t="str">
+        <v/>
+      </c>
+      <c r="AA163" t="str">
         <v/>
       </c>
     </row>
@@ -13503,11 +13993,11 @@
         <v/>
       </c>
       <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
         <v>Manual</v>
       </c>
-      <c r="M164" t="str">
-        <v/>
-      </c>
       <c r="N164" t="str">
         <v/>
       </c>
@@ -13545,6 +14035,9 @@
         <v/>
       </c>
       <c r="Z164" t="str">
+        <v/>
+      </c>
+      <c r="AA164" t="str">
         <v/>
       </c>
     </row>
@@ -13583,11 +14076,11 @@
         <v/>
       </c>
       <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
         <v>Manual</v>
       </c>
-      <c r="M165" t="str">
-        <v/>
-      </c>
       <c r="N165" t="str">
         <v/>
       </c>
@@ -13625,6 +14118,9 @@
         <v/>
       </c>
       <c r="Z165" t="str">
+        <v/>
+      </c>
+      <c r="AA165" t="str">
         <v/>
       </c>
     </row>
@@ -13663,11 +14159,11 @@
         <v/>
       </c>
       <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
         <v>Manual</v>
       </c>
-      <c r="M166" t="str">
-        <v/>
-      </c>
       <c r="N166" t="str">
         <v/>
       </c>
@@ -13705,6 +14201,9 @@
         <v/>
       </c>
       <c r="Z166" t="str">
+        <v/>
+      </c>
+      <c r="AA166" t="str">
         <v/>
       </c>
     </row>
@@ -13743,11 +14242,11 @@
         <v/>
       </c>
       <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
         <v>Manual</v>
       </c>
-      <c r="M167" t="str">
-        <v/>
-      </c>
       <c r="N167" t="str">
         <v/>
       </c>
@@ -13785,6 +14284,9 @@
         <v/>
       </c>
       <c r="Z167" t="str">
+        <v/>
+      </c>
+      <c r="AA167" t="str">
         <v/>
       </c>
     </row>
@@ -13823,11 +14325,11 @@
         <v/>
       </c>
       <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
         <v>Manual</v>
       </c>
-      <c r="M168" t="str">
-        <v/>
-      </c>
       <c r="N168" t="str">
         <v/>
       </c>
@@ -13865,6 +14367,9 @@
         <v/>
       </c>
       <c r="Z168" t="str">
+        <v/>
+      </c>
+      <c r="AA168" t="str">
         <v/>
       </c>
     </row>
@@ -13903,11 +14408,11 @@
         <v/>
       </c>
       <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str">
         <v>Manual</v>
       </c>
-      <c r="M169" t="str">
-        <v/>
-      </c>
       <c r="N169" t="str">
         <v/>
       </c>
@@ -13945,6 +14450,9 @@
         <v/>
       </c>
       <c r="Z169" t="str">
+        <v/>
+      </c>
+      <c r="AA169" t="str">
         <v/>
       </c>
     </row>
@@ -13983,11 +14491,11 @@
         <v/>
       </c>
       <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str">
         <v>Manual</v>
       </c>
-      <c r="M170" t="str">
-        <v/>
-      </c>
       <c r="N170" t="str">
         <v/>
       </c>
@@ -14025,6 +14533,9 @@
         <v/>
       </c>
       <c r="Z170" t="str">
+        <v/>
+      </c>
+      <c r="AA170" t="str">
         <v/>
       </c>
     </row>
@@ -14063,11 +14574,11 @@
         <v/>
       </c>
       <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
         <v>Manual</v>
       </c>
-      <c r="M171" t="str">
-        <v/>
-      </c>
       <c r="N171" t="str">
         <v/>
       </c>
@@ -14105,6 +14616,9 @@
         <v/>
       </c>
       <c r="Z171" t="str">
+        <v/>
+      </c>
+      <c r="AA171" t="str">
         <v/>
       </c>
     </row>
@@ -14143,11 +14657,11 @@
         <v/>
       </c>
       <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str">
         <v>Manual</v>
       </c>
-      <c r="M172" t="str">
-        <v/>
-      </c>
       <c r="N172" t="str">
         <v/>
       </c>
@@ -14185,6 +14699,9 @@
         <v/>
       </c>
       <c r="Z172" t="str">
+        <v/>
+      </c>
+      <c r="AA172" t="str">
         <v/>
       </c>
     </row>
@@ -14223,11 +14740,11 @@
         <v/>
       </c>
       <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
         <v>Manual</v>
       </c>
-      <c r="M173" t="str">
-        <v/>
-      </c>
       <c r="N173" t="str">
         <v/>
       </c>
@@ -14265,6 +14782,9 @@
         <v/>
       </c>
       <c r="Z173" t="str">
+        <v/>
+      </c>
+      <c r="AA173" t="str">
         <v/>
       </c>
     </row>
@@ -14303,11 +14823,11 @@
         <v/>
       </c>
       <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str">
         <v>Manual</v>
       </c>
-      <c r="M174" t="str">
-        <v/>
-      </c>
       <c r="N174" t="str">
         <v/>
       </c>
@@ -14345,6 +14865,9 @@
         <v/>
       </c>
       <c r="Z174" t="str">
+        <v/>
+      </c>
+      <c r="AA174" t="str">
         <v/>
       </c>
     </row>
@@ -14383,11 +14906,11 @@
         <v/>
       </c>
       <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str">
         <v>Manual</v>
       </c>
-      <c r="M175" t="str">
-        <v/>
-      </c>
       <c r="N175" t="str">
         <v/>
       </c>
@@ -14425,6 +14948,9 @@
         <v/>
       </c>
       <c r="Z175" t="str">
+        <v/>
+      </c>
+      <c r="AA175" t="str">
         <v/>
       </c>
     </row>
@@ -14463,11 +14989,11 @@
         <v/>
       </c>
       <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str">
         <v>Manual</v>
       </c>
-      <c r="M176" t="str">
-        <v/>
-      </c>
       <c r="N176" t="str">
         <v/>
       </c>
@@ -14505,6 +15031,9 @@
         <v/>
       </c>
       <c r="Z176" t="str">
+        <v/>
+      </c>
+      <c r="AA176" t="str">
         <v/>
       </c>
     </row>
@@ -14543,11 +15072,11 @@
         <v/>
       </c>
       <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str">
         <v>Manual</v>
       </c>
-      <c r="M177" t="str">
-        <v/>
-      </c>
       <c r="N177" t="str">
         <v/>
       </c>
@@ -14585,6 +15114,9 @@
         <v/>
       </c>
       <c r="Z177" t="str">
+        <v/>
+      </c>
+      <c r="AA177" t="str">
         <v/>
       </c>
     </row>
@@ -14623,11 +15155,11 @@
         <v/>
       </c>
       <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str">
         <v>Manual</v>
       </c>
-      <c r="M178" t="str">
-        <v/>
-      </c>
       <c r="N178" t="str">
         <v/>
       </c>
@@ -14665,6 +15197,9 @@
         <v/>
       </c>
       <c r="Z178" t="str">
+        <v/>
+      </c>
+      <c r="AA178" t="str">
         <v/>
       </c>
     </row>
@@ -14703,11 +15238,11 @@
         <v/>
       </c>
       <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
         <v>Manual</v>
       </c>
-      <c r="M179" t="str">
-        <v/>
-      </c>
       <c r="N179" t="str">
         <v/>
       </c>
@@ -14745,6 +15280,9 @@
         <v/>
       </c>
       <c r="Z179" t="str">
+        <v/>
+      </c>
+      <c r="AA179" t="str">
         <v/>
       </c>
     </row>
@@ -14783,11 +15321,11 @@
         <v/>
       </c>
       <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
         <v>Manual</v>
       </c>
-      <c r="M180" t="str">
-        <v/>
-      </c>
       <c r="N180" t="str">
         <v/>
       </c>
@@ -14825,6 +15363,9 @@
         <v/>
       </c>
       <c r="Z180" t="str">
+        <v/>
+      </c>
+      <c r="AA180" t="str">
         <v/>
       </c>
     </row>
@@ -14863,11 +15404,11 @@
         <v/>
       </c>
       <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
         <v>Manual</v>
       </c>
-      <c r="M181" t="str">
-        <v/>
-      </c>
       <c r="N181" t="str">
         <v/>
       </c>
@@ -14905,6 +15446,9 @@
         <v/>
       </c>
       <c r="Z181" t="str">
+        <v/>
+      </c>
+      <c r="AA181" t="str">
         <v/>
       </c>
     </row>
@@ -14943,11 +15487,11 @@
         <v/>
       </c>
       <c r="L182" t="str">
+        <v/>
+      </c>
+      <c r="M182" t="str">
         <v>Manual</v>
       </c>
-      <c r="M182" t="str">
-        <v/>
-      </c>
       <c r="N182" t="str">
         <v/>
       </c>
@@ -14985,6 +15529,9 @@
         <v/>
       </c>
       <c r="Z182" t="str">
+        <v/>
+      </c>
+      <c r="AA182" t="str">
         <v/>
       </c>
     </row>
@@ -15023,11 +15570,11 @@
         <v/>
       </c>
       <c r="L183" t="str">
+        <v/>
+      </c>
+      <c r="M183" t="str">
         <v>Manual</v>
       </c>
-      <c r="M183" t="str">
-        <v/>
-      </c>
       <c r="N183" t="str">
         <v/>
       </c>
@@ -15065,6 +15612,9 @@
         <v/>
       </c>
       <c r="Z183" t="str">
+        <v/>
+      </c>
+      <c r="AA183" t="str">
         <v/>
       </c>
     </row>
@@ -15103,11 +15653,11 @@
         <v/>
       </c>
       <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
         <v>Manual</v>
       </c>
-      <c r="M184" t="str">
-        <v/>
-      </c>
       <c r="N184" t="str">
         <v/>
       </c>
@@ -15145,6 +15695,9 @@
         <v/>
       </c>
       <c r="Z184" t="str">
+        <v/>
+      </c>
+      <c r="AA184" t="str">
         <v/>
       </c>
     </row>
@@ -15183,11 +15736,11 @@
         <v/>
       </c>
       <c r="L185" t="str">
+        <v/>
+      </c>
+      <c r="M185" t="str">
         <v>Manual</v>
       </c>
-      <c r="M185" t="str">
-        <v/>
-      </c>
       <c r="N185" t="str">
         <v/>
       </c>
@@ -15225,6 +15778,9 @@
         <v/>
       </c>
       <c r="Z185" t="str">
+        <v/>
+      </c>
+      <c r="AA185" t="str">
         <v/>
       </c>
     </row>
@@ -15263,11 +15819,11 @@
         <v/>
       </c>
       <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str">
         <v>Manual</v>
       </c>
-      <c r="M186" t="str">
-        <v/>
-      </c>
       <c r="N186" t="str">
         <v/>
       </c>
@@ -15305,6 +15861,9 @@
         <v/>
       </c>
       <c r="Z186" t="str">
+        <v/>
+      </c>
+      <c r="AA186" t="str">
         <v/>
       </c>
     </row>
@@ -15343,11 +15902,11 @@
         <v/>
       </c>
       <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str">
         <v>Manual</v>
       </c>
-      <c r="M187" t="str">
-        <v/>
-      </c>
       <c r="N187" t="str">
         <v/>
       </c>
@@ -15385,6 +15944,9 @@
         <v/>
       </c>
       <c r="Z187" t="str">
+        <v/>
+      </c>
+      <c r="AA187" t="str">
         <v/>
       </c>
     </row>
@@ -15423,11 +15985,11 @@
         <v/>
       </c>
       <c r="L188" t="str">
+        <v/>
+      </c>
+      <c r="M188" t="str">
         <v>Manual</v>
       </c>
-      <c r="M188" t="str">
-        <v/>
-      </c>
       <c r="N188" t="str">
         <v/>
       </c>
@@ -15465,6 +16027,9 @@
         <v/>
       </c>
       <c r="Z188" t="str">
+        <v/>
+      </c>
+      <c r="AA188" t="str">
         <v/>
       </c>
     </row>
@@ -15503,11 +16068,11 @@
         <v/>
       </c>
       <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str">
         <v>Manual</v>
       </c>
-      <c r="M189" t="str">
-        <v/>
-      </c>
       <c r="N189" t="str">
         <v/>
       </c>
@@ -15545,6 +16110,9 @@
         <v/>
       </c>
       <c r="Z189" t="str">
+        <v/>
+      </c>
+      <c r="AA189" t="str">
         <v/>
       </c>
     </row>
@@ -15583,11 +16151,11 @@
         <v/>
       </c>
       <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
         <v>Manual</v>
       </c>
-      <c r="M190" t="str">
-        <v/>
-      </c>
       <c r="N190" t="str">
         <v/>
       </c>
@@ -15625,6 +16193,9 @@
         <v/>
       </c>
       <c r="Z190" t="str">
+        <v/>
+      </c>
+      <c r="AA190" t="str">
         <v/>
       </c>
     </row>
@@ -15663,11 +16234,11 @@
         <v/>
       </c>
       <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
         <v>Manual</v>
       </c>
-      <c r="M191" t="str">
-        <v/>
-      </c>
       <c r="N191" t="str">
         <v/>
       </c>
@@ -15705,6 +16276,9 @@
         <v/>
       </c>
       <c r="Z191" t="str">
+        <v/>
+      </c>
+      <c r="AA191" t="str">
         <v/>
       </c>
     </row>
@@ -15743,11 +16317,11 @@
         <v/>
       </c>
       <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
         <v>Manual</v>
       </c>
-      <c r="M192" t="str">
-        <v/>
-      </c>
       <c r="N192" t="str">
         <v/>
       </c>
@@ -15785,6 +16359,9 @@
         <v/>
       </c>
       <c r="Z192" t="str">
+        <v/>
+      </c>
+      <c r="AA192" t="str">
         <v/>
       </c>
     </row>
@@ -15820,14 +16397,14 @@
         <v/>
       </c>
       <c r="K193" t="str">
+        <v/>
+      </c>
+      <c r="L193" t="str">
         <v>Yes</v>
       </c>
-      <c r="L193" t="str">
+      <c r="M193" t="str">
         <v>Manual</v>
       </c>
-      <c r="M193" t="str">
-        <v/>
-      </c>
       <c r="N193" t="str">
         <v/>
       </c>
@@ -15865,6 +16442,9 @@
         <v/>
       </c>
       <c r="Z193" t="str">
+        <v/>
+      </c>
+      <c r="AA193" t="str">
         <v/>
       </c>
     </row>
@@ -15903,11 +16483,11 @@
         <v/>
       </c>
       <c r="L194" t="str">
+        <v/>
+      </c>
+      <c r="M194" t="str">
         <v>Manual</v>
       </c>
-      <c r="M194" t="str">
-        <v/>
-      </c>
       <c r="N194" t="str">
         <v/>
       </c>
@@ -15945,6 +16525,9 @@
         <v/>
       </c>
       <c r="Z194" t="str">
+        <v/>
+      </c>
+      <c r="AA194" t="str">
         <v/>
       </c>
     </row>
@@ -15983,11 +16566,11 @@
         <v/>
       </c>
       <c r="L195" t="str">
+        <v/>
+      </c>
+      <c r="M195" t="str">
         <v>Manual</v>
       </c>
-      <c r="M195" t="str">
-        <v/>
-      </c>
       <c r="N195" t="str">
         <v/>
       </c>
@@ -16025,6 +16608,9 @@
         <v/>
       </c>
       <c r="Z195" t="str">
+        <v/>
+      </c>
+      <c r="AA195" t="str">
         <v/>
       </c>
     </row>
@@ -16060,14 +16646,14 @@
         <v/>
       </c>
       <c r="K196" t="str">
+        <v/>
+      </c>
+      <c r="L196" t="str">
         <v>Yes</v>
       </c>
-      <c r="L196" t="str">
+      <c r="M196" t="str">
         <v>Manual</v>
       </c>
-      <c r="M196" t="str">
-        <v/>
-      </c>
       <c r="N196" t="str">
         <v/>
       </c>
@@ -16105,6 +16691,9 @@
         <v/>
       </c>
       <c r="Z196" t="str">
+        <v/>
+      </c>
+      <c r="AA196" t="str">
         <v/>
       </c>
     </row>
@@ -16116,13 +16705,13 @@
         <v>Tuesday</v>
       </c>
       <c r="C197" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="D197" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="E197" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F197" t="str">
         <v/>
@@ -16130,11 +16719,11 @@
       <c r="G197" t="str">
         <v/>
       </c>
-      <c r="H197" t="str">
-        <v/>
-      </c>
-      <c r="I197" t="str">
-        <v/>
+      <c r="H197">
+        <v>51.73294285542534</v>
+      </c>
+      <c r="I197">
+        <v>-1.2373467146427453</v>
       </c>
       <c r="J197" t="str">
         <v/>
@@ -16143,10 +16732,10 @@
         <v/>
       </c>
       <c r="L197" t="str">
-        <v>Booking</v>
+        <v>Yes</v>
       </c>
       <c r="M197" t="str">
-        <v/>
+        <v>GPS + Manual</v>
       </c>
       <c r="N197" t="str">
         <v/>
@@ -16176,16 +16765,19 @@
         <v/>
       </c>
       <c r="W197" t="str">
-        <v>email: Fw: Your booking confirmation Z9VFXQ</v>
+        <v/>
       </c>
       <c r="X197" t="str">
         <v/>
       </c>
       <c r="Y197" t="str">
+        <v/>
+      </c>
+      <c r="Z197" t="str">
+        <v/>
+      </c>
+      <c r="AA197" t="str">
         <v>Yes</v>
-      </c>
-      <c r="Z197" t="str">
-        <v/>
       </c>
     </row>
     <row r="198">
@@ -16196,7 +16788,7 @@
         <v>Wednesday</v>
       </c>
       <c r="C198" t="str">
-        <v>417 Meadow Lane</v>
+        <v>Oxford</v>
       </c>
       <c r="D198" t="str">
         <v>Oxford</v>
@@ -16210,11 +16802,11 @@
       <c r="G198" t="str">
         <v/>
       </c>
-      <c r="H198" t="str">
-        <v/>
-      </c>
-      <c r="I198" t="str">
-        <v/>
+      <c r="H198">
+        <v>51.7329714</v>
+      </c>
+      <c r="I198">
+        <v>-1.2376777</v>
       </c>
       <c r="J198" t="str">
         <v/>
@@ -16223,10 +16815,10 @@
         <v/>
       </c>
       <c r="L198" t="str">
-        <v>Manual</v>
+        <v>Yes</v>
       </c>
       <c r="M198" t="str">
-        <v/>
+        <v>GPS + Manual</v>
       </c>
       <c r="N198" t="str">
         <v/>
@@ -16266,6 +16858,9 @@
       </c>
       <c r="Z198" t="str">
         <v/>
+      </c>
+      <c r="AA198" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="199">
@@ -16303,11 +16898,11 @@
         <v/>
       </c>
       <c r="L199" t="str">
+        <v/>
+      </c>
+      <c r="M199" t="str">
         <v>Manual</v>
       </c>
-      <c r="M199" t="str">
-        <v/>
-      </c>
       <c r="N199" t="str">
         <v/>
       </c>
@@ -16345,6 +16940,9 @@
         <v/>
       </c>
       <c r="Z199" t="str">
+        <v/>
+      </c>
+      <c r="AA199" t="str">
         <v/>
       </c>
     </row>
@@ -16383,11 +16981,11 @@
         <v/>
       </c>
       <c r="L200" t="str">
+        <v/>
+      </c>
+      <c r="M200" t="str">
         <v>Manual</v>
       </c>
-      <c r="M200" t="str">
-        <v/>
-      </c>
       <c r="N200" t="str">
         <v/>
       </c>
@@ -16425,6 +17023,9 @@
         <v/>
       </c>
       <c r="Z200" t="str">
+        <v/>
+      </c>
+      <c r="AA200" t="str">
         <v/>
       </c>
     </row>
@@ -16463,11 +17064,11 @@
         <v/>
       </c>
       <c r="L201" t="str">
+        <v/>
+      </c>
+      <c r="M201" t="str">
         <v>Manual</v>
       </c>
-      <c r="M201" t="str">
-        <v/>
-      </c>
       <c r="N201" t="str">
         <v/>
       </c>
@@ -16505,6 +17106,9 @@
         <v/>
       </c>
       <c r="Z201" t="str">
+        <v/>
+      </c>
+      <c r="AA201" t="str">
         <v/>
       </c>
     </row>
@@ -16543,11 +17147,11 @@
         <v/>
       </c>
       <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str">
         <v>Manual</v>
       </c>
-      <c r="M202" t="str">
-        <v/>
-      </c>
       <c r="N202" t="str">
         <v/>
       </c>
@@ -16585,6 +17189,9 @@
         <v/>
       </c>
       <c r="Z202" t="str">
+        <v/>
+      </c>
+      <c r="AA202" t="str">
         <v/>
       </c>
     </row>
@@ -16623,11 +17230,11 @@
         <v/>
       </c>
       <c r="L203" t="str">
+        <v/>
+      </c>
+      <c r="M203" t="str">
         <v>Manual</v>
       </c>
-      <c r="M203" t="str">
-        <v/>
-      </c>
       <c r="N203" t="str">
         <v/>
       </c>
@@ -16665,6 +17272,9 @@
         <v/>
       </c>
       <c r="Z203" t="str">
+        <v/>
+      </c>
+      <c r="AA203" t="str">
         <v/>
       </c>
     </row>
@@ -16703,11 +17313,11 @@
         <v/>
       </c>
       <c r="L204" t="str">
+        <v/>
+      </c>
+      <c r="M204" t="str">
         <v>Manual</v>
       </c>
-      <c r="M204" t="str">
-        <v/>
-      </c>
       <c r="N204" t="str">
         <v/>
       </c>
@@ -16745,6 +17355,9 @@
         <v/>
       </c>
       <c r="Z204" t="str">
+        <v/>
+      </c>
+      <c r="AA204" t="str">
         <v/>
       </c>
     </row>
@@ -16783,11 +17396,11 @@
         <v/>
       </c>
       <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str">
         <v>Manual</v>
       </c>
-      <c r="M205" t="str">
-        <v/>
-      </c>
       <c r="N205" t="str">
         <v/>
       </c>
@@ -16825,6 +17438,9 @@
         <v/>
       </c>
       <c r="Z205" t="str">
+        <v/>
+      </c>
+      <c r="AA205" t="str">
         <v/>
       </c>
     </row>
@@ -16863,11 +17479,11 @@
         <v/>
       </c>
       <c r="L206" t="str">
+        <v/>
+      </c>
+      <c r="M206" t="str">
         <v>Manual</v>
       </c>
-      <c r="M206" t="str">
-        <v/>
-      </c>
       <c r="N206" t="str">
         <v/>
       </c>
@@ -16905,6 +17521,9 @@
         <v/>
       </c>
       <c r="Z206" t="str">
+        <v/>
+      </c>
+      <c r="AA206" t="str">
         <v/>
       </c>
     </row>
@@ -16943,11 +17562,11 @@
         <v/>
       </c>
       <c r="L207" t="str">
+        <v/>
+      </c>
+      <c r="M207" t="str">
         <v>Manual</v>
       </c>
-      <c r="M207" t="str">
-        <v/>
-      </c>
       <c r="N207" t="str">
         <v/>
       </c>
@@ -16985,6 +17604,9 @@
         <v/>
       </c>
       <c r="Z207" t="str">
+        <v/>
+      </c>
+      <c r="AA207" t="str">
         <v/>
       </c>
     </row>
@@ -17023,11 +17645,11 @@
         <v/>
       </c>
       <c r="L208" t="str">
+        <v/>
+      </c>
+      <c r="M208" t="str">
         <v>Manual</v>
       </c>
-      <c r="M208" t="str">
-        <v/>
-      </c>
       <c r="N208" t="str">
         <v/>
       </c>
@@ -17065,6 +17687,9 @@
         <v/>
       </c>
       <c r="Z208" t="str">
+        <v/>
+      </c>
+      <c r="AA208" t="str">
         <v/>
       </c>
     </row>
@@ -17103,11 +17728,11 @@
         <v/>
       </c>
       <c r="L209" t="str">
+        <v/>
+      </c>
+      <c r="M209" t="str">
         <v>Manual</v>
       </c>
-      <c r="M209" t="str">
-        <v/>
-      </c>
       <c r="N209" t="str">
         <v/>
       </c>
@@ -17145,6 +17770,9 @@
         <v/>
       </c>
       <c r="Z209" t="str">
+        <v/>
+      </c>
+      <c r="AA209" t="str">
         <v/>
       </c>
     </row>
@@ -17183,11 +17811,11 @@
         <v/>
       </c>
       <c r="L210" t="str">
+        <v/>
+      </c>
+      <c r="M210" t="str">
         <v>Manual</v>
       </c>
-      <c r="M210" t="str">
-        <v/>
-      </c>
       <c r="N210" t="str">
         <v/>
       </c>
@@ -17225,6 +17853,9 @@
         <v/>
       </c>
       <c r="Z210" t="str">
+        <v/>
+      </c>
+      <c r="AA210" t="str">
         <v/>
       </c>
     </row>
@@ -17263,11 +17894,11 @@
         <v/>
       </c>
       <c r="L211" t="str">
+        <v/>
+      </c>
+      <c r="M211" t="str">
         <v>Manual</v>
       </c>
-      <c r="M211" t="str">
-        <v/>
-      </c>
       <c r="N211" t="str">
         <v/>
       </c>
@@ -17305,6 +17936,9 @@
         <v/>
       </c>
       <c r="Z211" t="str">
+        <v/>
+      </c>
+      <c r="AA211" t="str">
         <v/>
       </c>
     </row>
@@ -17343,11 +17977,11 @@
         <v/>
       </c>
       <c r="L212" t="str">
+        <v/>
+      </c>
+      <c r="M212" t="str">
         <v>Manual</v>
       </c>
-      <c r="M212" t="str">
-        <v/>
-      </c>
       <c r="N212" t="str">
         <v/>
       </c>
@@ -17385,6 +18019,9 @@
         <v/>
       </c>
       <c r="Z212" t="str">
+        <v/>
+      </c>
+      <c r="AA212" t="str">
         <v/>
       </c>
     </row>
@@ -17423,11 +18060,11 @@
         <v/>
       </c>
       <c r="L213" t="str">
+        <v/>
+      </c>
+      <c r="M213" t="str">
         <v>Manual</v>
       </c>
-      <c r="M213" t="str">
-        <v/>
-      </c>
       <c r="N213" t="str">
         <v/>
       </c>
@@ -17465,6 +18102,9 @@
         <v/>
       </c>
       <c r="Z213" t="str">
+        <v/>
+      </c>
+      <c r="AA213" t="str">
         <v/>
       </c>
     </row>
@@ -17503,11 +18143,11 @@
         <v/>
       </c>
       <c r="L214" t="str">
+        <v/>
+      </c>
+      <c r="M214" t="str">
         <v>Manual</v>
       </c>
-      <c r="M214" t="str">
-        <v/>
-      </c>
       <c r="N214" t="str">
         <v/>
       </c>
@@ -17545,6 +18185,9 @@
         <v/>
       </c>
       <c r="Z214" t="str">
+        <v/>
+      </c>
+      <c r="AA214" t="str">
         <v/>
       </c>
     </row>
@@ -17583,11 +18226,11 @@
         <v/>
       </c>
       <c r="L215" t="str">
+        <v/>
+      </c>
+      <c r="M215" t="str">
         <v>Manual</v>
       </c>
-      <c r="M215" t="str">
-        <v/>
-      </c>
       <c r="N215" t="str">
         <v/>
       </c>
@@ -17625,6 +18268,9 @@
         <v/>
       </c>
       <c r="Z215" t="str">
+        <v/>
+      </c>
+      <c r="AA215" t="str">
         <v/>
       </c>
     </row>
@@ -17663,11 +18309,11 @@
         <v/>
       </c>
       <c r="L216" t="str">
+        <v/>
+      </c>
+      <c r="M216" t="str">
         <v>Manual</v>
       </c>
-      <c r="M216" t="str">
-        <v/>
-      </c>
       <c r="N216" t="str">
         <v/>
       </c>
@@ -17705,6 +18351,9 @@
         <v/>
       </c>
       <c r="Z216" t="str">
+        <v/>
+      </c>
+      <c r="AA216" t="str">
         <v/>
       </c>
     </row>
@@ -17743,11 +18392,11 @@
         <v/>
       </c>
       <c r="L217" t="str">
+        <v/>
+      </c>
+      <c r="M217" t="str">
         <v>Manual</v>
       </c>
-      <c r="M217" t="str">
-        <v/>
-      </c>
       <c r="N217" t="str">
         <v/>
       </c>
@@ -17785,6 +18434,9 @@
         <v/>
       </c>
       <c r="Z217" t="str">
+        <v/>
+      </c>
+      <c r="AA217" t="str">
         <v/>
       </c>
     </row>
@@ -17823,11 +18475,11 @@
         <v/>
       </c>
       <c r="L218" t="str">
+        <v/>
+      </c>
+      <c r="M218" t="str">
         <v>Manual</v>
       </c>
-      <c r="M218" t="str">
-        <v/>
-      </c>
       <c r="N218" t="str">
         <v/>
       </c>
@@ -17865,6 +18517,9 @@
         <v/>
       </c>
       <c r="Z218" t="str">
+        <v/>
+      </c>
+      <c r="AA218" t="str">
         <v/>
       </c>
     </row>
@@ -17903,11 +18558,11 @@
         <v/>
       </c>
       <c r="L219" t="str">
+        <v/>
+      </c>
+      <c r="M219" t="str">
         <v>Manual</v>
       </c>
-      <c r="M219" t="str">
-        <v/>
-      </c>
       <c r="N219" t="str">
         <v/>
       </c>
@@ -17945,6 +18600,9 @@
         <v/>
       </c>
       <c r="Z219" t="str">
+        <v/>
+      </c>
+      <c r="AA219" t="str">
         <v/>
       </c>
     </row>
@@ -17983,11 +18641,11 @@
         <v/>
       </c>
       <c r="L220" t="str">
+        <v/>
+      </c>
+      <c r="M220" t="str">
         <v>Manual</v>
       </c>
-      <c r="M220" t="str">
-        <v/>
-      </c>
       <c r="N220" t="str">
         <v/>
       </c>
@@ -18025,6 +18683,9 @@
         <v/>
       </c>
       <c r="Z220" t="str">
+        <v/>
+      </c>
+      <c r="AA220" t="str">
         <v/>
       </c>
     </row>
@@ -18063,11 +18724,11 @@
         <v/>
       </c>
       <c r="L221" t="str">
+        <v/>
+      </c>
+      <c r="M221" t="str">
         <v>Manual</v>
       </c>
-      <c r="M221" t="str">
-        <v/>
-      </c>
       <c r="N221" t="str">
         <v/>
       </c>
@@ -18105,6 +18766,9 @@
         <v/>
       </c>
       <c r="Z221" t="str">
+        <v/>
+      </c>
+      <c r="AA221" t="str">
         <v/>
       </c>
     </row>
@@ -18143,11 +18807,11 @@
         <v/>
       </c>
       <c r="L222" t="str">
+        <v/>
+      </c>
+      <c r="M222" t="str">
         <v>Manual</v>
       </c>
-      <c r="M222" t="str">
-        <v/>
-      </c>
       <c r="N222" t="str">
         <v/>
       </c>
@@ -18185,6 +18849,9 @@
         <v/>
       </c>
       <c r="Z222" t="str">
+        <v/>
+      </c>
+      <c r="AA222" t="str">
         <v/>
       </c>
     </row>
@@ -18223,11 +18890,11 @@
         <v/>
       </c>
       <c r="L223" t="str">
+        <v/>
+      </c>
+      <c r="M223" t="str">
         <v>Manual</v>
       </c>
-      <c r="M223" t="str">
-        <v/>
-      </c>
       <c r="N223" t="str">
         <v/>
       </c>
@@ -18265,6 +18932,9 @@
         <v/>
       </c>
       <c r="Z223" t="str">
+        <v/>
+      </c>
+      <c r="AA223" t="str">
         <v/>
       </c>
     </row>
@@ -18303,11 +18973,11 @@
         <v/>
       </c>
       <c r="L224" t="str">
+        <v/>
+      </c>
+      <c r="M224" t="str">
         <v>Manual</v>
       </c>
-      <c r="M224" t="str">
-        <v/>
-      </c>
       <c r="N224" t="str">
         <v/>
       </c>
@@ -18345,6 +19015,9 @@
         <v/>
       </c>
       <c r="Z224" t="str">
+        <v/>
+      </c>
+      <c r="AA224" t="str">
         <v/>
       </c>
     </row>
@@ -18383,11 +19056,11 @@
         <v/>
       </c>
       <c r="L225" t="str">
+        <v/>
+      </c>
+      <c r="M225" t="str">
         <v>Manual</v>
       </c>
-      <c r="M225" t="str">
-        <v/>
-      </c>
       <c r="N225" t="str">
         <v/>
       </c>
@@ -18425,6 +19098,9 @@
         <v/>
       </c>
       <c r="Z225" t="str">
+        <v/>
+      </c>
+      <c r="AA225" t="str">
         <v/>
       </c>
     </row>
@@ -18463,11 +19139,11 @@
         <v/>
       </c>
       <c r="L226" t="str">
+        <v/>
+      </c>
+      <c r="M226" t="str">
         <v>Manual</v>
       </c>
-      <c r="M226" t="str">
-        <v/>
-      </c>
       <c r="N226" t="str">
         <v/>
       </c>
@@ -18505,6 +19181,9 @@
         <v/>
       </c>
       <c r="Z226" t="str">
+        <v/>
+      </c>
+      <c r="AA226" t="str">
         <v/>
       </c>
     </row>
@@ -18543,11 +19222,11 @@
         <v/>
       </c>
       <c r="L227" t="str">
+        <v/>
+      </c>
+      <c r="M227" t="str">
         <v>Manual</v>
       </c>
-      <c r="M227" t="str">
-        <v/>
-      </c>
       <c r="N227" t="str">
         <v/>
       </c>
@@ -18585,6 +19264,9 @@
         <v/>
       </c>
       <c r="Z227" t="str">
+        <v/>
+      </c>
+      <c r="AA227" t="str">
         <v/>
       </c>
     </row>
@@ -18623,11 +19305,11 @@
         <v/>
       </c>
       <c r="L228" t="str">
+        <v/>
+      </c>
+      <c r="M228" t="str">
         <v>Manual</v>
       </c>
-      <c r="M228" t="str">
-        <v/>
-      </c>
       <c r="N228" t="str">
         <v/>
       </c>
@@ -18665,6 +19347,9 @@
         <v/>
       </c>
       <c r="Z228" t="str">
+        <v/>
+      </c>
+      <c r="AA228" t="str">
         <v/>
       </c>
     </row>
@@ -18703,11 +19388,11 @@
         <v/>
       </c>
       <c r="L229" t="str">
+        <v/>
+      </c>
+      <c r="M229" t="str">
         <v>Manual</v>
       </c>
-      <c r="M229" t="str">
-        <v/>
-      </c>
       <c r="N229" t="str">
         <v/>
       </c>
@@ -18745,6 +19430,9 @@
         <v/>
       </c>
       <c r="Z229" t="str">
+        <v/>
+      </c>
+      <c r="AA229" t="str">
         <v/>
       </c>
     </row>
@@ -18783,11 +19471,11 @@
         <v/>
       </c>
       <c r="L230" t="str">
+        <v/>
+      </c>
+      <c r="M230" t="str">
         <v>Manual</v>
       </c>
-      <c r="M230" t="str">
-        <v/>
-      </c>
       <c r="N230" t="str">
         <v/>
       </c>
@@ -18825,6 +19513,9 @@
         <v/>
       </c>
       <c r="Z230" t="str">
+        <v/>
+      </c>
+      <c r="AA230" t="str">
         <v/>
       </c>
     </row>
@@ -18863,11 +19554,11 @@
         <v/>
       </c>
       <c r="L231" t="str">
+        <v/>
+      </c>
+      <c r="M231" t="str">
         <v>Manual</v>
       </c>
-      <c r="M231" t="str">
-        <v/>
-      </c>
       <c r="N231" t="str">
         <v/>
       </c>
@@ -18905,6 +19596,9 @@
         <v/>
       </c>
       <c r="Z231" t="str">
+        <v/>
+      </c>
+      <c r="AA231" t="str">
         <v/>
       </c>
     </row>
@@ -18943,11 +19637,11 @@
         <v/>
       </c>
       <c r="L232" t="str">
+        <v/>
+      </c>
+      <c r="M232" t="str">
         <v>Manual</v>
       </c>
-      <c r="M232" t="str">
-        <v/>
-      </c>
       <c r="N232" t="str">
         <v/>
       </c>
@@ -18985,6 +19679,9 @@
         <v/>
       </c>
       <c r="Z232" t="str">
+        <v/>
+      </c>
+      <c r="AA232" t="str">
         <v/>
       </c>
     </row>
@@ -19023,11 +19720,11 @@
         <v/>
       </c>
       <c r="L233" t="str">
+        <v/>
+      </c>
+      <c r="M233" t="str">
         <v>Manual</v>
       </c>
-      <c r="M233" t="str">
-        <v/>
-      </c>
       <c r="N233" t="str">
         <v/>
       </c>
@@ -19065,6 +19762,9 @@
         <v/>
       </c>
       <c r="Z233" t="str">
+        <v/>
+      </c>
+      <c r="AA233" t="str">
         <v/>
       </c>
     </row>
@@ -19103,11 +19803,11 @@
         <v/>
       </c>
       <c r="L234" t="str">
+        <v/>
+      </c>
+      <c r="M234" t="str">
         <v>Manual</v>
       </c>
-      <c r="M234" t="str">
-        <v/>
-      </c>
       <c r="N234" t="str">
         <v/>
       </c>
@@ -19145,6 +19845,9 @@
         <v/>
       </c>
       <c r="Z234" t="str">
+        <v/>
+      </c>
+      <c r="AA234" t="str">
         <v/>
       </c>
     </row>
@@ -19183,11 +19886,11 @@
         <v/>
       </c>
       <c r="L235" t="str">
+        <v/>
+      </c>
+      <c r="M235" t="str">
         <v>Manual</v>
       </c>
-      <c r="M235" t="str">
-        <v/>
-      </c>
       <c r="N235" t="str">
         <v/>
       </c>
@@ -19225,6 +19928,9 @@
         <v/>
       </c>
       <c r="Z235" t="str">
+        <v/>
+      </c>
+      <c r="AA235" t="str">
         <v/>
       </c>
     </row>
@@ -19263,11 +19969,11 @@
         <v/>
       </c>
       <c r="L236" t="str">
+        <v/>
+      </c>
+      <c r="M236" t="str">
         <v>Manual</v>
       </c>
-      <c r="M236" t="str">
-        <v/>
-      </c>
       <c r="N236" t="str">
         <v/>
       </c>
@@ -19305,6 +20011,9 @@
         <v/>
       </c>
       <c r="Z236" t="str">
+        <v/>
+      </c>
+      <c r="AA236" t="str">
         <v/>
       </c>
     </row>
@@ -19343,11 +20052,11 @@
         <v/>
       </c>
       <c r="L237" t="str">
+        <v/>
+      </c>
+      <c r="M237" t="str">
         <v>Manual</v>
       </c>
-      <c r="M237" t="str">
-        <v/>
-      </c>
       <c r="N237" t="str">
         <v/>
       </c>
@@ -19385,6 +20094,9 @@
         <v/>
       </c>
       <c r="Z237" t="str">
+        <v/>
+      </c>
+      <c r="AA237" t="str">
         <v/>
       </c>
     </row>
@@ -19423,11 +20135,11 @@
         <v/>
       </c>
       <c r="L238" t="str">
+        <v/>
+      </c>
+      <c r="M238" t="str">
         <v>Manual</v>
       </c>
-      <c r="M238" t="str">
-        <v/>
-      </c>
       <c r="N238" t="str">
         <v/>
       </c>
@@ -19465,6 +20177,9 @@
         <v/>
       </c>
       <c r="Z238" t="str">
+        <v/>
+      </c>
+      <c r="AA238" t="str">
         <v/>
       </c>
     </row>
@@ -19503,11 +20218,11 @@
         <v/>
       </c>
       <c r="L239" t="str">
+        <v/>
+      </c>
+      <c r="M239" t="str">
         <v>Manual</v>
       </c>
-      <c r="M239" t="str">
-        <v/>
-      </c>
       <c r="N239" t="str">
         <v/>
       </c>
@@ -19545,6 +20260,9 @@
         <v/>
       </c>
       <c r="Z239" t="str">
+        <v/>
+      </c>
+      <c r="AA239" t="str">
         <v/>
       </c>
     </row>
@@ -19583,11 +20301,11 @@
         <v/>
       </c>
       <c r="L240" t="str">
+        <v/>
+      </c>
+      <c r="M240" t="str">
         <v>Manual</v>
       </c>
-      <c r="M240" t="str">
-        <v/>
-      </c>
       <c r="N240" t="str">
         <v/>
       </c>
@@ -19625,6 +20343,9 @@
         <v/>
       </c>
       <c r="Z240" t="str">
+        <v/>
+      </c>
+      <c r="AA240" t="str">
         <v/>
       </c>
     </row>
@@ -19663,11 +20384,11 @@
         <v/>
       </c>
       <c r="L241" t="str">
+        <v/>
+      </c>
+      <c r="M241" t="str">
         <v>Manual</v>
       </c>
-      <c r="M241" t="str">
-        <v/>
-      </c>
       <c r="N241" t="str">
         <v/>
       </c>
@@ -19705,6 +20426,9 @@
         <v/>
       </c>
       <c r="Z241" t="str">
+        <v/>
+      </c>
+      <c r="AA241" t="str">
         <v/>
       </c>
     </row>
@@ -19743,11 +20467,11 @@
         <v/>
       </c>
       <c r="L242" t="str">
+        <v/>
+      </c>
+      <c r="M242" t="str">
         <v>Manual</v>
       </c>
-      <c r="M242" t="str">
-        <v/>
-      </c>
       <c r="N242" t="str">
         <v/>
       </c>
@@ -19785,6 +20509,9 @@
         <v/>
       </c>
       <c r="Z242" t="str">
+        <v/>
+      </c>
+      <c r="AA242" t="str">
         <v/>
       </c>
     </row>
@@ -19823,11 +20550,11 @@
         <v/>
       </c>
       <c r="L243" t="str">
+        <v/>
+      </c>
+      <c r="M243" t="str">
         <v>Manual</v>
       </c>
-      <c r="M243" t="str">
-        <v/>
-      </c>
       <c r="N243" t="str">
         <v/>
       </c>
@@ -19865,6 +20592,9 @@
         <v/>
       </c>
       <c r="Z243" t="str">
+        <v/>
+      </c>
+      <c r="AA243" t="str">
         <v/>
       </c>
     </row>
@@ -19903,11 +20633,11 @@
         <v/>
       </c>
       <c r="L244" t="str">
+        <v/>
+      </c>
+      <c r="M244" t="str">
         <v>Manual</v>
       </c>
-      <c r="M244" t="str">
-        <v/>
-      </c>
       <c r="N244" t="str">
         <v/>
       </c>
@@ -19945,6 +20675,9 @@
         <v/>
       </c>
       <c r="Z244" t="str">
+        <v/>
+      </c>
+      <c r="AA244" t="str">
         <v/>
       </c>
     </row>
@@ -19983,11 +20716,11 @@
         <v/>
       </c>
       <c r="L245" t="str">
+        <v/>
+      </c>
+      <c r="M245" t="str">
         <v>Manual</v>
       </c>
-      <c r="M245" t="str">
-        <v/>
-      </c>
       <c r="N245" t="str">
         <v/>
       </c>
@@ -20025,6 +20758,9 @@
         <v/>
       </c>
       <c r="Z245" t="str">
+        <v/>
+      </c>
+      <c r="AA245" t="str">
         <v/>
       </c>
     </row>
@@ -20063,11 +20799,11 @@
         <v/>
       </c>
       <c r="L246" t="str">
+        <v/>
+      </c>
+      <c r="M246" t="str">
         <v>Manual</v>
       </c>
-      <c r="M246" t="str">
-        <v/>
-      </c>
       <c r="N246" t="str">
         <v/>
       </c>
@@ -20105,6 +20841,9 @@
         <v/>
       </c>
       <c r="Z246" t="str">
+        <v/>
+      </c>
+      <c r="AA246" t="str">
         <v/>
       </c>
     </row>
@@ -20143,11 +20882,11 @@
         <v/>
       </c>
       <c r="L247" t="str">
+        <v/>
+      </c>
+      <c r="M247" t="str">
         <v>Manual</v>
       </c>
-      <c r="M247" t="str">
-        <v/>
-      </c>
       <c r="N247" t="str">
         <v/>
       </c>
@@ -20185,6 +20924,9 @@
         <v/>
       </c>
       <c r="Z247" t="str">
+        <v/>
+      </c>
+      <c r="AA247" t="str">
         <v/>
       </c>
     </row>
@@ -20223,11 +20965,11 @@
         <v/>
       </c>
       <c r="L248" t="str">
+        <v/>
+      </c>
+      <c r="M248" t="str">
         <v>Manual</v>
       </c>
-      <c r="M248" t="str">
-        <v/>
-      </c>
       <c r="N248" t="str">
         <v/>
       </c>
@@ -20265,6 +21007,9 @@
         <v/>
       </c>
       <c r="Z248" t="str">
+        <v/>
+      </c>
+      <c r="AA248" t="str">
         <v/>
       </c>
     </row>
@@ -20303,11 +21048,11 @@
         <v/>
       </c>
       <c r="L249" t="str">
+        <v/>
+      </c>
+      <c r="M249" t="str">
         <v>Manual</v>
       </c>
-      <c r="M249" t="str">
-        <v/>
-      </c>
       <c r="N249" t="str">
         <v/>
       </c>
@@ -20345,6 +21090,9 @@
         <v/>
       </c>
       <c r="Z249" t="str">
+        <v/>
+      </c>
+      <c r="AA249" t="str">
         <v/>
       </c>
     </row>
@@ -20383,11 +21131,11 @@
         <v/>
       </c>
       <c r="L250" t="str">
+        <v/>
+      </c>
+      <c r="M250" t="str">
         <v>Manual</v>
       </c>
-      <c r="M250" t="str">
-        <v/>
-      </c>
       <c r="N250" t="str">
         <v/>
       </c>
@@ -20425,6 +21173,9 @@
         <v/>
       </c>
       <c r="Z250" t="str">
+        <v/>
+      </c>
+      <c r="AA250" t="str">
         <v/>
       </c>
     </row>
@@ -20463,11 +21214,11 @@
         <v/>
       </c>
       <c r="L251" t="str">
+        <v/>
+      </c>
+      <c r="M251" t="str">
         <v>Manual</v>
       </c>
-      <c r="M251" t="str">
-        <v/>
-      </c>
       <c r="N251" t="str">
         <v/>
       </c>
@@ -20505,6 +21256,9 @@
         <v/>
       </c>
       <c r="Z251" t="str">
+        <v/>
+      </c>
+      <c r="AA251" t="str">
         <v/>
       </c>
     </row>
@@ -20543,11 +21297,11 @@
         <v/>
       </c>
       <c r="L252" t="str">
+        <v/>
+      </c>
+      <c r="M252" t="str">
         <v>Manual</v>
       </c>
-      <c r="M252" t="str">
-        <v/>
-      </c>
       <c r="N252" t="str">
         <v/>
       </c>
@@ -20585,6 +21339,9 @@
         <v/>
       </c>
       <c r="Z252" t="str">
+        <v/>
+      </c>
+      <c r="AA252" t="str">
         <v/>
       </c>
     </row>
@@ -20623,11 +21380,11 @@
         <v/>
       </c>
       <c r="L253" t="str">
+        <v/>
+      </c>
+      <c r="M253" t="str">
         <v>Manual</v>
       </c>
-      <c r="M253" t="str">
-        <v/>
-      </c>
       <c r="N253" t="str">
         <v/>
       </c>
@@ -20665,6 +21422,9 @@
         <v/>
       </c>
       <c r="Z253" t="str">
+        <v/>
+      </c>
+      <c r="AA253" t="str">
         <v/>
       </c>
     </row>
@@ -20703,11 +21463,11 @@
         <v/>
       </c>
       <c r="L254" t="str">
+        <v/>
+      </c>
+      <c r="M254" t="str">
         <v>Manual</v>
       </c>
-      <c r="M254" t="str">
-        <v/>
-      </c>
       <c r="N254" t="str">
         <v/>
       </c>
@@ -20745,6 +21505,9 @@
         <v/>
       </c>
       <c r="Z254" t="str">
+        <v/>
+      </c>
+      <c r="AA254" t="str">
         <v/>
       </c>
     </row>
@@ -20783,11 +21546,11 @@
         <v/>
       </c>
       <c r="L255" t="str">
+        <v/>
+      </c>
+      <c r="M255" t="str">
         <v>Manual</v>
       </c>
-      <c r="M255" t="str">
-        <v/>
-      </c>
       <c r="N255" t="str">
         <v/>
       </c>
@@ -20825,6 +21588,9 @@
         <v/>
       </c>
       <c r="Z255" t="str">
+        <v/>
+      </c>
+      <c r="AA255" t="str">
         <v/>
       </c>
     </row>
@@ -20863,11 +21629,11 @@
         <v/>
       </c>
       <c r="L256" t="str">
+        <v/>
+      </c>
+      <c r="M256" t="str">
         <v>Manual</v>
       </c>
-      <c r="M256" t="str">
-        <v/>
-      </c>
       <c r="N256" t="str">
         <v/>
       </c>
@@ -20905,6 +21671,9 @@
         <v/>
       </c>
       <c r="Z256" t="str">
+        <v/>
+      </c>
+      <c r="AA256" t="str">
         <v/>
       </c>
     </row>
@@ -20943,11 +21712,11 @@
         <v/>
       </c>
       <c r="L257" t="str">
+        <v/>
+      </c>
+      <c r="M257" t="str">
         <v>Manual</v>
       </c>
-      <c r="M257" t="str">
-        <v/>
-      </c>
       <c r="N257" t="str">
         <v/>
       </c>
@@ -20985,12 +21754,15 @@
         <v/>
       </c>
       <c r="Z257" t="str">
+        <v/>
+      </c>
+      <c r="AA257" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z257"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA257"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -21016,7 +21788,7 @@
         <v>UK</v>
       </c>
       <c r="B2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -21032,7 +21804,7 @@
         <v>Unrecorded</v>
       </c>
       <c r="B4">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
@@ -21112,7 +21884,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B15">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
@@ -21128,7 +21900,7 @@
         <v>UK work days (max 30)</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -21144,7 +21916,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA257"/>
+  <dimension ref="A1:AA203"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -16735,7 +16735,7 @@
         <v>Yes</v>
       </c>
       <c r="M197" t="str">
-        <v>GPS + Manual</v>
+        <v>Booking</v>
       </c>
       <c r="N197" t="str">
         <v/>
@@ -16768,16 +16768,16 @@
         <v/>
       </c>
       <c r="X197" t="str">
-        <v/>
+        <v>email: Fw: Your booking confirmation Z9VFXQ</v>
       </c>
       <c r="Y197" t="str">
         <v/>
       </c>
       <c r="Z197" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA197" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
     </row>
     <row r="198">
@@ -16818,7 +16818,7 @@
         <v>Yes</v>
       </c>
       <c r="M198" t="str">
-        <v>GPS + Manual</v>
+        <v>Manual</v>
       </c>
       <c r="N198" t="str">
         <v/>
@@ -16860,18 +16860,18 @@
         <v/>
       </c>
       <c r="AA198" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-28</v>
       </c>
       <c r="B199" t="str">
-        <v>Thursday</v>
+        <v>Saturday</v>
       </c>
       <c r="C199" t="str">
-        <v>417 Meadow Lane</v>
+        <v>Oxford</v>
       </c>
       <c r="D199" t="str">
         <v>Oxford</v>
@@ -16885,23 +16885,23 @@
       <c r="G199" t="str">
         <v/>
       </c>
-      <c r="H199" t="str">
-        <v/>
-      </c>
-      <c r="I199" t="str">
-        <v/>
+      <c r="H199">
+        <v>51.7329666</v>
+      </c>
+      <c r="I199">
+        <v>-1.2372956</v>
       </c>
       <c r="J199" t="str">
-        <v/>
+        <v>2026-02-28 22:59:01 GMT</v>
       </c>
       <c r="K199" t="str">
-        <v/>
+        <v>app</v>
       </c>
       <c r="L199" t="str">
         <v/>
       </c>
       <c r="M199" t="str">
-        <v>Manual</v>
+        <v>GPS + Manual</v>
       </c>
       <c r="N199" t="str">
         <v/>
@@ -16943,18 +16943,18 @@
         <v/>
       </c>
       <c r="AA199" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>2026-02-27</v>
+        <v>2026-03-01</v>
       </c>
       <c r="B200" t="str">
-        <v>Friday</v>
+        <v>Sunday</v>
       </c>
       <c r="C200" t="str">
-        <v>417 Meadow Lane</v>
+        <v>Oxford</v>
       </c>
       <c r="D200" t="str">
         <v>Oxford</v>
@@ -16968,17 +16968,17 @@
       <c r="G200" t="str">
         <v/>
       </c>
-      <c r="H200" t="str">
-        <v/>
-      </c>
-      <c r="I200" t="str">
-        <v/>
+      <c r="H200">
+        <v>51.73297</v>
+      </c>
+      <c r="I200">
+        <v>-1.2373507</v>
       </c>
       <c r="J200" t="str">
-        <v/>
+        <v>2026-03-01 07:28:23 GMT</v>
       </c>
       <c r="K200" t="str">
-        <v/>
+        <v>12am</v>
       </c>
       <c r="L200" t="str">
         <v/>
@@ -16987,16 +16987,16 @@
         <v>Manual</v>
       </c>
       <c r="N200" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="O200" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="P200" t="str">
-        <v/>
+        <v>51.73298, -1.23728</v>
       </c>
       <c r="Q200" t="str">
-        <v/>
+        <v>2026-03-01 22:56:17 GMT</v>
       </c>
       <c r="R200" t="str">
         <v/>
@@ -17031,31 +17031,31 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>2026-02-28</v>
+        <v>2026-03-02</v>
       </c>
       <c r="B201" t="str">
-        <v>Saturday</v>
+        <v>Monday</v>
       </c>
       <c r="C201" t="str">
-        <v>417 Meadow Lane</v>
+        <v>Cernobbio</v>
       </c>
       <c r="D201" t="str">
-        <v>Oxford</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E201" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F201" t="str">
-        <v/>
+        <v>BA574</v>
       </c>
       <c r="G201" t="str">
-        <v/>
-      </c>
-      <c r="H201" t="str">
-        <v/>
-      </c>
-      <c r="I201" t="str">
-        <v/>
+        <v>Bracket mismatch: evening=Cernobbio,Italy vs morning=Oxford,UK</v>
+      </c>
+      <c r="H201">
+        <v>45.4786567</v>
+      </c>
+      <c r="I201">
+        <v>9.1993005</v>
       </c>
       <c r="J201" t="str">
         <v/>
@@ -17067,7 +17067,7 @@
         <v/>
       </c>
       <c r="M201" t="str">
-        <v>Manual</v>
+        <v>GPS</v>
       </c>
       <c r="N201" t="str">
         <v/>
@@ -17103,7 +17103,7 @@
         <v/>
       </c>
       <c r="Y201" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Z201" t="str">
         <v/>
@@ -17114,19 +17114,19 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="B202" t="str">
-        <v>Sunday</v>
+        <v>Tuesday</v>
       </c>
       <c r="C202" t="str">
-        <v>417 Meadow Lane</v>
+        <v>Cernobbio</v>
       </c>
       <c r="D202" t="str">
-        <v>Oxford</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E202" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F202" t="str">
         <v/>
@@ -17134,11 +17134,11 @@
       <c r="G202" t="str">
         <v/>
       </c>
-      <c r="H202" t="str">
-        <v/>
-      </c>
-      <c r="I202" t="str">
-        <v/>
+      <c r="H202">
+        <v>45.4786558</v>
+      </c>
+      <c r="I202">
+        <v>9.1993042</v>
       </c>
       <c r="J202" t="str">
         <v/>
@@ -17150,7 +17150,7 @@
         <v/>
       </c>
       <c r="M202" t="str">
-        <v>Manual</v>
+        <v>GPS</v>
       </c>
       <c r="N202" t="str">
         <v/>
@@ -17186,7 +17186,7 @@
         <v/>
       </c>
       <c r="Y202" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Z202" t="str">
         <v/>
@@ -17197,22 +17197,22 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-04</v>
       </c>
       <c r="B203" t="str">
-        <v>Monday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C203" t="str">
-        <v>417 Meadow Lane</v>
+        <v/>
       </c>
       <c r="D203" t="str">
-        <v>Oxford</v>
+        <v>Milan</v>
       </c>
       <c r="E203" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F203" t="str">
-        <v/>
+        <v>BA579</v>
       </c>
       <c r="G203" t="str">
         <v/>
@@ -17233,7 +17233,7 @@
         <v/>
       </c>
       <c r="M203" t="str">
-        <v>Manual</v>
+        <v>Booking</v>
       </c>
       <c r="N203" t="str">
         <v/>
@@ -17266,4503 +17266,21 @@
         <v/>
       </c>
       <c r="X203" t="str">
-        <v/>
+        <v>calendar: Flight BA579: LIN - LHR, departs 15:30</v>
       </c>
       <c r="Y203" t="str">
         <v/>
       </c>
       <c r="Z203" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA203" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="B204" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="C204" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D204" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E204" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F204" t="str">
-        <v/>
-      </c>
-      <c r="G204" t="str">
-        <v/>
-      </c>
-      <c r="H204" t="str">
-        <v/>
-      </c>
-      <c r="I204" t="str">
-        <v/>
-      </c>
-      <c r="J204" t="str">
-        <v/>
-      </c>
-      <c r="K204" t="str">
-        <v/>
-      </c>
-      <c r="L204" t="str">
-        <v/>
-      </c>
-      <c r="M204" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N204" t="str">
-        <v/>
-      </c>
-      <c r="O204" t="str">
-        <v/>
-      </c>
-      <c r="P204" t="str">
-        <v/>
-      </c>
-      <c r="Q204" t="str">
-        <v/>
-      </c>
-      <c r="R204" t="str">
-        <v/>
-      </c>
-      <c r="S204" t="str">
-        <v/>
-      </c>
-      <c r="T204" t="str">
-        <v/>
-      </c>
-      <c r="U204" t="str">
-        <v/>
-      </c>
-      <c r="V204" t="str">
-        <v/>
-      </c>
-      <c r="W204" t="str">
-        <v/>
-      </c>
-      <c r="X204" t="str">
-        <v/>
-      </c>
-      <c r="Y204" t="str">
-        <v/>
-      </c>
-      <c r="Z204" t="str">
-        <v/>
-      </c>
-      <c r="AA204" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="B205" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="C205" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D205" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E205" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F205" t="str">
-        <v/>
-      </c>
-      <c r="G205" t="str">
-        <v/>
-      </c>
-      <c r="H205" t="str">
-        <v/>
-      </c>
-      <c r="I205" t="str">
-        <v/>
-      </c>
-      <c r="J205" t="str">
-        <v/>
-      </c>
-      <c r="K205" t="str">
-        <v/>
-      </c>
-      <c r="L205" t="str">
-        <v/>
-      </c>
-      <c r="M205" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N205" t="str">
-        <v/>
-      </c>
-      <c r="O205" t="str">
-        <v/>
-      </c>
-      <c r="P205" t="str">
-        <v/>
-      </c>
-      <c r="Q205" t="str">
-        <v/>
-      </c>
-      <c r="R205" t="str">
-        <v/>
-      </c>
-      <c r="S205" t="str">
-        <v/>
-      </c>
-      <c r="T205" t="str">
-        <v/>
-      </c>
-      <c r="U205" t="str">
-        <v/>
-      </c>
-      <c r="V205" t="str">
-        <v/>
-      </c>
-      <c r="W205" t="str">
-        <v/>
-      </c>
-      <c r="X205" t="str">
-        <v/>
-      </c>
-      <c r="Y205" t="str">
-        <v/>
-      </c>
-      <c r="Z205" t="str">
-        <v/>
-      </c>
-      <c r="AA205" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>2026-03-05</v>
-      </c>
-      <c r="B206" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="C206" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D206" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E206" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F206" t="str">
-        <v/>
-      </c>
-      <c r="G206" t="str">
-        <v/>
-      </c>
-      <c r="H206" t="str">
-        <v/>
-      </c>
-      <c r="I206" t="str">
-        <v/>
-      </c>
-      <c r="J206" t="str">
-        <v/>
-      </c>
-      <c r="K206" t="str">
-        <v/>
-      </c>
-      <c r="L206" t="str">
-        <v/>
-      </c>
-      <c r="M206" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N206" t="str">
-        <v/>
-      </c>
-      <c r="O206" t="str">
-        <v/>
-      </c>
-      <c r="P206" t="str">
-        <v/>
-      </c>
-      <c r="Q206" t="str">
-        <v/>
-      </c>
-      <c r="R206" t="str">
-        <v/>
-      </c>
-      <c r="S206" t="str">
-        <v/>
-      </c>
-      <c r="T206" t="str">
-        <v/>
-      </c>
-      <c r="U206" t="str">
-        <v/>
-      </c>
-      <c r="V206" t="str">
-        <v/>
-      </c>
-      <c r="W206" t="str">
-        <v/>
-      </c>
-      <c r="X206" t="str">
-        <v/>
-      </c>
-      <c r="Y206" t="str">
-        <v/>
-      </c>
-      <c r="Z206" t="str">
-        <v/>
-      </c>
-      <c r="AA206" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>2026-03-07</v>
-      </c>
-      <c r="B207" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="C207" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D207" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E207" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F207" t="str">
-        <v/>
-      </c>
-      <c r="G207" t="str">
-        <v/>
-      </c>
-      <c r="H207" t="str">
-        <v/>
-      </c>
-      <c r="I207" t="str">
-        <v/>
-      </c>
-      <c r="J207" t="str">
-        <v/>
-      </c>
-      <c r="K207" t="str">
-        <v/>
-      </c>
-      <c r="L207" t="str">
-        <v/>
-      </c>
-      <c r="M207" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N207" t="str">
-        <v/>
-      </c>
-      <c r="O207" t="str">
-        <v/>
-      </c>
-      <c r="P207" t="str">
-        <v/>
-      </c>
-      <c r="Q207" t="str">
-        <v/>
-      </c>
-      <c r="R207" t="str">
-        <v/>
-      </c>
-      <c r="S207" t="str">
-        <v/>
-      </c>
-      <c r="T207" t="str">
-        <v/>
-      </c>
-      <c r="U207" t="str">
-        <v/>
-      </c>
-      <c r="V207" t="str">
-        <v/>
-      </c>
-      <c r="W207" t="str">
-        <v/>
-      </c>
-      <c r="X207" t="str">
-        <v/>
-      </c>
-      <c r="Y207" t="str">
-        <v/>
-      </c>
-      <c r="Z207" t="str">
-        <v/>
-      </c>
-      <c r="AA207" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="B208" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="C208" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D208" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E208" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F208" t="str">
-        <v/>
-      </c>
-      <c r="G208" t="str">
-        <v/>
-      </c>
-      <c r="H208" t="str">
-        <v/>
-      </c>
-      <c r="I208" t="str">
-        <v/>
-      </c>
-      <c r="J208" t="str">
-        <v/>
-      </c>
-      <c r="K208" t="str">
-        <v/>
-      </c>
-      <c r="L208" t="str">
-        <v/>
-      </c>
-      <c r="M208" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N208" t="str">
-        <v/>
-      </c>
-      <c r="O208" t="str">
-        <v/>
-      </c>
-      <c r="P208" t="str">
-        <v/>
-      </c>
-      <c r="Q208" t="str">
-        <v/>
-      </c>
-      <c r="R208" t="str">
-        <v/>
-      </c>
-      <c r="S208" t="str">
-        <v/>
-      </c>
-      <c r="T208" t="str">
-        <v/>
-      </c>
-      <c r="U208" t="str">
-        <v/>
-      </c>
-      <c r="V208" t="str">
-        <v/>
-      </c>
-      <c r="W208" t="str">
-        <v/>
-      </c>
-      <c r="X208" t="str">
-        <v/>
-      </c>
-      <c r="Y208" t="str">
-        <v/>
-      </c>
-      <c r="Z208" t="str">
-        <v/>
-      </c>
-      <c r="AA208" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="B209" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="C209" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D209" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E209" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F209" t="str">
-        <v/>
-      </c>
-      <c r="G209" t="str">
-        <v/>
-      </c>
-      <c r="H209" t="str">
-        <v/>
-      </c>
-      <c r="I209" t="str">
-        <v/>
-      </c>
-      <c r="J209" t="str">
-        <v/>
-      </c>
-      <c r="K209" t="str">
-        <v/>
-      </c>
-      <c r="L209" t="str">
-        <v/>
-      </c>
-      <c r="M209" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N209" t="str">
-        <v/>
-      </c>
-      <c r="O209" t="str">
-        <v/>
-      </c>
-      <c r="P209" t="str">
-        <v/>
-      </c>
-      <c r="Q209" t="str">
-        <v/>
-      </c>
-      <c r="R209" t="str">
-        <v/>
-      </c>
-      <c r="S209" t="str">
-        <v/>
-      </c>
-      <c r="T209" t="str">
-        <v/>
-      </c>
-      <c r="U209" t="str">
-        <v/>
-      </c>
-      <c r="V209" t="str">
-        <v/>
-      </c>
-      <c r="W209" t="str">
-        <v/>
-      </c>
-      <c r="X209" t="str">
-        <v/>
-      </c>
-      <c r="Y209" t="str">
-        <v/>
-      </c>
-      <c r="Z209" t="str">
-        <v/>
-      </c>
-      <c r="AA209" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="B210" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="C210" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D210" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E210" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F210" t="str">
-        <v/>
-      </c>
-      <c r="G210" t="str">
-        <v/>
-      </c>
-      <c r="H210" t="str">
-        <v/>
-      </c>
-      <c r="I210" t="str">
-        <v/>
-      </c>
-      <c r="J210" t="str">
-        <v/>
-      </c>
-      <c r="K210" t="str">
-        <v/>
-      </c>
-      <c r="L210" t="str">
-        <v/>
-      </c>
-      <c r="M210" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N210" t="str">
-        <v/>
-      </c>
-      <c r="O210" t="str">
-        <v/>
-      </c>
-      <c r="P210" t="str">
-        <v/>
-      </c>
-      <c r="Q210" t="str">
-        <v/>
-      </c>
-      <c r="R210" t="str">
-        <v/>
-      </c>
-      <c r="S210" t="str">
-        <v/>
-      </c>
-      <c r="T210" t="str">
-        <v/>
-      </c>
-      <c r="U210" t="str">
-        <v/>
-      </c>
-      <c r="V210" t="str">
-        <v/>
-      </c>
-      <c r="W210" t="str">
-        <v/>
-      </c>
-      <c r="X210" t="str">
-        <v/>
-      </c>
-      <c r="Y210" t="str">
-        <v/>
-      </c>
-      <c r="Z210" t="str">
-        <v/>
-      </c>
-      <c r="AA210" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="B211" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="C211" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D211" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E211" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F211" t="str">
-        <v/>
-      </c>
-      <c r="G211" t="str">
-        <v/>
-      </c>
-      <c r="H211" t="str">
-        <v/>
-      </c>
-      <c r="I211" t="str">
-        <v/>
-      </c>
-      <c r="J211" t="str">
-        <v/>
-      </c>
-      <c r="K211" t="str">
-        <v/>
-      </c>
-      <c r="L211" t="str">
-        <v/>
-      </c>
-      <c r="M211" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N211" t="str">
-        <v/>
-      </c>
-      <c r="O211" t="str">
-        <v/>
-      </c>
-      <c r="P211" t="str">
-        <v/>
-      </c>
-      <c r="Q211" t="str">
-        <v/>
-      </c>
-      <c r="R211" t="str">
-        <v/>
-      </c>
-      <c r="S211" t="str">
-        <v/>
-      </c>
-      <c r="T211" t="str">
-        <v/>
-      </c>
-      <c r="U211" t="str">
-        <v/>
-      </c>
-      <c r="V211" t="str">
-        <v/>
-      </c>
-      <c r="W211" t="str">
-        <v/>
-      </c>
-      <c r="X211" t="str">
-        <v/>
-      </c>
-      <c r="Y211" t="str">
-        <v/>
-      </c>
-      <c r="Z211" t="str">
-        <v/>
-      </c>
-      <c r="AA211" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="B212" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="C212" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D212" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E212" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F212" t="str">
-        <v/>
-      </c>
-      <c r="G212" t="str">
-        <v/>
-      </c>
-      <c r="H212" t="str">
-        <v/>
-      </c>
-      <c r="I212" t="str">
-        <v/>
-      </c>
-      <c r="J212" t="str">
-        <v/>
-      </c>
-      <c r="K212" t="str">
-        <v/>
-      </c>
-      <c r="L212" t="str">
-        <v/>
-      </c>
-      <c r="M212" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N212" t="str">
-        <v/>
-      </c>
-      <c r="O212" t="str">
-        <v/>
-      </c>
-      <c r="P212" t="str">
-        <v/>
-      </c>
-      <c r="Q212" t="str">
-        <v/>
-      </c>
-      <c r="R212" t="str">
-        <v/>
-      </c>
-      <c r="S212" t="str">
-        <v/>
-      </c>
-      <c r="T212" t="str">
-        <v/>
-      </c>
-      <c r="U212" t="str">
-        <v/>
-      </c>
-      <c r="V212" t="str">
-        <v/>
-      </c>
-      <c r="W212" t="str">
-        <v/>
-      </c>
-      <c r="X212" t="str">
-        <v/>
-      </c>
-      <c r="Y212" t="str">
-        <v/>
-      </c>
-      <c r="Z212" t="str">
-        <v/>
-      </c>
-      <c r="AA212" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>2026-03-13</v>
-      </c>
-      <c r="B213" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="C213" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D213" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E213" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F213" t="str">
-        <v/>
-      </c>
-      <c r="G213" t="str">
-        <v/>
-      </c>
-      <c r="H213" t="str">
-        <v/>
-      </c>
-      <c r="I213" t="str">
-        <v/>
-      </c>
-      <c r="J213" t="str">
-        <v/>
-      </c>
-      <c r="K213" t="str">
-        <v/>
-      </c>
-      <c r="L213" t="str">
-        <v/>
-      </c>
-      <c r="M213" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N213" t="str">
-        <v/>
-      </c>
-      <c r="O213" t="str">
-        <v/>
-      </c>
-      <c r="P213" t="str">
-        <v/>
-      </c>
-      <c r="Q213" t="str">
-        <v/>
-      </c>
-      <c r="R213" t="str">
-        <v/>
-      </c>
-      <c r="S213" t="str">
-        <v/>
-      </c>
-      <c r="T213" t="str">
-        <v/>
-      </c>
-      <c r="U213" t="str">
-        <v/>
-      </c>
-      <c r="V213" t="str">
-        <v/>
-      </c>
-      <c r="W213" t="str">
-        <v/>
-      </c>
-      <c r="X213" t="str">
-        <v/>
-      </c>
-      <c r="Y213" t="str">
-        <v/>
-      </c>
-      <c r="Z213" t="str">
-        <v/>
-      </c>
-      <c r="AA213" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>2026-03-14</v>
-      </c>
-      <c r="B214" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="C214" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D214" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E214" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F214" t="str">
-        <v/>
-      </c>
-      <c r="G214" t="str">
-        <v/>
-      </c>
-      <c r="H214" t="str">
-        <v/>
-      </c>
-      <c r="I214" t="str">
-        <v/>
-      </c>
-      <c r="J214" t="str">
-        <v/>
-      </c>
-      <c r="K214" t="str">
-        <v/>
-      </c>
-      <c r="L214" t="str">
-        <v/>
-      </c>
-      <c r="M214" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N214" t="str">
-        <v/>
-      </c>
-      <c r="O214" t="str">
-        <v/>
-      </c>
-      <c r="P214" t="str">
-        <v/>
-      </c>
-      <c r="Q214" t="str">
-        <v/>
-      </c>
-      <c r="R214" t="str">
-        <v/>
-      </c>
-      <c r="S214" t="str">
-        <v/>
-      </c>
-      <c r="T214" t="str">
-        <v/>
-      </c>
-      <c r="U214" t="str">
-        <v/>
-      </c>
-      <c r="V214" t="str">
-        <v/>
-      </c>
-      <c r="W214" t="str">
-        <v/>
-      </c>
-      <c r="X214" t="str">
-        <v/>
-      </c>
-      <c r="Y214" t="str">
-        <v/>
-      </c>
-      <c r="Z214" t="str">
-        <v/>
-      </c>
-      <c r="AA214" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="B215" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="C215" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D215" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E215" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F215" t="str">
-        <v/>
-      </c>
-      <c r="G215" t="str">
-        <v/>
-      </c>
-      <c r="H215" t="str">
-        <v/>
-      </c>
-      <c r="I215" t="str">
-        <v/>
-      </c>
-      <c r="J215" t="str">
-        <v/>
-      </c>
-      <c r="K215" t="str">
-        <v/>
-      </c>
-      <c r="L215" t="str">
-        <v/>
-      </c>
-      <c r="M215" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N215" t="str">
-        <v/>
-      </c>
-      <c r="O215" t="str">
-        <v/>
-      </c>
-      <c r="P215" t="str">
-        <v/>
-      </c>
-      <c r="Q215" t="str">
-        <v/>
-      </c>
-      <c r="R215" t="str">
-        <v/>
-      </c>
-      <c r="S215" t="str">
-        <v/>
-      </c>
-      <c r="T215" t="str">
-        <v/>
-      </c>
-      <c r="U215" t="str">
-        <v/>
-      </c>
-      <c r="V215" t="str">
-        <v/>
-      </c>
-      <c r="W215" t="str">
-        <v/>
-      </c>
-      <c r="X215" t="str">
-        <v/>
-      </c>
-      <c r="Y215" t="str">
-        <v/>
-      </c>
-      <c r="Z215" t="str">
-        <v/>
-      </c>
-      <c r="AA215" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="B216" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="C216" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D216" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E216" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F216" t="str">
-        <v/>
-      </c>
-      <c r="G216" t="str">
-        <v/>
-      </c>
-      <c r="H216" t="str">
-        <v/>
-      </c>
-      <c r="I216" t="str">
-        <v/>
-      </c>
-      <c r="J216" t="str">
-        <v/>
-      </c>
-      <c r="K216" t="str">
-        <v/>
-      </c>
-      <c r="L216" t="str">
-        <v/>
-      </c>
-      <c r="M216" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N216" t="str">
-        <v/>
-      </c>
-      <c r="O216" t="str">
-        <v/>
-      </c>
-      <c r="P216" t="str">
-        <v/>
-      </c>
-      <c r="Q216" t="str">
-        <v/>
-      </c>
-      <c r="R216" t="str">
-        <v/>
-      </c>
-      <c r="S216" t="str">
-        <v/>
-      </c>
-      <c r="T216" t="str">
-        <v/>
-      </c>
-      <c r="U216" t="str">
-        <v/>
-      </c>
-      <c r="V216" t="str">
-        <v/>
-      </c>
-      <c r="W216" t="str">
-        <v/>
-      </c>
-      <c r="X216" t="str">
-        <v/>
-      </c>
-      <c r="Y216" t="str">
-        <v/>
-      </c>
-      <c r="Z216" t="str">
-        <v/>
-      </c>
-      <c r="AA216" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="B217" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="C217" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D217" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E217" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F217" t="str">
-        <v/>
-      </c>
-      <c r="G217" t="str">
-        <v/>
-      </c>
-      <c r="H217" t="str">
-        <v/>
-      </c>
-      <c r="I217" t="str">
-        <v/>
-      </c>
-      <c r="J217" t="str">
-        <v/>
-      </c>
-      <c r="K217" t="str">
-        <v/>
-      </c>
-      <c r="L217" t="str">
-        <v/>
-      </c>
-      <c r="M217" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N217" t="str">
-        <v/>
-      </c>
-      <c r="O217" t="str">
-        <v/>
-      </c>
-      <c r="P217" t="str">
-        <v/>
-      </c>
-      <c r="Q217" t="str">
-        <v/>
-      </c>
-      <c r="R217" t="str">
-        <v/>
-      </c>
-      <c r="S217" t="str">
-        <v/>
-      </c>
-      <c r="T217" t="str">
-        <v/>
-      </c>
-      <c r="U217" t="str">
-        <v/>
-      </c>
-      <c r="V217" t="str">
-        <v/>
-      </c>
-      <c r="W217" t="str">
-        <v/>
-      </c>
-      <c r="X217" t="str">
-        <v/>
-      </c>
-      <c r="Y217" t="str">
-        <v/>
-      </c>
-      <c r="Z217" t="str">
-        <v/>
-      </c>
-      <c r="AA217" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="B218" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="C218" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D218" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E218" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F218" t="str">
-        <v/>
-      </c>
-      <c r="G218" t="str">
-        <v/>
-      </c>
-      <c r="H218" t="str">
-        <v/>
-      </c>
-      <c r="I218" t="str">
-        <v/>
-      </c>
-      <c r="J218" t="str">
-        <v/>
-      </c>
-      <c r="K218" t="str">
-        <v/>
-      </c>
-      <c r="L218" t="str">
-        <v/>
-      </c>
-      <c r="M218" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N218" t="str">
-        <v/>
-      </c>
-      <c r="O218" t="str">
-        <v/>
-      </c>
-      <c r="P218" t="str">
-        <v/>
-      </c>
-      <c r="Q218" t="str">
-        <v/>
-      </c>
-      <c r="R218" t="str">
-        <v/>
-      </c>
-      <c r="S218" t="str">
-        <v/>
-      </c>
-      <c r="T218" t="str">
-        <v/>
-      </c>
-      <c r="U218" t="str">
-        <v/>
-      </c>
-      <c r="V218" t="str">
-        <v/>
-      </c>
-      <c r="W218" t="str">
-        <v/>
-      </c>
-      <c r="X218" t="str">
-        <v/>
-      </c>
-      <c r="Y218" t="str">
-        <v/>
-      </c>
-      <c r="Z218" t="str">
-        <v/>
-      </c>
-      <c r="AA218" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="B219" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="C219" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D219" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E219" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F219" t="str">
-        <v/>
-      </c>
-      <c r="G219" t="str">
-        <v/>
-      </c>
-      <c r="H219" t="str">
-        <v/>
-      </c>
-      <c r="I219" t="str">
-        <v/>
-      </c>
-      <c r="J219" t="str">
-        <v/>
-      </c>
-      <c r="K219" t="str">
-        <v/>
-      </c>
-      <c r="L219" t="str">
-        <v/>
-      </c>
-      <c r="M219" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N219" t="str">
-        <v/>
-      </c>
-      <c r="O219" t="str">
-        <v/>
-      </c>
-      <c r="P219" t="str">
-        <v/>
-      </c>
-      <c r="Q219" t="str">
-        <v/>
-      </c>
-      <c r="R219" t="str">
-        <v/>
-      </c>
-      <c r="S219" t="str">
-        <v/>
-      </c>
-      <c r="T219" t="str">
-        <v/>
-      </c>
-      <c r="U219" t="str">
-        <v/>
-      </c>
-      <c r="V219" t="str">
-        <v/>
-      </c>
-      <c r="W219" t="str">
-        <v/>
-      </c>
-      <c r="X219" t="str">
-        <v/>
-      </c>
-      <c r="Y219" t="str">
-        <v/>
-      </c>
-      <c r="Z219" t="str">
-        <v/>
-      </c>
-      <c r="AA219" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>2026-03-20</v>
-      </c>
-      <c r="B220" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="C220" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="D220" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E220" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F220" t="str">
-        <v/>
-      </c>
-      <c r="G220" t="str">
-        <v/>
-      </c>
-      <c r="H220" t="str">
-        <v/>
-      </c>
-      <c r="I220" t="str">
-        <v/>
-      </c>
-      <c r="J220" t="str">
-        <v/>
-      </c>
-      <c r="K220" t="str">
-        <v/>
-      </c>
-      <c r="L220" t="str">
-        <v/>
-      </c>
-      <c r="M220" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N220" t="str">
-        <v/>
-      </c>
-      <c r="O220" t="str">
-        <v/>
-      </c>
-      <c r="P220" t="str">
-        <v/>
-      </c>
-      <c r="Q220" t="str">
-        <v/>
-      </c>
-      <c r="R220" t="str">
-        <v/>
-      </c>
-      <c r="S220" t="str">
-        <v/>
-      </c>
-      <c r="T220" t="str">
-        <v/>
-      </c>
-      <c r="U220" t="str">
-        <v/>
-      </c>
-      <c r="V220" t="str">
-        <v/>
-      </c>
-      <c r="W220" t="str">
-        <v/>
-      </c>
-      <c r="X220" t="str">
-        <v/>
-      </c>
-      <c r="Y220" t="str">
-        <v/>
-      </c>
-      <c r="Z220" t="str">
-        <v/>
-      </c>
-      <c r="AA220" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="B221" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="C221" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D221" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E221" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F221" t="str">
-        <v/>
-      </c>
-      <c r="G221" t="str">
-        <v/>
-      </c>
-      <c r="H221" t="str">
-        <v/>
-      </c>
-      <c r="I221" t="str">
-        <v/>
-      </c>
-      <c r="J221" t="str">
-        <v/>
-      </c>
-      <c r="K221" t="str">
-        <v/>
-      </c>
-      <c r="L221" t="str">
-        <v/>
-      </c>
-      <c r="M221" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N221" t="str">
-        <v/>
-      </c>
-      <c r="O221" t="str">
-        <v/>
-      </c>
-      <c r="P221" t="str">
-        <v/>
-      </c>
-      <c r="Q221" t="str">
-        <v/>
-      </c>
-      <c r="R221" t="str">
-        <v/>
-      </c>
-      <c r="S221" t="str">
-        <v/>
-      </c>
-      <c r="T221" t="str">
-        <v/>
-      </c>
-      <c r="U221" t="str">
-        <v/>
-      </c>
-      <c r="V221" t="str">
-        <v/>
-      </c>
-      <c r="W221" t="str">
-        <v/>
-      </c>
-      <c r="X221" t="str">
-        <v/>
-      </c>
-      <c r="Y221" t="str">
-        <v/>
-      </c>
-      <c r="Z221" t="str">
-        <v/>
-      </c>
-      <c r="AA221" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="B222" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="C222" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D222" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E222" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F222" t="str">
-        <v/>
-      </c>
-      <c r="G222" t="str">
-        <v/>
-      </c>
-      <c r="H222" t="str">
-        <v/>
-      </c>
-      <c r="I222" t="str">
-        <v/>
-      </c>
-      <c r="J222" t="str">
-        <v/>
-      </c>
-      <c r="K222" t="str">
-        <v/>
-      </c>
-      <c r="L222" t="str">
-        <v/>
-      </c>
-      <c r="M222" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N222" t="str">
-        <v/>
-      </c>
-      <c r="O222" t="str">
-        <v/>
-      </c>
-      <c r="P222" t="str">
-        <v/>
-      </c>
-      <c r="Q222" t="str">
-        <v/>
-      </c>
-      <c r="R222" t="str">
-        <v/>
-      </c>
-      <c r="S222" t="str">
-        <v/>
-      </c>
-      <c r="T222" t="str">
-        <v/>
-      </c>
-      <c r="U222" t="str">
-        <v/>
-      </c>
-      <c r="V222" t="str">
-        <v/>
-      </c>
-      <c r="W222" t="str">
-        <v/>
-      </c>
-      <c r="X222" t="str">
-        <v/>
-      </c>
-      <c r="Y222" t="str">
-        <v/>
-      </c>
-      <c r="Z222" t="str">
-        <v/>
-      </c>
-      <c r="AA222" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="B223" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="C223" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D223" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E223" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F223" t="str">
-        <v/>
-      </c>
-      <c r="G223" t="str">
-        <v/>
-      </c>
-      <c r="H223" t="str">
-        <v/>
-      </c>
-      <c r="I223" t="str">
-        <v/>
-      </c>
-      <c r="J223" t="str">
-        <v/>
-      </c>
-      <c r="K223" t="str">
-        <v/>
-      </c>
-      <c r="L223" t="str">
-        <v/>
-      </c>
-      <c r="M223" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N223" t="str">
-        <v/>
-      </c>
-      <c r="O223" t="str">
-        <v/>
-      </c>
-      <c r="P223" t="str">
-        <v/>
-      </c>
-      <c r="Q223" t="str">
-        <v/>
-      </c>
-      <c r="R223" t="str">
-        <v/>
-      </c>
-      <c r="S223" t="str">
-        <v/>
-      </c>
-      <c r="T223" t="str">
-        <v/>
-      </c>
-      <c r="U223" t="str">
-        <v/>
-      </c>
-      <c r="V223" t="str">
-        <v/>
-      </c>
-      <c r="W223" t="str">
-        <v/>
-      </c>
-      <c r="X223" t="str">
-        <v/>
-      </c>
-      <c r="Y223" t="str">
-        <v/>
-      </c>
-      <c r="Z223" t="str">
-        <v/>
-      </c>
-      <c r="AA223" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="B224" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="C224" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D224" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E224" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F224" t="str">
-        <v/>
-      </c>
-      <c r="G224" t="str">
-        <v/>
-      </c>
-      <c r="H224" t="str">
-        <v/>
-      </c>
-      <c r="I224" t="str">
-        <v/>
-      </c>
-      <c r="J224" t="str">
-        <v/>
-      </c>
-      <c r="K224" t="str">
-        <v/>
-      </c>
-      <c r="L224" t="str">
-        <v/>
-      </c>
-      <c r="M224" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N224" t="str">
-        <v/>
-      </c>
-      <c r="O224" t="str">
-        <v/>
-      </c>
-      <c r="P224" t="str">
-        <v/>
-      </c>
-      <c r="Q224" t="str">
-        <v/>
-      </c>
-      <c r="R224" t="str">
-        <v/>
-      </c>
-      <c r="S224" t="str">
-        <v/>
-      </c>
-      <c r="T224" t="str">
-        <v/>
-      </c>
-      <c r="U224" t="str">
-        <v/>
-      </c>
-      <c r="V224" t="str">
-        <v/>
-      </c>
-      <c r="W224" t="str">
-        <v/>
-      </c>
-      <c r="X224" t="str">
-        <v/>
-      </c>
-      <c r="Y224" t="str">
-        <v/>
-      </c>
-      <c r="Z224" t="str">
-        <v/>
-      </c>
-      <c r="AA224" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="B225" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="C225" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D225" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E225" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F225" t="str">
-        <v/>
-      </c>
-      <c r="G225" t="str">
-        <v/>
-      </c>
-      <c r="H225" t="str">
-        <v/>
-      </c>
-      <c r="I225" t="str">
-        <v/>
-      </c>
-      <c r="J225" t="str">
-        <v/>
-      </c>
-      <c r="K225" t="str">
-        <v/>
-      </c>
-      <c r="L225" t="str">
-        <v/>
-      </c>
-      <c r="M225" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N225" t="str">
-        <v/>
-      </c>
-      <c r="O225" t="str">
-        <v/>
-      </c>
-      <c r="P225" t="str">
-        <v/>
-      </c>
-      <c r="Q225" t="str">
-        <v/>
-      </c>
-      <c r="R225" t="str">
-        <v/>
-      </c>
-      <c r="S225" t="str">
-        <v/>
-      </c>
-      <c r="T225" t="str">
-        <v/>
-      </c>
-      <c r="U225" t="str">
-        <v/>
-      </c>
-      <c r="V225" t="str">
-        <v/>
-      </c>
-      <c r="W225" t="str">
-        <v/>
-      </c>
-      <c r="X225" t="str">
-        <v/>
-      </c>
-      <c r="Y225" t="str">
-        <v/>
-      </c>
-      <c r="Z225" t="str">
-        <v/>
-      </c>
-      <c r="AA225" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="B226" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="C226" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D226" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E226" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F226" t="str">
-        <v/>
-      </c>
-      <c r="G226" t="str">
-        <v/>
-      </c>
-      <c r="H226" t="str">
-        <v/>
-      </c>
-      <c r="I226" t="str">
-        <v/>
-      </c>
-      <c r="J226" t="str">
-        <v/>
-      </c>
-      <c r="K226" t="str">
-        <v/>
-      </c>
-      <c r="L226" t="str">
-        <v/>
-      </c>
-      <c r="M226" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N226" t="str">
-        <v/>
-      </c>
-      <c r="O226" t="str">
-        <v/>
-      </c>
-      <c r="P226" t="str">
-        <v/>
-      </c>
-      <c r="Q226" t="str">
-        <v/>
-      </c>
-      <c r="R226" t="str">
-        <v/>
-      </c>
-      <c r="S226" t="str">
-        <v/>
-      </c>
-      <c r="T226" t="str">
-        <v/>
-      </c>
-      <c r="U226" t="str">
-        <v/>
-      </c>
-      <c r="V226" t="str">
-        <v/>
-      </c>
-      <c r="W226" t="str">
-        <v/>
-      </c>
-      <c r="X226" t="str">
-        <v/>
-      </c>
-      <c r="Y226" t="str">
-        <v/>
-      </c>
-      <c r="Z226" t="str">
-        <v/>
-      </c>
-      <c r="AA226" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="str">
-        <v>2026-03-27</v>
-      </c>
-      <c r="B227" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="C227" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D227" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E227" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F227" t="str">
-        <v/>
-      </c>
-      <c r="G227" t="str">
-        <v/>
-      </c>
-      <c r="H227" t="str">
-        <v/>
-      </c>
-      <c r="I227" t="str">
-        <v/>
-      </c>
-      <c r="J227" t="str">
-        <v/>
-      </c>
-      <c r="K227" t="str">
-        <v/>
-      </c>
-      <c r="L227" t="str">
-        <v/>
-      </c>
-      <c r="M227" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N227" t="str">
-        <v/>
-      </c>
-      <c r="O227" t="str">
-        <v/>
-      </c>
-      <c r="P227" t="str">
-        <v/>
-      </c>
-      <c r="Q227" t="str">
-        <v/>
-      </c>
-      <c r="R227" t="str">
-        <v/>
-      </c>
-      <c r="S227" t="str">
-        <v/>
-      </c>
-      <c r="T227" t="str">
-        <v/>
-      </c>
-      <c r="U227" t="str">
-        <v/>
-      </c>
-      <c r="V227" t="str">
-        <v/>
-      </c>
-      <c r="W227" t="str">
-        <v/>
-      </c>
-      <c r="X227" t="str">
-        <v/>
-      </c>
-      <c r="Y227" t="str">
-        <v/>
-      </c>
-      <c r="Z227" t="str">
-        <v/>
-      </c>
-      <c r="AA227" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="B228" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="C228" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D228" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E228" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F228" t="str">
-        <v/>
-      </c>
-      <c r="G228" t="str">
-        <v/>
-      </c>
-      <c r="H228" t="str">
-        <v/>
-      </c>
-      <c r="I228" t="str">
-        <v/>
-      </c>
-      <c r="J228" t="str">
-        <v/>
-      </c>
-      <c r="K228" t="str">
-        <v/>
-      </c>
-      <c r="L228" t="str">
-        <v/>
-      </c>
-      <c r="M228" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N228" t="str">
-        <v/>
-      </c>
-      <c r="O228" t="str">
-        <v/>
-      </c>
-      <c r="P228" t="str">
-        <v/>
-      </c>
-      <c r="Q228" t="str">
-        <v/>
-      </c>
-      <c r="R228" t="str">
-        <v/>
-      </c>
-      <c r="S228" t="str">
-        <v/>
-      </c>
-      <c r="T228" t="str">
-        <v/>
-      </c>
-      <c r="U228" t="str">
-        <v/>
-      </c>
-      <c r="V228" t="str">
-        <v/>
-      </c>
-      <c r="W228" t="str">
-        <v/>
-      </c>
-      <c r="X228" t="str">
-        <v/>
-      </c>
-      <c r="Y228" t="str">
-        <v/>
-      </c>
-      <c r="Z228" t="str">
-        <v/>
-      </c>
-      <c r="AA228" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="str">
-        <v>2026-03-29</v>
-      </c>
-      <c r="B229" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="C229" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D229" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E229" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F229" t="str">
-        <v/>
-      </c>
-      <c r="G229" t="str">
-        <v/>
-      </c>
-      <c r="H229" t="str">
-        <v/>
-      </c>
-      <c r="I229" t="str">
-        <v/>
-      </c>
-      <c r="J229" t="str">
-        <v/>
-      </c>
-      <c r="K229" t="str">
-        <v/>
-      </c>
-      <c r="L229" t="str">
-        <v/>
-      </c>
-      <c r="M229" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N229" t="str">
-        <v/>
-      </c>
-      <c r="O229" t="str">
-        <v/>
-      </c>
-      <c r="P229" t="str">
-        <v/>
-      </c>
-      <c r="Q229" t="str">
-        <v/>
-      </c>
-      <c r="R229" t="str">
-        <v/>
-      </c>
-      <c r="S229" t="str">
-        <v/>
-      </c>
-      <c r="T229" t="str">
-        <v/>
-      </c>
-      <c r="U229" t="str">
-        <v/>
-      </c>
-      <c r="V229" t="str">
-        <v/>
-      </c>
-      <c r="W229" t="str">
-        <v/>
-      </c>
-      <c r="X229" t="str">
-        <v/>
-      </c>
-      <c r="Y229" t="str">
-        <v/>
-      </c>
-      <c r="Z229" t="str">
-        <v/>
-      </c>
-      <c r="AA229" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="str">
-        <v>2026-03-30</v>
-      </c>
-      <c r="B230" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="C230" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D230" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E230" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F230" t="str">
-        <v/>
-      </c>
-      <c r="G230" t="str">
-        <v/>
-      </c>
-      <c r="H230" t="str">
-        <v/>
-      </c>
-      <c r="I230" t="str">
-        <v/>
-      </c>
-      <c r="J230" t="str">
-        <v/>
-      </c>
-      <c r="K230" t="str">
-        <v/>
-      </c>
-      <c r="L230" t="str">
-        <v/>
-      </c>
-      <c r="M230" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N230" t="str">
-        <v/>
-      </c>
-      <c r="O230" t="str">
-        <v/>
-      </c>
-      <c r="P230" t="str">
-        <v/>
-      </c>
-      <c r="Q230" t="str">
-        <v/>
-      </c>
-      <c r="R230" t="str">
-        <v/>
-      </c>
-      <c r="S230" t="str">
-        <v/>
-      </c>
-      <c r="T230" t="str">
-        <v/>
-      </c>
-      <c r="U230" t="str">
-        <v/>
-      </c>
-      <c r="V230" t="str">
-        <v/>
-      </c>
-      <c r="W230" t="str">
-        <v/>
-      </c>
-      <c r="X230" t="str">
-        <v/>
-      </c>
-      <c r="Y230" t="str">
-        <v/>
-      </c>
-      <c r="Z230" t="str">
-        <v/>
-      </c>
-      <c r="AA230" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="str">
-        <v>2026-03-31</v>
-      </c>
-      <c r="B231" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="C231" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D231" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E231" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F231" t="str">
-        <v/>
-      </c>
-      <c r="G231" t="str">
-        <v/>
-      </c>
-      <c r="H231" t="str">
-        <v/>
-      </c>
-      <c r="I231" t="str">
-        <v/>
-      </c>
-      <c r="J231" t="str">
-        <v/>
-      </c>
-      <c r="K231" t="str">
-        <v/>
-      </c>
-      <c r="L231" t="str">
-        <v/>
-      </c>
-      <c r="M231" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N231" t="str">
-        <v/>
-      </c>
-      <c r="O231" t="str">
-        <v/>
-      </c>
-      <c r="P231" t="str">
-        <v/>
-      </c>
-      <c r="Q231" t="str">
-        <v/>
-      </c>
-      <c r="R231" t="str">
-        <v/>
-      </c>
-      <c r="S231" t="str">
-        <v/>
-      </c>
-      <c r="T231" t="str">
-        <v/>
-      </c>
-      <c r="U231" t="str">
-        <v/>
-      </c>
-      <c r="V231" t="str">
-        <v/>
-      </c>
-      <c r="W231" t="str">
-        <v/>
-      </c>
-      <c r="X231" t="str">
-        <v/>
-      </c>
-      <c r="Y231" t="str">
-        <v/>
-      </c>
-      <c r="Z231" t="str">
-        <v/>
-      </c>
-      <c r="AA231" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="B232" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="C232" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D232" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E232" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F232" t="str">
-        <v/>
-      </c>
-      <c r="G232" t="str">
-        <v/>
-      </c>
-      <c r="H232" t="str">
-        <v/>
-      </c>
-      <c r="I232" t="str">
-        <v/>
-      </c>
-      <c r="J232" t="str">
-        <v/>
-      </c>
-      <c r="K232" t="str">
-        <v/>
-      </c>
-      <c r="L232" t="str">
-        <v/>
-      </c>
-      <c r="M232" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N232" t="str">
-        <v/>
-      </c>
-      <c r="O232" t="str">
-        <v/>
-      </c>
-      <c r="P232" t="str">
-        <v/>
-      </c>
-      <c r="Q232" t="str">
-        <v/>
-      </c>
-      <c r="R232" t="str">
-        <v/>
-      </c>
-      <c r="S232" t="str">
-        <v/>
-      </c>
-      <c r="T232" t="str">
-        <v/>
-      </c>
-      <c r="U232" t="str">
-        <v/>
-      </c>
-      <c r="V232" t="str">
-        <v/>
-      </c>
-      <c r="W232" t="str">
-        <v/>
-      </c>
-      <c r="X232" t="str">
-        <v/>
-      </c>
-      <c r="Y232" t="str">
-        <v/>
-      </c>
-      <c r="Z232" t="str">
-        <v/>
-      </c>
-      <c r="AA232" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="B233" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="C233" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D233" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E233" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F233" t="str">
-        <v/>
-      </c>
-      <c r="G233" t="str">
-        <v/>
-      </c>
-      <c r="H233" t="str">
-        <v/>
-      </c>
-      <c r="I233" t="str">
-        <v/>
-      </c>
-      <c r="J233" t="str">
-        <v/>
-      </c>
-      <c r="K233" t="str">
-        <v/>
-      </c>
-      <c r="L233" t="str">
-        <v/>
-      </c>
-      <c r="M233" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N233" t="str">
-        <v/>
-      </c>
-      <c r="O233" t="str">
-        <v/>
-      </c>
-      <c r="P233" t="str">
-        <v/>
-      </c>
-      <c r="Q233" t="str">
-        <v/>
-      </c>
-      <c r="R233" t="str">
-        <v/>
-      </c>
-      <c r="S233" t="str">
-        <v/>
-      </c>
-      <c r="T233" t="str">
-        <v/>
-      </c>
-      <c r="U233" t="str">
-        <v/>
-      </c>
-      <c r="V233" t="str">
-        <v/>
-      </c>
-      <c r="W233" t="str">
-        <v/>
-      </c>
-      <c r="X233" t="str">
-        <v/>
-      </c>
-      <c r="Y233" t="str">
-        <v/>
-      </c>
-      <c r="Z233" t="str">
-        <v/>
-      </c>
-      <c r="AA233" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="B234" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="C234" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D234" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E234" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F234" t="str">
-        <v/>
-      </c>
-      <c r="G234" t="str">
-        <v/>
-      </c>
-      <c r="H234" t="str">
-        <v/>
-      </c>
-      <c r="I234" t="str">
-        <v/>
-      </c>
-      <c r="J234" t="str">
-        <v/>
-      </c>
-      <c r="K234" t="str">
-        <v/>
-      </c>
-      <c r="L234" t="str">
-        <v/>
-      </c>
-      <c r="M234" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N234" t="str">
-        <v/>
-      </c>
-      <c r="O234" t="str">
-        <v/>
-      </c>
-      <c r="P234" t="str">
-        <v/>
-      </c>
-      <c r="Q234" t="str">
-        <v/>
-      </c>
-      <c r="R234" t="str">
-        <v/>
-      </c>
-      <c r="S234" t="str">
-        <v/>
-      </c>
-      <c r="T234" t="str">
-        <v/>
-      </c>
-      <c r="U234" t="str">
-        <v/>
-      </c>
-      <c r="V234" t="str">
-        <v/>
-      </c>
-      <c r="W234" t="str">
-        <v/>
-      </c>
-      <c r="X234" t="str">
-        <v/>
-      </c>
-      <c r="Y234" t="str">
-        <v/>
-      </c>
-      <c r="Z234" t="str">
-        <v/>
-      </c>
-      <c r="AA234" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="B235" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="C235" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D235" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E235" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F235" t="str">
-        <v/>
-      </c>
-      <c r="G235" t="str">
-        <v/>
-      </c>
-      <c r="H235" t="str">
-        <v/>
-      </c>
-      <c r="I235" t="str">
-        <v/>
-      </c>
-      <c r="J235" t="str">
-        <v/>
-      </c>
-      <c r="K235" t="str">
-        <v/>
-      </c>
-      <c r="L235" t="str">
-        <v/>
-      </c>
-      <c r="M235" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N235" t="str">
-        <v/>
-      </c>
-      <c r="O235" t="str">
-        <v/>
-      </c>
-      <c r="P235" t="str">
-        <v/>
-      </c>
-      <c r="Q235" t="str">
-        <v/>
-      </c>
-      <c r="R235" t="str">
-        <v/>
-      </c>
-      <c r="S235" t="str">
-        <v/>
-      </c>
-      <c r="T235" t="str">
-        <v/>
-      </c>
-      <c r="U235" t="str">
-        <v/>
-      </c>
-      <c r="V235" t="str">
-        <v/>
-      </c>
-      <c r="W235" t="str">
-        <v/>
-      </c>
-      <c r="X235" t="str">
-        <v/>
-      </c>
-      <c r="Y235" t="str">
-        <v/>
-      </c>
-      <c r="Z235" t="str">
-        <v/>
-      </c>
-      <c r="AA235" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="B236" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="C236" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D236" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E236" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F236" t="str">
-        <v/>
-      </c>
-      <c r="G236" t="str">
-        <v/>
-      </c>
-      <c r="H236" t="str">
-        <v/>
-      </c>
-      <c r="I236" t="str">
-        <v/>
-      </c>
-      <c r="J236" t="str">
-        <v/>
-      </c>
-      <c r="K236" t="str">
-        <v/>
-      </c>
-      <c r="L236" t="str">
-        <v/>
-      </c>
-      <c r="M236" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N236" t="str">
-        <v/>
-      </c>
-      <c r="O236" t="str">
-        <v/>
-      </c>
-      <c r="P236" t="str">
-        <v/>
-      </c>
-      <c r="Q236" t="str">
-        <v/>
-      </c>
-      <c r="R236" t="str">
-        <v/>
-      </c>
-      <c r="S236" t="str">
-        <v/>
-      </c>
-      <c r="T236" t="str">
-        <v/>
-      </c>
-      <c r="U236" t="str">
-        <v/>
-      </c>
-      <c r="V236" t="str">
-        <v/>
-      </c>
-      <c r="W236" t="str">
-        <v/>
-      </c>
-      <c r="X236" t="str">
-        <v/>
-      </c>
-      <c r="Y236" t="str">
-        <v/>
-      </c>
-      <c r="Z236" t="str">
-        <v/>
-      </c>
-      <c r="AA236" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="B237" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="C237" t="str">
-        <v>Cernobbio</v>
-      </c>
-      <c r="D237" t="str">
-        <v>Cernobbio</v>
-      </c>
-      <c r="E237" t="str">
-        <v>Italy</v>
-      </c>
-      <c r="F237" t="str">
-        <v/>
-      </c>
-      <c r="G237" t="str">
-        <v/>
-      </c>
-      <c r="H237" t="str">
-        <v/>
-      </c>
-      <c r="I237" t="str">
-        <v/>
-      </c>
-      <c r="J237" t="str">
-        <v/>
-      </c>
-      <c r="K237" t="str">
-        <v/>
-      </c>
-      <c r="L237" t="str">
-        <v/>
-      </c>
-      <c r="M237" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N237" t="str">
-        <v/>
-      </c>
-      <c r="O237" t="str">
-        <v/>
-      </c>
-      <c r="P237" t="str">
-        <v/>
-      </c>
-      <c r="Q237" t="str">
-        <v/>
-      </c>
-      <c r="R237" t="str">
-        <v/>
-      </c>
-      <c r="S237" t="str">
-        <v/>
-      </c>
-      <c r="T237" t="str">
-        <v/>
-      </c>
-      <c r="U237" t="str">
-        <v/>
-      </c>
-      <c r="V237" t="str">
-        <v/>
-      </c>
-      <c r="W237" t="str">
-        <v/>
-      </c>
-      <c r="X237" t="str">
-        <v/>
-      </c>
-      <c r="Y237" t="str">
-        <v/>
-      </c>
-      <c r="Z237" t="str">
-        <v/>
-      </c>
-      <c r="AA237" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="str">
-        <v>2026-04-07</v>
-      </c>
-      <c r="B238" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="C238" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D238" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E238" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F238" t="str">
-        <v/>
-      </c>
-      <c r="G238" t="str">
-        <v/>
-      </c>
-      <c r="H238" t="str">
-        <v/>
-      </c>
-      <c r="I238" t="str">
-        <v/>
-      </c>
-      <c r="J238" t="str">
-        <v/>
-      </c>
-      <c r="K238" t="str">
-        <v/>
-      </c>
-      <c r="L238" t="str">
-        <v/>
-      </c>
-      <c r="M238" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N238" t="str">
-        <v/>
-      </c>
-      <c r="O238" t="str">
-        <v/>
-      </c>
-      <c r="P238" t="str">
-        <v/>
-      </c>
-      <c r="Q238" t="str">
-        <v/>
-      </c>
-      <c r="R238" t="str">
-        <v/>
-      </c>
-      <c r="S238" t="str">
-        <v/>
-      </c>
-      <c r="T238" t="str">
-        <v/>
-      </c>
-      <c r="U238" t="str">
-        <v/>
-      </c>
-      <c r="V238" t="str">
-        <v/>
-      </c>
-      <c r="W238" t="str">
-        <v/>
-      </c>
-      <c r="X238" t="str">
-        <v/>
-      </c>
-      <c r="Y238" t="str">
-        <v/>
-      </c>
-      <c r="Z238" t="str">
-        <v/>
-      </c>
-      <c r="AA238" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="str">
-        <v>2026-04-08</v>
-      </c>
-      <c r="B239" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="C239" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D239" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E239" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F239" t="str">
-        <v/>
-      </c>
-      <c r="G239" t="str">
-        <v/>
-      </c>
-      <c r="H239" t="str">
-        <v/>
-      </c>
-      <c r="I239" t="str">
-        <v/>
-      </c>
-      <c r="J239" t="str">
-        <v/>
-      </c>
-      <c r="K239" t="str">
-        <v/>
-      </c>
-      <c r="L239" t="str">
-        <v/>
-      </c>
-      <c r="M239" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N239" t="str">
-        <v/>
-      </c>
-      <c r="O239" t="str">
-        <v/>
-      </c>
-      <c r="P239" t="str">
-        <v/>
-      </c>
-      <c r="Q239" t="str">
-        <v/>
-      </c>
-      <c r="R239" t="str">
-        <v/>
-      </c>
-      <c r="S239" t="str">
-        <v/>
-      </c>
-      <c r="T239" t="str">
-        <v/>
-      </c>
-      <c r="U239" t="str">
-        <v/>
-      </c>
-      <c r="V239" t="str">
-        <v/>
-      </c>
-      <c r="W239" t="str">
-        <v/>
-      </c>
-      <c r="X239" t="str">
-        <v/>
-      </c>
-      <c r="Y239" t="str">
-        <v/>
-      </c>
-      <c r="Z239" t="str">
-        <v/>
-      </c>
-      <c r="AA239" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="B240" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="C240" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D240" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E240" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F240" t="str">
-        <v/>
-      </c>
-      <c r="G240" t="str">
-        <v/>
-      </c>
-      <c r="H240" t="str">
-        <v/>
-      </c>
-      <c r="I240" t="str">
-        <v/>
-      </c>
-      <c r="J240" t="str">
-        <v/>
-      </c>
-      <c r="K240" t="str">
-        <v/>
-      </c>
-      <c r="L240" t="str">
-        <v/>
-      </c>
-      <c r="M240" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N240" t="str">
-        <v/>
-      </c>
-      <c r="O240" t="str">
-        <v/>
-      </c>
-      <c r="P240" t="str">
-        <v/>
-      </c>
-      <c r="Q240" t="str">
-        <v/>
-      </c>
-      <c r="R240" t="str">
-        <v/>
-      </c>
-      <c r="S240" t="str">
-        <v/>
-      </c>
-      <c r="T240" t="str">
-        <v/>
-      </c>
-      <c r="U240" t="str">
-        <v/>
-      </c>
-      <c r="V240" t="str">
-        <v/>
-      </c>
-      <c r="W240" t="str">
-        <v/>
-      </c>
-      <c r="X240" t="str">
-        <v/>
-      </c>
-      <c r="Y240" t="str">
-        <v/>
-      </c>
-      <c r="Z240" t="str">
-        <v/>
-      </c>
-      <c r="AA240" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="str">
-        <v>2026-04-10</v>
-      </c>
-      <c r="B241" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="C241" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D241" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E241" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F241" t="str">
-        <v/>
-      </c>
-      <c r="G241" t="str">
-        <v/>
-      </c>
-      <c r="H241" t="str">
-        <v/>
-      </c>
-      <c r="I241" t="str">
-        <v/>
-      </c>
-      <c r="J241" t="str">
-        <v/>
-      </c>
-      <c r="K241" t="str">
-        <v/>
-      </c>
-      <c r="L241" t="str">
-        <v/>
-      </c>
-      <c r="M241" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N241" t="str">
-        <v/>
-      </c>
-      <c r="O241" t="str">
-        <v/>
-      </c>
-      <c r="P241" t="str">
-        <v/>
-      </c>
-      <c r="Q241" t="str">
-        <v/>
-      </c>
-      <c r="R241" t="str">
-        <v/>
-      </c>
-      <c r="S241" t="str">
-        <v/>
-      </c>
-      <c r="T241" t="str">
-        <v/>
-      </c>
-      <c r="U241" t="str">
-        <v/>
-      </c>
-      <c r="V241" t="str">
-        <v/>
-      </c>
-      <c r="W241" t="str">
-        <v/>
-      </c>
-      <c r="X241" t="str">
-        <v/>
-      </c>
-      <c r="Y241" t="str">
-        <v/>
-      </c>
-      <c r="Z241" t="str">
-        <v/>
-      </c>
-      <c r="AA241" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="B242" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="C242" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D242" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E242" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F242" t="str">
-        <v/>
-      </c>
-      <c r="G242" t="str">
-        <v/>
-      </c>
-      <c r="H242" t="str">
-        <v/>
-      </c>
-      <c r="I242" t="str">
-        <v/>
-      </c>
-      <c r="J242" t="str">
-        <v/>
-      </c>
-      <c r="K242" t="str">
-        <v/>
-      </c>
-      <c r="L242" t="str">
-        <v/>
-      </c>
-      <c r="M242" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N242" t="str">
-        <v/>
-      </c>
-      <c r="O242" t="str">
-        <v/>
-      </c>
-      <c r="P242" t="str">
-        <v/>
-      </c>
-      <c r="Q242" t="str">
-        <v/>
-      </c>
-      <c r="R242" t="str">
-        <v/>
-      </c>
-      <c r="S242" t="str">
-        <v/>
-      </c>
-      <c r="T242" t="str">
-        <v/>
-      </c>
-      <c r="U242" t="str">
-        <v/>
-      </c>
-      <c r="V242" t="str">
-        <v/>
-      </c>
-      <c r="W242" t="str">
-        <v/>
-      </c>
-      <c r="X242" t="str">
-        <v/>
-      </c>
-      <c r="Y242" t="str">
-        <v/>
-      </c>
-      <c r="Z242" t="str">
-        <v/>
-      </c>
-      <c r="AA242" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="B243" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="C243" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D243" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E243" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F243" t="str">
-        <v/>
-      </c>
-      <c r="G243" t="str">
-        <v/>
-      </c>
-      <c r="H243" t="str">
-        <v/>
-      </c>
-      <c r="I243" t="str">
-        <v/>
-      </c>
-      <c r="J243" t="str">
-        <v/>
-      </c>
-      <c r="K243" t="str">
-        <v/>
-      </c>
-      <c r="L243" t="str">
-        <v/>
-      </c>
-      <c r="M243" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N243" t="str">
-        <v/>
-      </c>
-      <c r="O243" t="str">
-        <v/>
-      </c>
-      <c r="P243" t="str">
-        <v/>
-      </c>
-      <c r="Q243" t="str">
-        <v/>
-      </c>
-      <c r="R243" t="str">
-        <v/>
-      </c>
-      <c r="S243" t="str">
-        <v/>
-      </c>
-      <c r="T243" t="str">
-        <v/>
-      </c>
-      <c r="U243" t="str">
-        <v/>
-      </c>
-      <c r="V243" t="str">
-        <v/>
-      </c>
-      <c r="W243" t="str">
-        <v/>
-      </c>
-      <c r="X243" t="str">
-        <v/>
-      </c>
-      <c r="Y243" t="str">
-        <v/>
-      </c>
-      <c r="Z243" t="str">
-        <v/>
-      </c>
-      <c r="AA243" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="B244" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="C244" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D244" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E244" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F244" t="str">
-        <v/>
-      </c>
-      <c r="G244" t="str">
-        <v/>
-      </c>
-      <c r="H244" t="str">
-        <v/>
-      </c>
-      <c r="I244" t="str">
-        <v/>
-      </c>
-      <c r="J244" t="str">
-        <v/>
-      </c>
-      <c r="K244" t="str">
-        <v/>
-      </c>
-      <c r="L244" t="str">
-        <v/>
-      </c>
-      <c r="M244" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N244" t="str">
-        <v/>
-      </c>
-      <c r="O244" t="str">
-        <v/>
-      </c>
-      <c r="P244" t="str">
-        <v/>
-      </c>
-      <c r="Q244" t="str">
-        <v/>
-      </c>
-      <c r="R244" t="str">
-        <v/>
-      </c>
-      <c r="S244" t="str">
-        <v/>
-      </c>
-      <c r="T244" t="str">
-        <v/>
-      </c>
-      <c r="U244" t="str">
-        <v/>
-      </c>
-      <c r="V244" t="str">
-        <v/>
-      </c>
-      <c r="W244" t="str">
-        <v/>
-      </c>
-      <c r="X244" t="str">
-        <v/>
-      </c>
-      <c r="Y244" t="str">
-        <v/>
-      </c>
-      <c r="Z244" t="str">
-        <v/>
-      </c>
-      <c r="AA244" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="str">
-        <v>2026-04-14</v>
-      </c>
-      <c r="B245" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="C245" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D245" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E245" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F245" t="str">
-        <v/>
-      </c>
-      <c r="G245" t="str">
-        <v/>
-      </c>
-      <c r="H245" t="str">
-        <v/>
-      </c>
-      <c r="I245" t="str">
-        <v/>
-      </c>
-      <c r="J245" t="str">
-        <v/>
-      </c>
-      <c r="K245" t="str">
-        <v/>
-      </c>
-      <c r="L245" t="str">
-        <v/>
-      </c>
-      <c r="M245" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N245" t="str">
-        <v/>
-      </c>
-      <c r="O245" t="str">
-        <v/>
-      </c>
-      <c r="P245" t="str">
-        <v/>
-      </c>
-      <c r="Q245" t="str">
-        <v/>
-      </c>
-      <c r="R245" t="str">
-        <v/>
-      </c>
-      <c r="S245" t="str">
-        <v/>
-      </c>
-      <c r="T245" t="str">
-        <v/>
-      </c>
-      <c r="U245" t="str">
-        <v/>
-      </c>
-      <c r="V245" t="str">
-        <v/>
-      </c>
-      <c r="W245" t="str">
-        <v/>
-      </c>
-      <c r="X245" t="str">
-        <v/>
-      </c>
-      <c r="Y245" t="str">
-        <v/>
-      </c>
-      <c r="Z245" t="str">
-        <v/>
-      </c>
-      <c r="AA245" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="B246" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="C246" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D246" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E246" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F246" t="str">
-        <v/>
-      </c>
-      <c r="G246" t="str">
-        <v/>
-      </c>
-      <c r="H246" t="str">
-        <v/>
-      </c>
-      <c r="I246" t="str">
-        <v/>
-      </c>
-      <c r="J246" t="str">
-        <v/>
-      </c>
-      <c r="K246" t="str">
-        <v/>
-      </c>
-      <c r="L246" t="str">
-        <v/>
-      </c>
-      <c r="M246" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N246" t="str">
-        <v/>
-      </c>
-      <c r="O246" t="str">
-        <v/>
-      </c>
-      <c r="P246" t="str">
-        <v/>
-      </c>
-      <c r="Q246" t="str">
-        <v/>
-      </c>
-      <c r="R246" t="str">
-        <v/>
-      </c>
-      <c r="S246" t="str">
-        <v/>
-      </c>
-      <c r="T246" t="str">
-        <v/>
-      </c>
-      <c r="U246" t="str">
-        <v/>
-      </c>
-      <c r="V246" t="str">
-        <v/>
-      </c>
-      <c r="W246" t="str">
-        <v/>
-      </c>
-      <c r="X246" t="str">
-        <v/>
-      </c>
-      <c r="Y246" t="str">
-        <v/>
-      </c>
-      <c r="Z246" t="str">
-        <v/>
-      </c>
-      <c r="AA246" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="B247" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="C247" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D247" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E247" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F247" t="str">
-        <v/>
-      </c>
-      <c r="G247" t="str">
-        <v/>
-      </c>
-      <c r="H247" t="str">
-        <v/>
-      </c>
-      <c r="I247" t="str">
-        <v/>
-      </c>
-      <c r="J247" t="str">
-        <v/>
-      </c>
-      <c r="K247" t="str">
-        <v/>
-      </c>
-      <c r="L247" t="str">
-        <v/>
-      </c>
-      <c r="M247" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N247" t="str">
-        <v/>
-      </c>
-      <c r="O247" t="str">
-        <v/>
-      </c>
-      <c r="P247" t="str">
-        <v/>
-      </c>
-      <c r="Q247" t="str">
-        <v/>
-      </c>
-      <c r="R247" t="str">
-        <v/>
-      </c>
-      <c r="S247" t="str">
-        <v/>
-      </c>
-      <c r="T247" t="str">
-        <v/>
-      </c>
-      <c r="U247" t="str">
-        <v/>
-      </c>
-      <c r="V247" t="str">
-        <v/>
-      </c>
-      <c r="W247" t="str">
-        <v/>
-      </c>
-      <c r="X247" t="str">
-        <v/>
-      </c>
-      <c r="Y247" t="str">
-        <v/>
-      </c>
-      <c r="Z247" t="str">
-        <v/>
-      </c>
-      <c r="AA247" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="B248" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="C248" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D248" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E248" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F248" t="str">
-        <v/>
-      </c>
-      <c r="G248" t="str">
-        <v/>
-      </c>
-      <c r="H248" t="str">
-        <v/>
-      </c>
-      <c r="I248" t="str">
-        <v/>
-      </c>
-      <c r="J248" t="str">
-        <v/>
-      </c>
-      <c r="K248" t="str">
-        <v/>
-      </c>
-      <c r="L248" t="str">
-        <v/>
-      </c>
-      <c r="M248" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N248" t="str">
-        <v/>
-      </c>
-      <c r="O248" t="str">
-        <v/>
-      </c>
-      <c r="P248" t="str">
-        <v/>
-      </c>
-      <c r="Q248" t="str">
-        <v/>
-      </c>
-      <c r="R248" t="str">
-        <v/>
-      </c>
-      <c r="S248" t="str">
-        <v/>
-      </c>
-      <c r="T248" t="str">
-        <v/>
-      </c>
-      <c r="U248" t="str">
-        <v/>
-      </c>
-      <c r="V248" t="str">
-        <v/>
-      </c>
-      <c r="W248" t="str">
-        <v/>
-      </c>
-      <c r="X248" t="str">
-        <v/>
-      </c>
-      <c r="Y248" t="str">
-        <v/>
-      </c>
-      <c r="Z248" t="str">
-        <v/>
-      </c>
-      <c r="AA248" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="B249" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="C249" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D249" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E249" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F249" t="str">
-        <v/>
-      </c>
-      <c r="G249" t="str">
-        <v/>
-      </c>
-      <c r="H249" t="str">
-        <v/>
-      </c>
-      <c r="I249" t="str">
-        <v/>
-      </c>
-      <c r="J249" t="str">
-        <v/>
-      </c>
-      <c r="K249" t="str">
-        <v/>
-      </c>
-      <c r="L249" t="str">
-        <v/>
-      </c>
-      <c r="M249" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N249" t="str">
-        <v/>
-      </c>
-      <c r="O249" t="str">
-        <v/>
-      </c>
-      <c r="P249" t="str">
-        <v/>
-      </c>
-      <c r="Q249" t="str">
-        <v/>
-      </c>
-      <c r="R249" t="str">
-        <v/>
-      </c>
-      <c r="S249" t="str">
-        <v/>
-      </c>
-      <c r="T249" t="str">
-        <v/>
-      </c>
-      <c r="U249" t="str">
-        <v/>
-      </c>
-      <c r="V249" t="str">
-        <v/>
-      </c>
-      <c r="W249" t="str">
-        <v/>
-      </c>
-      <c r="X249" t="str">
-        <v/>
-      </c>
-      <c r="Y249" t="str">
-        <v/>
-      </c>
-      <c r="Z249" t="str">
-        <v/>
-      </c>
-      <c r="AA249" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="B250" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="C250" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D250" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E250" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F250" t="str">
-        <v/>
-      </c>
-      <c r="G250" t="str">
-        <v/>
-      </c>
-      <c r="H250" t="str">
-        <v/>
-      </c>
-      <c r="I250" t="str">
-        <v/>
-      </c>
-      <c r="J250" t="str">
-        <v/>
-      </c>
-      <c r="K250" t="str">
-        <v/>
-      </c>
-      <c r="L250" t="str">
-        <v/>
-      </c>
-      <c r="M250" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N250" t="str">
-        <v/>
-      </c>
-      <c r="O250" t="str">
-        <v/>
-      </c>
-      <c r="P250" t="str">
-        <v/>
-      </c>
-      <c r="Q250" t="str">
-        <v/>
-      </c>
-      <c r="R250" t="str">
-        <v/>
-      </c>
-      <c r="S250" t="str">
-        <v/>
-      </c>
-      <c r="T250" t="str">
-        <v/>
-      </c>
-      <c r="U250" t="str">
-        <v/>
-      </c>
-      <c r="V250" t="str">
-        <v/>
-      </c>
-      <c r="W250" t="str">
-        <v/>
-      </c>
-      <c r="X250" t="str">
-        <v/>
-      </c>
-      <c r="Y250" t="str">
-        <v/>
-      </c>
-      <c r="Z250" t="str">
-        <v/>
-      </c>
-      <c r="AA250" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="B251" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="C251" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D251" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E251" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F251" t="str">
-        <v/>
-      </c>
-      <c r="G251" t="str">
-        <v/>
-      </c>
-      <c r="H251" t="str">
-        <v/>
-      </c>
-      <c r="I251" t="str">
-        <v/>
-      </c>
-      <c r="J251" t="str">
-        <v/>
-      </c>
-      <c r="K251" t="str">
-        <v/>
-      </c>
-      <c r="L251" t="str">
-        <v/>
-      </c>
-      <c r="M251" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N251" t="str">
-        <v/>
-      </c>
-      <c r="O251" t="str">
-        <v/>
-      </c>
-      <c r="P251" t="str">
-        <v/>
-      </c>
-      <c r="Q251" t="str">
-        <v/>
-      </c>
-      <c r="R251" t="str">
-        <v/>
-      </c>
-      <c r="S251" t="str">
-        <v/>
-      </c>
-      <c r="T251" t="str">
-        <v/>
-      </c>
-      <c r="U251" t="str">
-        <v/>
-      </c>
-      <c r="V251" t="str">
-        <v/>
-      </c>
-      <c r="W251" t="str">
-        <v/>
-      </c>
-      <c r="X251" t="str">
-        <v/>
-      </c>
-      <c r="Y251" t="str">
-        <v/>
-      </c>
-      <c r="Z251" t="str">
-        <v/>
-      </c>
-      <c r="AA251" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="B252" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="C252" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D252" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E252" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F252" t="str">
-        <v/>
-      </c>
-      <c r="G252" t="str">
-        <v/>
-      </c>
-      <c r="H252" t="str">
-        <v/>
-      </c>
-      <c r="I252" t="str">
-        <v/>
-      </c>
-      <c r="J252" t="str">
-        <v/>
-      </c>
-      <c r="K252" t="str">
-        <v/>
-      </c>
-      <c r="L252" t="str">
-        <v/>
-      </c>
-      <c r="M252" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N252" t="str">
-        <v/>
-      </c>
-      <c r="O252" t="str">
-        <v/>
-      </c>
-      <c r="P252" t="str">
-        <v/>
-      </c>
-      <c r="Q252" t="str">
-        <v/>
-      </c>
-      <c r="R252" t="str">
-        <v/>
-      </c>
-      <c r="S252" t="str">
-        <v/>
-      </c>
-      <c r="T252" t="str">
-        <v/>
-      </c>
-      <c r="U252" t="str">
-        <v/>
-      </c>
-      <c r="V252" t="str">
-        <v/>
-      </c>
-      <c r="W252" t="str">
-        <v/>
-      </c>
-      <c r="X252" t="str">
-        <v/>
-      </c>
-      <c r="Y252" t="str">
-        <v/>
-      </c>
-      <c r="Z252" t="str">
-        <v/>
-      </c>
-      <c r="AA252" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="str">
-        <v>2026-04-22</v>
-      </c>
-      <c r="B253" t="str">
-        <v>Wednesday</v>
-      </c>
-      <c r="C253" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D253" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E253" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F253" t="str">
-        <v/>
-      </c>
-      <c r="G253" t="str">
-        <v/>
-      </c>
-      <c r="H253" t="str">
-        <v/>
-      </c>
-      <c r="I253" t="str">
-        <v/>
-      </c>
-      <c r="J253" t="str">
-        <v/>
-      </c>
-      <c r="K253" t="str">
-        <v/>
-      </c>
-      <c r="L253" t="str">
-        <v/>
-      </c>
-      <c r="M253" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N253" t="str">
-        <v/>
-      </c>
-      <c r="O253" t="str">
-        <v/>
-      </c>
-      <c r="P253" t="str">
-        <v/>
-      </c>
-      <c r="Q253" t="str">
-        <v/>
-      </c>
-      <c r="R253" t="str">
-        <v/>
-      </c>
-      <c r="S253" t="str">
-        <v/>
-      </c>
-      <c r="T253" t="str">
-        <v/>
-      </c>
-      <c r="U253" t="str">
-        <v/>
-      </c>
-      <c r="V253" t="str">
-        <v/>
-      </c>
-      <c r="W253" t="str">
-        <v/>
-      </c>
-      <c r="X253" t="str">
-        <v/>
-      </c>
-      <c r="Y253" t="str">
-        <v/>
-      </c>
-      <c r="Z253" t="str">
-        <v/>
-      </c>
-      <c r="AA253" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="B254" t="str">
-        <v>Thursday</v>
-      </c>
-      <c r="C254" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D254" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E254" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F254" t="str">
-        <v/>
-      </c>
-      <c r="G254" t="str">
-        <v/>
-      </c>
-      <c r="H254" t="str">
-        <v/>
-      </c>
-      <c r="I254" t="str">
-        <v/>
-      </c>
-      <c r="J254" t="str">
-        <v/>
-      </c>
-      <c r="K254" t="str">
-        <v/>
-      </c>
-      <c r="L254" t="str">
-        <v/>
-      </c>
-      <c r="M254" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N254" t="str">
-        <v/>
-      </c>
-      <c r="O254" t="str">
-        <v/>
-      </c>
-      <c r="P254" t="str">
-        <v/>
-      </c>
-      <c r="Q254" t="str">
-        <v/>
-      </c>
-      <c r="R254" t="str">
-        <v/>
-      </c>
-      <c r="S254" t="str">
-        <v/>
-      </c>
-      <c r="T254" t="str">
-        <v/>
-      </c>
-      <c r="U254" t="str">
-        <v/>
-      </c>
-      <c r="V254" t="str">
-        <v/>
-      </c>
-      <c r="W254" t="str">
-        <v/>
-      </c>
-      <c r="X254" t="str">
-        <v/>
-      </c>
-      <c r="Y254" t="str">
-        <v/>
-      </c>
-      <c r="Z254" t="str">
-        <v/>
-      </c>
-      <c r="AA254" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="B255" t="str">
-        <v>Friday</v>
-      </c>
-      <c r="C255" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D255" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E255" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F255" t="str">
-        <v/>
-      </c>
-      <c r="G255" t="str">
-        <v/>
-      </c>
-      <c r="H255" t="str">
-        <v/>
-      </c>
-      <c r="I255" t="str">
-        <v/>
-      </c>
-      <c r="J255" t="str">
-        <v/>
-      </c>
-      <c r="K255" t="str">
-        <v/>
-      </c>
-      <c r="L255" t="str">
-        <v/>
-      </c>
-      <c r="M255" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N255" t="str">
-        <v/>
-      </c>
-      <c r="O255" t="str">
-        <v/>
-      </c>
-      <c r="P255" t="str">
-        <v/>
-      </c>
-      <c r="Q255" t="str">
-        <v/>
-      </c>
-      <c r="R255" t="str">
-        <v/>
-      </c>
-      <c r="S255" t="str">
-        <v/>
-      </c>
-      <c r="T255" t="str">
-        <v/>
-      </c>
-      <c r="U255" t="str">
-        <v/>
-      </c>
-      <c r="V255" t="str">
-        <v/>
-      </c>
-      <c r="W255" t="str">
-        <v/>
-      </c>
-      <c r="X255" t="str">
-        <v/>
-      </c>
-      <c r="Y255" t="str">
-        <v/>
-      </c>
-      <c r="Z255" t="str">
-        <v/>
-      </c>
-      <c r="AA255" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="str">
-        <v>2026-04-25</v>
-      </c>
-      <c r="B256" t="str">
-        <v>Saturday</v>
-      </c>
-      <c r="C256" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D256" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E256" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F256" t="str">
-        <v/>
-      </c>
-      <c r="G256" t="str">
-        <v/>
-      </c>
-      <c r="H256" t="str">
-        <v/>
-      </c>
-      <c r="I256" t="str">
-        <v/>
-      </c>
-      <c r="J256" t="str">
-        <v/>
-      </c>
-      <c r="K256" t="str">
-        <v/>
-      </c>
-      <c r="L256" t="str">
-        <v/>
-      </c>
-      <c r="M256" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N256" t="str">
-        <v/>
-      </c>
-      <c r="O256" t="str">
-        <v/>
-      </c>
-      <c r="P256" t="str">
-        <v/>
-      </c>
-      <c r="Q256" t="str">
-        <v/>
-      </c>
-      <c r="R256" t="str">
-        <v/>
-      </c>
-      <c r="S256" t="str">
-        <v/>
-      </c>
-      <c r="T256" t="str">
-        <v/>
-      </c>
-      <c r="U256" t="str">
-        <v/>
-      </c>
-      <c r="V256" t="str">
-        <v/>
-      </c>
-      <c r="W256" t="str">
-        <v/>
-      </c>
-      <c r="X256" t="str">
-        <v/>
-      </c>
-      <c r="Y256" t="str">
-        <v/>
-      </c>
-      <c r="Z256" t="str">
-        <v/>
-      </c>
-      <c r="AA256" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="B257" t="str">
-        <v>Sunday</v>
-      </c>
-      <c r="C257" t="str">
-        <v>417 Meadow Lane</v>
-      </c>
-      <c r="D257" t="str">
-        <v>Oxford</v>
-      </c>
-      <c r="E257" t="str">
-        <v>UK</v>
-      </c>
-      <c r="F257" t="str">
-        <v/>
-      </c>
-      <c r="G257" t="str">
-        <v/>
-      </c>
-      <c r="H257" t="str">
-        <v/>
-      </c>
-      <c r="I257" t="str">
-        <v/>
-      </c>
-      <c r="J257" t="str">
-        <v/>
-      </c>
-      <c r="K257" t="str">
-        <v/>
-      </c>
-      <c r="L257" t="str">
-        <v/>
-      </c>
-      <c r="M257" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="N257" t="str">
-        <v/>
-      </c>
-      <c r="O257" t="str">
-        <v/>
-      </c>
-      <c r="P257" t="str">
-        <v/>
-      </c>
-      <c r="Q257" t="str">
-        <v/>
-      </c>
-      <c r="R257" t="str">
-        <v/>
-      </c>
-      <c r="S257" t="str">
-        <v/>
-      </c>
-      <c r="T257" t="str">
-        <v/>
-      </c>
-      <c r="U257" t="str">
-        <v/>
-      </c>
-      <c r="V257" t="str">
-        <v/>
-      </c>
-      <c r="W257" t="str">
-        <v/>
-      </c>
-      <c r="X257" t="str">
-        <v/>
-      </c>
-      <c r="Y257" t="str">
-        <v/>
-      </c>
-      <c r="Z257" t="str">
-        <v/>
-      </c>
-      <c r="AA257" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA257"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA203"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -21785,26 +17303,26 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>UK</v>
+        <v>Thailand</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Thailand</v>
+        <v>Unrecorded</v>
       </c>
       <c r="B3">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Unrecorded</v>
+        <v>UK</v>
       </c>
       <c r="B4">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -21812,7 +17330,7 @@
         <v>Italy</v>
       </c>
       <c r="B5">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -21884,7 +17402,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B15">
-        <v>99</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -21892,7 +17410,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B16">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -21908,7 +17426,7 @@
         <v>Total entries</v>
       </c>
       <c r="B18">
-        <v>256</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20">
@@ -21916,7 +17434,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-03</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -17037,10 +17037,10 @@
         <v>Monday</v>
       </c>
       <c r="C201" t="str">
-        <v>Cernobbio</v>
+        <v>Milan</v>
       </c>
       <c r="D201" t="str">
-        <v>Cernobbio</v>
+        <v>Milan</v>
       </c>
       <c r="E201" t="str">
         <v>Italy</v>
@@ -17067,7 +17067,7 @@
         <v/>
       </c>
       <c r="M201" t="str">
-        <v>GPS</v>
+        <v>GPS + Manual</v>
       </c>
       <c r="N201" t="str">
         <v/>
@@ -17109,7 +17109,7 @@
         <v/>
       </c>
       <c r="AA201" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="202">
@@ -17135,10 +17135,10 @@
         <v/>
       </c>
       <c r="H202">
-        <v>45.4786558</v>
+        <v>45.4786514</v>
       </c>
       <c r="I202">
-        <v>9.1993042</v>
+        <v>9.1993028</v>
       </c>
       <c r="J202" t="str">
         <v/>
@@ -17153,28 +17153,28 @@
         <v>GPS</v>
       </c>
       <c r="N202" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="O202" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="P202" t="str">
-        <v/>
+        <v>45.81802, 9.06568</v>
       </c>
       <c r="Q202" t="str">
-        <v/>
+        <v>2026-03-03 22:12:03 GMT</v>
       </c>
       <c r="R202" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="S202" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="T202" t="str">
-        <v/>
+        <v>45.47865, 9.19928</v>
       </c>
       <c r="U202" t="str">
-        <v/>
+        <v>2026-03-03 07:12:31 GMT</v>
       </c>
       <c r="V202" t="str">
         <v/>
@@ -17434,7 +17434,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -17203,10 +17203,10 @@
         <v>Wednesday</v>
       </c>
       <c r="C203" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D203" t="str">
-        <v>Milan</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E203" t="str">
         <v>Italy</v>
@@ -17215,19 +17215,19 @@
         <v>BA579</v>
       </c>
       <c r="G203" t="str">
-        <v/>
-      </c>
-      <c r="H203" t="str">
-        <v/>
-      </c>
-      <c r="I203" t="str">
-        <v/>
+        <v>Bracket mismatch: evening=Oxford,UK vs morning=Cernobbio,Italy</v>
+      </c>
+      <c r="H203">
+        <v>45.816591</v>
+      </c>
+      <c r="I203">
+        <v>9.0639415</v>
       </c>
       <c r="J203" t="str">
-        <v/>
+        <v>2026-03-04 07:04:52 GMT</v>
       </c>
       <c r="K203" t="str">
-        <v/>
+        <v>12am</v>
       </c>
       <c r="L203" t="str">
         <v/>
@@ -17236,28 +17236,28 @@
         <v>Booking</v>
       </c>
       <c r="N203" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="O203" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="P203" t="str">
-        <v/>
+        <v>51.73297, -1.23730</v>
       </c>
       <c r="Q203" t="str">
-        <v/>
+        <v>2026-03-04 22:37:28 GMT</v>
       </c>
       <c r="R203" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="S203" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="T203" t="str">
-        <v/>
+        <v>45.81658, 9.06396</v>
       </c>
       <c r="U203" t="str">
-        <v/>
+        <v>2026-03-04 07:04:59 GMT</v>
       </c>
       <c r="V203" t="str">
         <v/>
@@ -17269,7 +17269,7 @@
         <v>calendar: Flight BA579: LIN - LHR, departs 15:30</v>
       </c>
       <c r="Y203" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Z203" t="str">
         <v>Yes</v>
@@ -17434,7 +17434,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA203"/>
+  <dimension ref="A1:AA204"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -17203,13 +17203,13 @@
         <v>Wednesday</v>
       </c>
       <c r="C203" t="str">
-        <v>Cernobbio</v>
+        <v>Oxford</v>
       </c>
       <c r="D203" t="str">
-        <v>Cernobbio</v>
+        <v>Oxford</v>
       </c>
       <c r="E203" t="str">
-        <v>Italy</v>
+        <v>UK</v>
       </c>
       <c r="F203" t="str">
         <v>BA579</v>
@@ -17218,13 +17218,13 @@
         <v>Bracket mismatch: evening=Oxford,UK vs morning=Cernobbio,Italy</v>
       </c>
       <c r="H203">
-        <v>45.816591</v>
+        <v>51.7329525</v>
       </c>
       <c r="I203">
-        <v>9.0639415</v>
+        <v>-1.2376135</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-03-04 07:04:52 GMT</v>
+        <v>2026-03-05 07:29:48 GMT</v>
       </c>
       <c r="K203" t="str">
         <v>12am</v>
@@ -17263,7 +17263,7 @@
         <v/>
       </c>
       <c r="W203" t="str">
-        <v/>
+        <v>GPS says UK, booking says Italy</v>
       </c>
       <c r="X203" t="str">
         <v>calendar: Flight BA579: LIN - LHR, departs 15:30</v>
@@ -17278,9 +17278,92 @@
         <v/>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="E204" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204">
+        <v>51.7329525</v>
+      </c>
+      <c r="I204">
+        <v>-1.2376135</v>
+      </c>
+      <c r="J204" t="str">
+        <v>2026-03-05 07:29:48 GMT</v>
+      </c>
+      <c r="K204" t="str">
+        <v>12am</v>
+      </c>
+      <c r="L204" t="str">
+        <v/>
+      </c>
+      <c r="M204" t="str">
+        <v>GPS</v>
+      </c>
+      <c r="N204" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="O204" t="str">
+        <v>UK</v>
+      </c>
+      <c r="P204" t="str">
+        <v>51.73295, -1.23767</v>
+      </c>
+      <c r="Q204" t="str">
+        <v>2026-03-05 23:00:53 GMT</v>
+      </c>
+      <c r="R204" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="S204" t="str">
+        <v>UK</v>
+      </c>
+      <c r="T204" t="str">
+        <v>51.73297, -1.23761</v>
+      </c>
+      <c r="U204" t="str">
+        <v>2026-03-05 08:07:29 GMT</v>
+      </c>
+      <c r="V204" t="str">
+        <v/>
+      </c>
+      <c r="W204" t="str">
+        <v/>
+      </c>
+      <c r="X204" t="str">
+        <v/>
+      </c>
+      <c r="Y204" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z204" t="str">
+        <v/>
+      </c>
+      <c r="AA204" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA204"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17322,7 +17405,7 @@
         <v>UK</v>
       </c>
       <c r="B4">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -17330,7 +17413,7 @@
         <v>Italy</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -17402,7 +17485,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B15">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
@@ -17410,7 +17493,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B16">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -17426,7 +17509,7 @@
         <v>Total entries</v>
       </c>
       <c r="B18">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20">
@@ -17434,7 +17517,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA204"/>
+  <dimension ref="A1:AA205"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -17233,7 +17233,7 @@
         <v/>
       </c>
       <c r="M203" t="str">
-        <v>Booking</v>
+        <v>GPS + Manual</v>
       </c>
       <c r="N203" t="str">
         <v>Oxford</v>
@@ -17275,7 +17275,7 @@
         <v>Yes</v>
       </c>
       <c r="AA203" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="204">
@@ -17301,13 +17301,13 @@
         <v/>
       </c>
       <c r="H204">
-        <v>51.7329525</v>
+        <v>51.732967382090834</v>
       </c>
       <c r="I204">
-        <v>-1.2376135</v>
+        <v>-1.2372750225652596</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-03-05 07:29:48 GMT</v>
+        <v>2026-03-06 09:08:06 GMT</v>
       </c>
       <c r="K204" t="str">
         <v>12am</v>
@@ -17319,16 +17319,16 @@
         <v>GPS</v>
       </c>
       <c r="N204" t="str">
-        <v>Oxford</v>
+        <v/>
       </c>
       <c r="O204" t="str">
-        <v>UK</v>
+        <v/>
       </c>
       <c r="P204" t="str">
-        <v>51.73295, -1.23767</v>
+        <v/>
       </c>
       <c r="Q204" t="str">
-        <v>2026-03-05 23:00:53 GMT</v>
+        <v/>
       </c>
       <c r="R204" t="str">
         <v>Oxford</v>
@@ -17361,9 +17361,92 @@
         <v/>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="E205" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205">
+        <v>51.7329759</v>
+      </c>
+      <c r="I205">
+        <v>-1.2373195</v>
+      </c>
+      <c r="J205" t="str">
+        <v>2026-03-06 07:34:13 GMT</v>
+      </c>
+      <c r="K205" t="str">
+        <v>12am</v>
+      </c>
+      <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str">
+        <v>GPS</v>
+      </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
+      <c r="R205" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="S205" t="str">
+        <v>UK</v>
+      </c>
+      <c r="T205" t="str">
+        <v>51.73307, -1.23736</v>
+      </c>
+      <c r="U205" t="str">
+        <v>2026-03-06 07:33:48 GMT</v>
+      </c>
+      <c r="V205" t="str">
+        <v/>
+      </c>
+      <c r="W205" t="str">
+        <v/>
+      </c>
+      <c r="X205" t="str">
+        <v/>
+      </c>
+      <c r="Y205" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z205" t="str">
+        <v/>
+      </c>
+      <c r="AA205" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA205"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17405,7 +17488,7 @@
         <v>UK</v>
       </c>
       <c r="B4">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -17485,7 +17568,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B15">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -17509,7 +17592,7 @@
         <v>Total entries</v>
       </c>
       <c r="B18">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -17402,16 +17402,16 @@
         <v>GPS</v>
       </c>
       <c r="N205" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="O205" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="P205" t="str">
-        <v/>
+        <v>51.73303, -1.23726</v>
       </c>
       <c r="Q205" t="str">
-        <v/>
+        <v>2026-03-06 23:12:52 GMT</v>
       </c>
       <c r="R205" t="str">
         <v>Oxford</v>
@@ -17600,7 +17600,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -17363,10 +17363,10 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="B205" t="str">
-        <v>Friday</v>
+        <v>Saturday</v>
       </c>
       <c r="C205" t="str">
         <v>Oxford</v>
@@ -17384,13 +17384,13 @@
         <v/>
       </c>
       <c r="H205">
-        <v>51.7329759</v>
+        <v>51.7329665</v>
       </c>
       <c r="I205">
-        <v>-1.2373195</v>
+        <v>-1.2373187</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-03-06 07:34:13 GMT</v>
+        <v>2026-03-07 06:38:24 GMT</v>
       </c>
       <c r="K205" t="str">
         <v>12am</v>
@@ -17402,28 +17402,28 @@
         <v>GPS</v>
       </c>
       <c r="N205" t="str">
-        <v>Oxford</v>
+        <v/>
       </c>
       <c r="O205" t="str">
-        <v>UK</v>
+        <v/>
       </c>
       <c r="P205" t="str">
-        <v>51.73303, -1.23726</v>
+        <v/>
       </c>
       <c r="Q205" t="str">
-        <v>2026-03-06 23:12:52 GMT</v>
+        <v/>
       </c>
       <c r="R205" t="str">
-        <v>Oxford</v>
+        <v/>
       </c>
       <c r="S205" t="str">
-        <v>UK</v>
+        <v/>
       </c>
       <c r="T205" t="str">
-        <v>51.73307, -1.23736</v>
+        <v/>
       </c>
       <c r="U205" t="str">
-        <v>2026-03-06 07:33:48 GMT</v>
+        <v/>
       </c>
       <c r="V205" t="str">
         <v/>
@@ -17600,7 +17600,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-08</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -17600,7 +17600,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA205"/>
+  <dimension ref="A1:AA207"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -17363,10 +17363,10 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-06</v>
       </c>
       <c r="B205" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="C205" t="str">
         <v>Oxford</v>
@@ -17383,70 +17383,236 @@
       <c r="G205" t="str">
         <v/>
       </c>
-      <c r="H205">
+      <c r="H205" t="str">
+        <v/>
+      </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
+      <c r="J205" t="str">
+        <v/>
+      </c>
+      <c r="K205" t="str">
+        <v/>
+      </c>
+      <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
+      <c r="R205" t="str">
+        <v/>
+      </c>
+      <c r="S205" t="str">
+        <v/>
+      </c>
+      <c r="T205" t="str">
+        <v/>
+      </c>
+      <c r="U205" t="str">
+        <v/>
+      </c>
+      <c r="V205" t="str">
+        <v/>
+      </c>
+      <c r="W205" t="str">
+        <v/>
+      </c>
+      <c r="X205" t="str">
+        <v/>
+      </c>
+      <c r="Y205" t="str">
+        <v/>
+      </c>
+      <c r="Z205" t="str">
+        <v/>
+      </c>
+      <c r="AA205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="E206" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206">
         <v>51.7329665</v>
       </c>
-      <c r="I205">
+      <c r="I206">
         <v>-1.2373187</v>
       </c>
-      <c r="J205" t="str">
+      <c r="J206" t="str">
         <v>2026-03-07 06:38:24 GMT</v>
       </c>
-      <c r="K205" t="str">
+      <c r="K206" t="str">
         <v>12am</v>
       </c>
-      <c r="L205" t="str">
-        <v/>
-      </c>
-      <c r="M205" t="str">
+      <c r="L206" t="str">
+        <v/>
+      </c>
+      <c r="M206" t="str">
         <v>GPS</v>
       </c>
-      <c r="N205" t="str">
-        <v/>
-      </c>
-      <c r="O205" t="str">
-        <v/>
-      </c>
-      <c r="P205" t="str">
-        <v/>
-      </c>
-      <c r="Q205" t="str">
-        <v/>
-      </c>
-      <c r="R205" t="str">
-        <v/>
-      </c>
-      <c r="S205" t="str">
-        <v/>
-      </c>
-      <c r="T205" t="str">
-        <v/>
-      </c>
-      <c r="U205" t="str">
-        <v/>
-      </c>
-      <c r="V205" t="str">
-        <v/>
-      </c>
-      <c r="W205" t="str">
-        <v/>
-      </c>
-      <c r="X205" t="str">
-        <v/>
-      </c>
-      <c r="Y205" t="str">
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v/>
+      </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
+      <c r="R206" t="str">
+        <v/>
+      </c>
+      <c r="S206" t="str">
+        <v/>
+      </c>
+      <c r="T206" t="str">
+        <v/>
+      </c>
+      <c r="U206" t="str">
+        <v/>
+      </c>
+      <c r="V206" t="str">
+        <v/>
+      </c>
+      <c r="W206" t="str">
+        <v/>
+      </c>
+      <c r="X206" t="str">
+        <v/>
+      </c>
+      <c r="Y206" t="str">
         <v>Yes</v>
       </c>
-      <c r="Z205" t="str">
-        <v/>
-      </c>
-      <c r="AA205" t="str">
+      <c r="Z206" t="str">
+        <v/>
+      </c>
+      <c r="AA206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Sunday</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="E207" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v>Late backfill: GPS captured 2026-03-09 08:55:05 GMT (midnight push missed)</v>
+      </c>
+      <c r="H207">
+        <v>51.7329639</v>
+      </c>
+      <c r="I207">
+        <v>-1.2374748</v>
+      </c>
+      <c r="J207" t="str">
+        <v>2026-03-09 08:55:05 GMT</v>
+      </c>
+      <c r="K207" t="str">
+        <v>backfill</v>
+      </c>
+      <c r="L207" t="str">
+        <v/>
+      </c>
+      <c r="M207" t="str">
+        <v>GPS</v>
+      </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
+      <c r="R207" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="S207" t="str">
+        <v>UK</v>
+      </c>
+      <c r="T207" t="str">
+        <v>51.73296, -1.23747</v>
+      </c>
+      <c r="U207" t="str">
+        <v>2026-03-09 08:55:05 GMT</v>
+      </c>
+      <c r="V207" t="str">
+        <v/>
+      </c>
+      <c r="W207" t="str">
+        <v/>
+      </c>
+      <c r="X207" t="str">
+        <v/>
+      </c>
+      <c r="Y207" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z207" t="str">
+        <v/>
+      </c>
+      <c r="AA207" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA207"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17488,7 +17654,7 @@
         <v>UK</v>
       </c>
       <c r="B4">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -17568,7 +17734,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B15">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -17592,7 +17758,7 @@
         <v>Total entries</v>
       </c>
       <c r="B18">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20">
@@ -17600,7 +17766,7 @@
         <v>Backup date</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA207"/>
+  <dimension ref="A1:AA209"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -17610,16 +17610,182 @@
         <v/>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="E208" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v>Late backfill: GPS captured 2026-03-10 10:06:11 GMT (midnight push missed)</v>
+      </c>
+      <c r="H208">
+        <v>51.732964</v>
+      </c>
+      <c r="I208">
+        <v>-1.2373389</v>
+      </c>
+      <c r="J208" t="str">
+        <v>2026-03-10 10:06:11 GMT</v>
+      </c>
+      <c r="K208" t="str">
+        <v>backfill</v>
+      </c>
+      <c r="L208" t="str">
+        <v/>
+      </c>
+      <c r="M208" t="str">
+        <v>GPS</v>
+      </c>
+      <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
+        <v/>
+      </c>
+      <c r="P208" t="str">
+        <v/>
+      </c>
+      <c r="Q208" t="str">
+        <v/>
+      </c>
+      <c r="R208" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="S208" t="str">
+        <v>UK</v>
+      </c>
+      <c r="T208" t="str">
+        <v>51.73297, -1.23732</v>
+      </c>
+      <c r="U208" t="str">
+        <v>2026-03-10 10:24:13 GMT</v>
+      </c>
+      <c r="V208" t="str">
+        <v/>
+      </c>
+      <c r="W208" t="str">
+        <v/>
+      </c>
+      <c r="X208" t="str">
+        <v/>
+      </c>
+      <c r="Y208" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z208" t="str">
+        <v/>
+      </c>
+      <c r="AA208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="C209" t="str">
+        <v>The Luggage Room</v>
+      </c>
+      <c r="D209" t="str">
+        <v>City of Westminster</v>
+      </c>
+      <c r="E209" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209">
+        <v>51.5124577</v>
+      </c>
+      <c r="I209">
+        <v>-0.1508501</v>
+      </c>
+      <c r="J209" t="str">
+        <v>2026-03-10 23:18:43 GMT</v>
+      </c>
+      <c r="K209" t="str">
+        <v>12am</v>
+      </c>
+      <c r="L209" t="str">
+        <v/>
+      </c>
+      <c r="M209" t="str">
+        <v>GPS</v>
+      </c>
+      <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
+        <v/>
+      </c>
+      <c r="P209" t="str">
+        <v/>
+      </c>
+      <c r="Q209" t="str">
+        <v/>
+      </c>
+      <c r="R209" t="str">
+        <v/>
+      </c>
+      <c r="S209" t="str">
+        <v/>
+      </c>
+      <c r="T209" t="str">
+        <v/>
+      </c>
+      <c r="U209" t="str">
+        <v/>
+      </c>
+      <c r="V209" t="str">
+        <v/>
+      </c>
+      <c r="W209" t="str">
+        <v/>
+      </c>
+      <c r="X209" t="str">
+        <v/>
+      </c>
+      <c r="Y209" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z209" t="str">
+        <v/>
+      </c>
+      <c r="AA209" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA209"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -17654,7 +17820,7 @@
         <v>UK</v>
       </c>
       <c r="B4">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -17729,49 +17895,57 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>UK nights (max 90)</v>
-      </c>
-      <c r="B15">
-        <v>48</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Italy days (target 183+)</v>
+        <v>UK nights (max 90)</v>
       </c>
       <c r="B16">
-        <v>18</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>UK work days (max 30)</v>
+        <v>Italy days (target 183+)</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>UK work days (max 30)</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>Total entries</v>
       </c>
-      <c r="B18">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
+      <c r="B19">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
         <v>Backup date</v>
       </c>
-      <c r="B20" t="str">
-        <v>2026-03-10</v>
+      <c r="B21" t="str">
+        <v>2026-03-11</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA209"/>
+  <dimension ref="A1:AA210"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -17648,7 +17648,7 @@
         <v/>
       </c>
       <c r="M208" t="str">
-        <v>GPS</v>
+        <v>GPS + Manual</v>
       </c>
       <c r="N208" t="str">
         <v/>
@@ -17690,7 +17690,7 @@
         <v/>
       </c>
       <c r="AA208" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="209">
@@ -17716,13 +17716,13 @@
         <v/>
       </c>
       <c r="H209">
-        <v>51.5124577</v>
+        <v>51.5124927</v>
       </c>
       <c r="I209">
-        <v>-0.1508501</v>
+        <v>-0.1508516</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-03-10 23:18:43 GMT</v>
+        <v>2026-03-11 08:05:59 GMT</v>
       </c>
       <c r="K209" t="str">
         <v>12am</v>
@@ -17731,7 +17731,7 @@
         <v/>
       </c>
       <c r="M209" t="str">
-        <v>GPS</v>
+        <v>GPS + Manual</v>
       </c>
       <c r="N209" t="str">
         <v/>
@@ -17746,16 +17746,16 @@
         <v/>
       </c>
       <c r="R209" t="str">
-        <v/>
+        <v>City of Westminster</v>
       </c>
       <c r="S209" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="T209" t="str">
-        <v/>
+        <v>51.51248, -0.15079</v>
       </c>
       <c r="U209" t="str">
-        <v/>
+        <v>2026-03-11 08:25:21 GMT</v>
       </c>
       <c r="V209" t="str">
         <v/>
@@ -17773,12 +17773,95 @@
         <v/>
       </c>
       <c r="AA209" t="str">
-        <v/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="E210" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210">
+        <v>51.7329703</v>
+      </c>
+      <c r="I210">
+        <v>-1.2373051</v>
+      </c>
+      <c r="J210" t="str">
+        <v>2026-03-11 23:02:58 GMT</v>
+      </c>
+      <c r="K210" t="str">
+        <v>12am</v>
+      </c>
+      <c r="L210" t="str">
+        <v/>
+      </c>
+      <c r="M210" t="str">
+        <v>GPS + Manual</v>
+      </c>
+      <c r="N210" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="O210" t="str">
+        <v>UK</v>
+      </c>
+      <c r="P210" t="str">
+        <v>51.73299, -1.23739</v>
+      </c>
+      <c r="Q210" t="str">
+        <v>2026-03-11 23:03:10 GMT</v>
+      </c>
+      <c r="R210" t="str">
+        <v/>
+      </c>
+      <c r="S210" t="str">
+        <v/>
+      </c>
+      <c r="T210" t="str">
+        <v/>
+      </c>
+      <c r="U210" t="str">
+        <v/>
+      </c>
+      <c r="V210" t="str">
+        <v/>
+      </c>
+      <c r="W210" t="str">
+        <v/>
+      </c>
+      <c r="X210" t="str">
+        <v/>
+      </c>
+      <c r="Y210" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z210" t="str">
+        <v/>
+      </c>
+      <c r="AA210" t="str">
+        <v>Yes</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA210"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17820,7 +17903,7 @@
         <v>UK</v>
       </c>
       <c r="B4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -17908,7 +17991,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B16">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -17932,7 +18015,7 @@
         <v>Total entries</v>
       </c>
       <c r="B19">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21">
@@ -17940,7 +18023,7 @@
         <v>Backup date</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA210"/>
+  <dimension ref="A1:AA211"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -17799,13 +17799,13 @@
         <v/>
       </c>
       <c r="H210">
-        <v>51.7329703</v>
+        <v>51.7329737</v>
       </c>
       <c r="I210">
-        <v>-1.2373051</v>
+        <v>-1.2373169</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-03-11 23:02:58 GMT</v>
+        <v>2026-03-12 07:39:46 GMT</v>
       </c>
       <c r="K210" t="str">
         <v>12am</v>
@@ -17859,9 +17859,92 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="E211" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211">
+        <v>51.7329737</v>
+      </c>
+      <c r="I211">
+        <v>-1.2373169</v>
+      </c>
+      <c r="J211" t="str">
+        <v>2026-03-12 07:39:46 GMT</v>
+      </c>
+      <c r="K211" t="str">
+        <v>12am</v>
+      </c>
+      <c r="L211" t="str">
+        <v/>
+      </c>
+      <c r="M211" t="str">
+        <v>GPS</v>
+      </c>
+      <c r="N211" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" t="str">
+        <v/>
+      </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
+      <c r="R211" t="str">
+        <v/>
+      </c>
+      <c r="S211" t="str">
+        <v/>
+      </c>
+      <c r="T211" t="str">
+        <v/>
+      </c>
+      <c r="U211" t="str">
+        <v/>
+      </c>
+      <c r="V211" t="str">
+        <v/>
+      </c>
+      <c r="W211" t="str">
+        <v/>
+      </c>
+      <c r="X211" t="str">
+        <v/>
+      </c>
+      <c r="Y211" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z211" t="str">
+        <v/>
+      </c>
+      <c r="AA211" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA210"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA211"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17903,7 +17986,7 @@
         <v>UK</v>
       </c>
       <c r="B4">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -17991,7 +18074,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B16">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
@@ -18015,7 +18098,7 @@
         <v>Total entries</v>
       </c>
       <c r="B19">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21">
@@ -18023,7 +18106,7 @@
         <v>Backup date</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-13</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA211"/>
+  <dimension ref="A1:AA212"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -17912,16 +17912,16 @@
         <v/>
       </c>
       <c r="R211" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="S211" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="T211" t="str">
-        <v/>
+        <v>51.73295, -1.23730</v>
       </c>
       <c r="U211" t="str">
-        <v/>
+        <v>2026-03-13 07:58:53 GMT</v>
       </c>
       <c r="V211" t="str">
         <v/>
@@ -17942,9 +17942,92 @@
         <v/>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="E212" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+      <c r="H212">
+        <v>51.7329725</v>
+      </c>
+      <c r="I212">
+        <v>-1.2372984</v>
+      </c>
+      <c r="J212" t="str">
+        <v>2026-03-13 22:59:41 GMT</v>
+      </c>
+      <c r="K212" t="str">
+        <v>12am</v>
+      </c>
+      <c r="L212" t="str">
+        <v/>
+      </c>
+      <c r="M212" t="str">
+        <v>GPS</v>
+      </c>
+      <c r="N212" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
+        <v/>
+      </c>
+      <c r="P212" t="str">
+        <v/>
+      </c>
+      <c r="Q212" t="str">
+        <v/>
+      </c>
+      <c r="R212" t="str">
+        <v/>
+      </c>
+      <c r="S212" t="str">
+        <v/>
+      </c>
+      <c r="T212" t="str">
+        <v/>
+      </c>
+      <c r="U212" t="str">
+        <v/>
+      </c>
+      <c r="V212" t="str">
+        <v/>
+      </c>
+      <c r="W212" t="str">
+        <v/>
+      </c>
+      <c r="X212" t="str">
+        <v/>
+      </c>
+      <c r="Y212" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z212" t="str">
+        <v/>
+      </c>
+      <c r="AA212" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA211"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA212"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17986,7 +18069,7 @@
         <v>UK</v>
       </c>
       <c r="B4">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -18074,7 +18157,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B16">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -18098,7 +18181,7 @@
         <v>Total entries</v>
       </c>
       <c r="B19">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21">
@@ -18106,7 +18189,7 @@
         <v>Backup date</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-14</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA212"/>
+  <dimension ref="A1:AA213"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -17995,16 +17995,16 @@
         <v/>
       </c>
       <c r="R212" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="S212" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="T212" t="str">
-        <v/>
+        <v>51.73297, -1.23734</v>
       </c>
       <c r="U212" t="str">
-        <v/>
+        <v>2026-03-14 07:58:58 GMT</v>
       </c>
       <c r="V212" t="str">
         <v/>
@@ -18025,9 +18025,92 @@
         <v/>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C213" t="str">
+        <v>A34</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Vale of White Horse</v>
+      </c>
+      <c r="E213" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="F213" t="str">
+        <v/>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+      <c r="H213">
+        <v>51.6655096</v>
+      </c>
+      <c r="I213">
+        <v>-1.312472</v>
+      </c>
+      <c r="J213" t="str">
+        <v>2026-03-14 23:04:20 GMT</v>
+      </c>
+      <c r="K213" t="str">
+        <v>12am</v>
+      </c>
+      <c r="L213" t="str">
+        <v/>
+      </c>
+      <c r="M213" t="str">
+        <v>GPS</v>
+      </c>
+      <c r="N213" t="str">
+        <v>Vale of White Horse</v>
+      </c>
+      <c r="O213" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="P213" t="str">
+        <v>51.66551, -1.31247</v>
+      </c>
+      <c r="Q213" t="str">
+        <v>2026-03-14 23:04:20 GMT</v>
+      </c>
+      <c r="R213" t="str">
+        <v/>
+      </c>
+      <c r="S213" t="str">
+        <v/>
+      </c>
+      <c r="T213" t="str">
+        <v/>
+      </c>
+      <c r="U213" t="str">
+        <v/>
+      </c>
+      <c r="V213" t="str">
+        <v/>
+      </c>
+      <c r="W213" t="str">
+        <v/>
+      </c>
+      <c r="X213" t="str">
+        <v/>
+      </c>
+      <c r="Y213" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z213" t="str">
+        <v/>
+      </c>
+      <c r="AA213" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA212"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA213"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -18106,15 +18189,15 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Singapore</v>
+        <v>United Kingdom</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Germany</v>
+        <v>Singapore</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -18122,7 +18205,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>NA</v>
+        <v>Germany</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -18130,7 +18213,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Taiwan</v>
+        <v>NA</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -18138,7 +18221,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Switzerland</v>
+        <v>Taiwan</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -18146,7 +18229,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>United Kingdom</v>
+        <v>Switzerland</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -18181,7 +18264,7 @@
         <v>Total entries</v>
       </c>
       <c r="B19">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21">
@@ -18189,7 +18272,7 @@
         <v>Backup date</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-15</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA213"/>
+  <dimension ref="A1:AA214"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -18045,7 +18045,7 @@
         <v/>
       </c>
       <c r="G213" t="str">
-        <v/>
+        <v>Bracket mismatch: evening=Vale of White Horse,United Kingdom vs morning=Oxford,UK</v>
       </c>
       <c r="H213">
         <v>51.6655096</v>
@@ -18063,7 +18063,7 @@
         <v/>
       </c>
       <c r="M213" t="str">
-        <v>GPS</v>
+        <v>GPS + Manual</v>
       </c>
       <c r="N213" t="str">
         <v>Vale of White Horse</v>
@@ -18078,16 +18078,16 @@
         <v>2026-03-14 23:04:20 GMT</v>
       </c>
       <c r="R213" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="S213" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="T213" t="str">
-        <v/>
+        <v>51.73297, -1.23733</v>
       </c>
       <c r="U213" t="str">
-        <v/>
+        <v>2026-03-15 07:34:22 GMT</v>
       </c>
       <c r="V213" t="str">
         <v/>
@@ -18105,12 +18105,95 @@
         <v/>
       </c>
       <c r="AA213" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Sunday</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="E214" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+      <c r="H214">
+        <v>51.7331115</v>
+      </c>
+      <c r="I214">
+        <v>-1.2374288</v>
+      </c>
+      <c r="J214" t="str">
+        <v>2026-03-15 23:03:48 GMT</v>
+      </c>
+      <c r="K214" t="str">
+        <v>12am</v>
+      </c>
+      <c r="L214" t="str">
+        <v/>
+      </c>
+      <c r="M214" t="str">
+        <v>GPS</v>
+      </c>
+      <c r="N214" t="str">
+        <v>Oxford</v>
+      </c>
+      <c r="O214" t="str">
+        <v>UK</v>
+      </c>
+      <c r="P214" t="str">
+        <v>51.73311, -1.23743</v>
+      </c>
+      <c r="Q214" t="str">
+        <v>2026-03-15 23:03:48 GMT</v>
+      </c>
+      <c r="R214" t="str">
+        <v/>
+      </c>
+      <c r="S214" t="str">
+        <v/>
+      </c>
+      <c r="T214" t="str">
+        <v/>
+      </c>
+      <c r="U214" t="str">
+        <v/>
+      </c>
+      <c r="V214" t="str">
+        <v/>
+      </c>
+      <c r="W214" t="str">
+        <v/>
+      </c>
+      <c r="X214" t="str">
+        <v/>
+      </c>
+      <c r="Y214" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z214" t="str">
+        <v/>
+      </c>
+      <c r="AA214" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA213"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA214"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -18152,7 +18235,7 @@
         <v>UK</v>
       </c>
       <c r="B4">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -18240,7 +18323,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B16">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -18264,7 +18347,7 @@
         <v>Total entries</v>
       </c>
       <c r="B19">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
@@ -18272,7 +18355,7 @@
         <v>Backup date</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -20867,7 +20867,7 @@
         <v>BA1583, BA4598</v>
       </c>
       <c r="G247" t="str">
-        <v>Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21…[TRUNCATED]</v>
+        <v/>
       </c>
       <c r="H247" t="str">
         <v>40.6486852</v>
@@ -20927,7 +20927,7 @@
         <v>Yes</v>
       </c>
       <c r="AA247" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="248">
@@ -21033,7 +21033,7 @@
         <v/>
       </c>
       <c r="G249" t="str">
-        <v>Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST</v>
+        <v/>
       </c>
       <c r="H249" t="str">
         <v>30.2916689</v>
@@ -21093,7 +21093,7 @@
         <v/>
       </c>
       <c r="AA249" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="250">
